--- a/YarnBook-TEX WEAVES.xlsx
+++ b/YarnBook-TEX WEAVES.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="90" windowWidth="28755" windowHeight="12090" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="90" windowWidth="28755" windowHeight="12090"/>
   </bookViews>
   <sheets>
     <sheet name="25-26" sheetId="1" r:id="rId1"/>
@@ -3176,7 +3176,7 @@
       <c r="AG15" s="2"/>
       <c r="AH15" s="23"/>
     </row>
-    <row r="16" spans="1:34" hidden="1">
+    <row r="16" spans="1:34">
       <c r="A16" t="s">
         <v>113</v>
       </c>
@@ -3222,7 +3222,7 @@
       <c r="O16" s="2"/>
       <c r="P16" s="7">
         <f t="shared" ref="P16:P17" ca="1" si="9">DAYS360(L16,TODAY())-(1)</f>
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
@@ -3244,7 +3244,7 @@
       <c r="AG16" s="2"/>
       <c r="AH16" s="23"/>
     </row>
-    <row r="17" spans="1:34" hidden="1">
+    <row r="17" spans="1:34">
       <c r="A17" t="s">
         <v>113</v>
       </c>
@@ -3294,11 +3294,11 @@
       <c r="O17" s="49"/>
       <c r="P17" s="53">
         <f t="shared" ca="1" si="9"/>
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q17" s="66">
         <f t="shared" ref="Q17:Q26" ca="1" si="10">0.18*P17*M17/365</f>
-        <v>10935.516016780275</v>
+        <v>10968.062195401646</v>
       </c>
       <c r="R17" s="49"/>
       <c r="S17" s="49">
@@ -3334,7 +3334,7 @@
       <c r="AG17" s="49"/>
       <c r="AH17" s="57"/>
     </row>
-    <row r="18" spans="1:34" hidden="1">
+    <row r="18" spans="1:34">
       <c r="A18" t="s">
         <v>113</v>
       </c>
@@ -3967,7 +3967,7 @@
       <c r="AG25" s="2"/>
       <c r="AH25" s="23"/>
     </row>
-    <row r="26" spans="1:34" hidden="1">
+    <row r="26" spans="1:34">
       <c r="A26" t="s">
         <v>113</v>
       </c>
@@ -4046,7 +4046,7 @@
       <c r="AG26" s="2"/>
       <c r="AH26" s="23"/>
     </row>
-    <row r="27" spans="1:34">
+    <row r="27" spans="1:34" hidden="1">
       <c r="A27" t="s">
         <v>113</v>
       </c>
@@ -5008,7 +5008,7 @@
       <c r="AG38" s="2"/>
       <c r="AH38" s="23"/>
     </row>
-    <row r="39" spans="1:34">
+    <row r="39" spans="1:34" hidden="1">
       <c r="A39" t="s">
         <v>113</v>
       </c>
@@ -5087,7 +5087,7 @@
       <c r="AG39" s="2"/>
       <c r="AH39" s="23"/>
     </row>
-    <row r="40" spans="1:34" ht="15.75" hidden="1" thickBot="1">
+    <row r="40" spans="1:34" ht="15.75" thickBot="1">
       <c r="A40" t="s">
         <v>113</v>
       </c>
@@ -5159,7 +5159,7 @@
       <c r="AG40" s="2"/>
       <c r="AH40" s="23"/>
     </row>
-    <row r="41" spans="1:34">
+    <row r="41" spans="1:34" hidden="1">
       <c r="A41" t="s">
         <v>113</v>
       </c>
@@ -5697,7 +5697,7 @@
       <c r="AG47" s="2"/>
       <c r="AH47" s="23"/>
     </row>
-    <row r="48" spans="1:34">
+    <row r="48" spans="1:34" hidden="1">
       <c r="A48" t="s">
         <v>113</v>
       </c>
@@ -6094,7 +6094,7 @@
       <c r="AG52" s="2"/>
       <c r="AH52" s="23"/>
     </row>
-    <row r="53" spans="1:34" hidden="1">
+    <row r="53" spans="1:34">
       <c r="A53" t="s">
         <v>113</v>
       </c>
@@ -6166,7 +6166,7 @@
       <c r="AG53" s="2"/>
       <c r="AH53" s="23"/>
     </row>
-    <row r="54" spans="1:34">
+    <row r="54" spans="1:34" hidden="1">
       <c r="A54" t="s">
         <v>113</v>
       </c>
@@ -6564,7 +6564,7 @@
       <c r="AG58" s="2"/>
       <c r="AH58" s="23"/>
     </row>
-    <row r="59" spans="1:34">
+    <row r="59" spans="1:34" hidden="1">
       <c r="A59" t="s">
         <v>113</v>
       </c>
@@ -6638,7 +6638,7 @@
       <c r="AG59" s="2"/>
       <c r="AH59" s="23"/>
     </row>
-    <row r="60" spans="1:34">
+    <row r="60" spans="1:34" hidden="1">
       <c r="A60" t="s">
         <v>113</v>
       </c>
@@ -6876,7 +6876,7 @@
       <c r="AG62" s="2"/>
       <c r="AH62" s="23"/>
     </row>
-    <row r="63" spans="1:34">
+    <row r="63" spans="1:34" hidden="1">
       <c r="A63" s="85" t="s">
         <v>113</v>
       </c>
@@ -6929,7 +6929,7 @@
         <v>30</v>
       </c>
       <c r="Q63" s="66">
-        <f t="shared" ref="Q63" si="39">0.18*P63*M63/365</f>
+        <f t="shared" ref="Q63:Q64" si="39">0.18*P63*M63/365</f>
         <v>2701.6697553248218</v>
       </c>
       <c r="R63" s="89"/>
@@ -6955,7 +6955,7 @@
       <c r="AG63" s="2"/>
       <c r="AH63" s="23"/>
     </row>
-    <row r="64" spans="1:34" hidden="1">
+    <row r="64" spans="1:34">
       <c r="A64" t="s">
         <v>113</v>
       </c>
@@ -7007,7 +7007,10 @@
         <f t="shared" ref="P64:P65" si="40">DAYS360(L64,W64)-(1)</f>
         <v>75</v>
       </c>
-      <c r="Q64" s="2"/>
+      <c r="Q64" s="66">
+        <f t="shared" si="39"/>
+        <v>5164.9504824476717</v>
+      </c>
       <c r="R64" s="2"/>
       <c r="S64" s="2">
         <v>22819</v>
@@ -7103,7 +7106,7 @@
       <c r="AG65" s="2"/>
       <c r="AH65" s="23"/>
     </row>
-    <row r="66" spans="1:34">
+    <row r="66" spans="1:34" hidden="1">
       <c r="A66" t="s">
         <v>113</v>
       </c>
@@ -7156,7 +7159,7 @@
         <v>24</v>
       </c>
       <c r="Q66" s="66">
-        <f t="shared" ref="Q66" si="41">0.18*P66*M66/365</f>
+        <f t="shared" ref="Q66:Q67" si="41">0.18*P66*M66/365</f>
         <v>1670.8139805789374</v>
       </c>
       <c r="R66" s="2"/>
@@ -7182,7 +7185,7 @@
       <c r="AG66" s="2"/>
       <c r="AH66" s="23"/>
     </row>
-    <row r="67" spans="1:34" hidden="1">
+    <row r="67" spans="1:34">
       <c r="A67" t="s">
         <v>113</v>
       </c>
@@ -7232,7 +7235,10 @@
         <f t="shared" ref="P67:P68" si="42">DAYS360(L67,W67)-(1)</f>
         <v>73</v>
       </c>
-      <c r="Q67" s="2"/>
+      <c r="Q67" s="66">
+        <f t="shared" si="41"/>
+        <v>3398.3990207999996</v>
+      </c>
       <c r="R67" s="2"/>
       <c r="S67" s="2">
         <v>23010</v>
@@ -7407,7 +7413,7 @@
       <c r="AG69" s="2"/>
       <c r="AH69" s="23"/>
     </row>
-    <row r="70" spans="1:34">
+    <row r="70" spans="1:34" hidden="1">
       <c r="A70" t="s">
         <v>113</v>
       </c>
@@ -7460,7 +7466,7 @@
         <v>21</v>
       </c>
       <c r="Q70" s="66">
-        <f t="shared" ref="Q70:Q71" si="46">0.18*P70*M70/365</f>
+        <f t="shared" ref="Q70:Q72" si="46">0.18*P70*M70/365</f>
         <v>496.96882027397254</v>
       </c>
       <c r="R70" s="2"/>
@@ -7486,7 +7492,7 @@
       <c r="AG70" s="2"/>
       <c r="AH70" s="23"/>
     </row>
-    <row r="71" spans="1:34">
+    <row r="71" spans="1:34" hidden="1">
       <c r="A71" t="s">
         <v>113</v>
       </c>
@@ -7565,7 +7571,7 @@
       <c r="AG71" s="2"/>
       <c r="AH71" s="23"/>
     </row>
-    <row r="72" spans="1:34" hidden="1">
+    <row r="72" spans="1:34">
       <c r="A72" t="s">
         <v>113</v>
       </c>
@@ -7617,7 +7623,10 @@
         <f t="shared" si="45"/>
         <v>56</v>
       </c>
-      <c r="Q72" s="2"/>
+      <c r="Q72" s="66">
+        <f t="shared" si="46"/>
+        <v>7745.0841259054032</v>
+      </c>
       <c r="R72" s="2"/>
       <c r="S72" s="2">
         <v>24850</v>
@@ -7639,7 +7648,7 @@
       <c r="AG72" s="2"/>
       <c r="AH72" s="23"/>
     </row>
-    <row r="73" spans="1:34">
+    <row r="73" spans="1:34" hidden="1">
       <c r="A73" t="s">
         <v>113</v>
       </c>
@@ -7692,7 +7701,7 @@
         <v>23</v>
       </c>
       <c r="Q73" s="66">
-        <f t="shared" ref="Q73" si="47">0.18*P73*M73/365</f>
+        <f t="shared" ref="Q73:Q77" si="47">0.18*P73*M73/365</f>
         <v>966.10586301369847</v>
       </c>
       <c r="R73" s="2"/>
@@ -7718,7 +7727,7 @@
       <c r="AG73" s="2"/>
       <c r="AH73" s="23"/>
     </row>
-    <row r="74" spans="1:34" hidden="1">
+    <row r="74" spans="1:34">
       <c r="A74" t="s">
         <v>113</v>
       </c>
@@ -7770,7 +7779,10 @@
         <f t="shared" ref="P74:P77" si="48">DAYS360(L74,W74)-(1)</f>
         <v>40</v>
       </c>
-      <c r="Q74" s="2"/>
+      <c r="Q74" s="66">
+        <f t="shared" si="47"/>
+        <v>1125.922191780822</v>
+      </c>
       <c r="R74" s="2"/>
       <c r="S74" s="2">
         <v>26396</v>
@@ -7792,7 +7804,7 @@
       <c r="AG74" s="2"/>
       <c r="AH74" s="23"/>
     </row>
-    <row r="75" spans="1:34" hidden="1">
+    <row r="75" spans="1:34">
       <c r="A75" t="s">
         <v>113</v>
       </c>
@@ -7842,7 +7854,10 @@
         <f t="shared" si="48"/>
         <v>36</v>
       </c>
-      <c r="Q75" s="2"/>
+      <c r="Q75" s="66">
+        <f t="shared" si="47"/>
+        <v>2451.438991525808</v>
+      </c>
       <c r="R75" s="2"/>
       <c r="S75" s="2">
         <v>26842</v>
@@ -7864,7 +7879,7 @@
       <c r="AG75" s="2"/>
       <c r="AH75" s="23"/>
     </row>
-    <row r="76" spans="1:34" hidden="1">
+    <row r="76" spans="1:34">
       <c r="A76" t="s">
         <v>113</v>
       </c>
@@ -7914,7 +7929,10 @@
         <f t="shared" si="48"/>
         <v>57</v>
       </c>
-      <c r="Q76" s="2"/>
+      <c r="Q76" s="66">
+        <f t="shared" si="47"/>
+        <v>1782.7101369863014</v>
+      </c>
       <c r="R76" s="2"/>
       <c r="S76" s="2">
         <v>26999</v>
@@ -7936,7 +7954,7 @@
       <c r="AG76" s="2"/>
       <c r="AH76" s="23"/>
     </row>
-    <row r="77" spans="1:34" hidden="1">
+    <row r="77" spans="1:34">
       <c r="A77" t="s">
         <v>113</v>
       </c>
@@ -7986,7 +8004,10 @@
         <f t="shared" si="48"/>
         <v>51</v>
       </c>
-      <c r="Q77" s="2"/>
+      <c r="Q77" s="66">
+        <f t="shared" si="47"/>
+        <v>3462.6637448451615</v>
+      </c>
       <c r="R77" s="2"/>
       <c r="S77" s="2">
         <v>27689</v>
@@ -8008,7 +8029,7 @@
       <c r="AG77" s="2"/>
       <c r="AH77" s="23"/>
     </row>
-    <row r="78" spans="1:34">
+    <row r="78" spans="1:34" hidden="1">
       <c r="A78" t="s">
         <v>113</v>
       </c>
@@ -8061,7 +8082,7 @@
         <v>-2</v>
       </c>
       <c r="Q78" s="66">
-        <f t="shared" ref="Q78:Q83" si="49">0.18*P78*M78/365</f>
+        <f t="shared" ref="Q78:Q84" si="49">0.18*P78*M78/365</f>
         <v>-212.56227827566028</v>
       </c>
       <c r="R78" s="2"/>
@@ -8087,7 +8108,7 @@
       <c r="AG78" s="2"/>
       <c r="AH78" s="23"/>
     </row>
-    <row r="79" spans="1:34" hidden="1">
+    <row r="79" spans="1:34">
       <c r="A79" t="s">
         <v>113</v>
       </c>
@@ -8137,7 +8158,10 @@
         <f t="shared" ref="P79" si="50">DAYS360(L79,W79)-(1)</f>
         <v>45</v>
       </c>
-      <c r="Q79" s="2"/>
+      <c r="Q79" s="66">
+        <f t="shared" si="49"/>
+        <v>6652.1084360547939</v>
+      </c>
       <c r="R79" s="2"/>
       <c r="S79" s="2">
         <v>28387</v>
@@ -8159,7 +8183,7 @@
       <c r="AG79" s="2"/>
       <c r="AH79" s="23"/>
     </row>
-    <row r="80" spans="1:34">
+    <row r="80" spans="1:34" hidden="1">
       <c r="A80" t="s">
         <v>113</v>
       </c>
@@ -8238,7 +8262,7 @@
       <c r="AG80" s="2"/>
       <c r="AH80" s="23"/>
     </row>
-    <row r="81" spans="1:34">
+    <row r="81" spans="1:34" hidden="1">
       <c r="A81" t="s">
         <v>113</v>
       </c>
@@ -8315,7 +8339,7 @@
       <c r="AG81" s="2"/>
       <c r="AH81" s="23"/>
     </row>
-    <row r="82" spans="1:34" hidden="1">
+    <row r="82" spans="1:34">
       <c r="A82" t="s">
         <v>113</v>
       </c>
@@ -8365,7 +8389,10 @@
         <f t="shared" si="51"/>
         <v>44</v>
       </c>
-      <c r="Q82" s="2"/>
+      <c r="Q82" s="66">
+        <f t="shared" si="49"/>
+        <v>6445.3078120832879</v>
+      </c>
       <c r="R82" s="2"/>
       <c r="S82" s="2">
         <v>29149</v>
@@ -8387,7 +8414,7 @@
       <c r="AG82" s="2"/>
       <c r="AH82" s="23"/>
     </row>
-    <row r="83" spans="1:34">
+    <row r="83" spans="1:34" hidden="1">
       <c r="A83" t="s">
         <v>113</v>
       </c>
@@ -8464,7 +8491,7 @@
       <c r="AG83" s="2"/>
       <c r="AH83" s="23"/>
     </row>
-    <row r="84" spans="1:34" hidden="1">
+    <row r="84" spans="1:34">
       <c r="A84" t="s">
         <v>113</v>
       </c>
@@ -8514,7 +8541,10 @@
         <f t="shared" ref="P84" si="52">DAYS360(L84,W84)-(1)</f>
         <v>48</v>
       </c>
-      <c r="Q84" s="2"/>
+      <c r="Q84" s="66">
+        <f t="shared" si="49"/>
+        <v>3474.0090397676713</v>
+      </c>
       <c r="R84" s="2"/>
       <c r="S84" s="2">
         <v>29633</v>
@@ -8536,7 +8566,7 @@
       <c r="AG84" s="2"/>
       <c r="AH84" s="23"/>
     </row>
-    <row r="85" spans="1:34">
+    <row r="85" spans="1:34" hidden="1">
       <c r="A85" t="s">
         <v>113</v>
       </c>
@@ -8685,7 +8715,7 @@
       <c r="AG86" s="2"/>
       <c r="AH86" s="23"/>
     </row>
-    <row r="87" spans="1:34" hidden="1">
+    <row r="87" spans="1:34">
       <c r="A87" t="s">
         <v>113</v>
       </c>
@@ -8737,7 +8767,10 @@
         <f t="shared" ref="P87:P94" si="54">DAYS360(L87,W87)-(1)</f>
         <v>41</v>
       </c>
-      <c r="Q87" s="2"/>
+      <c r="Q87" s="66">
+        <f t="shared" ref="Q87" si="55">0.18*P87*M87/365</f>
+        <v>6003.307428489863</v>
+      </c>
       <c r="R87" s="2"/>
       <c r="S87" s="2">
         <v>30218</v>
@@ -9122,7 +9155,7 @@
       <c r="AG92" s="2"/>
       <c r="AH92" s="23"/>
     </row>
-    <row r="93" spans="1:34" hidden="1">
+    <row r="93" spans="1:34">
       <c r="A93" t="s">
         <v>113</v>
       </c>
@@ -9172,7 +9205,10 @@
         <f t="shared" si="54"/>
         <v>25</v>
       </c>
-      <c r="Q93" s="2"/>
+      <c r="Q93" s="66">
+        <f t="shared" ref="Q93:Q95" si="56">0.18*P93*M93/365</f>
+        <v>825.17503561643844</v>
+      </c>
       <c r="R93" s="2"/>
       <c r="S93" s="2" t="s">
         <v>193</v>
@@ -9194,7 +9230,7 @@
       <c r="AG93" s="2"/>
       <c r="AH93" s="23"/>
     </row>
-    <row r="94" spans="1:34" hidden="1">
+    <row r="94" spans="1:34">
       <c r="A94" t="s">
         <v>113</v>
       </c>
@@ -9244,7 +9280,10 @@
         <f t="shared" si="54"/>
         <v>25</v>
       </c>
-      <c r="Q94" s="2"/>
+      <c r="Q94" s="66">
+        <f t="shared" si="56"/>
+        <v>825.17503561643844</v>
+      </c>
       <c r="R94" s="2"/>
       <c r="S94" s="2" t="s">
         <v>194</v>
@@ -9266,7 +9305,7 @@
       <c r="AG94" s="2"/>
       <c r="AH94" s="23"/>
     </row>
-    <row r="95" spans="1:34" hidden="1">
+    <row r="95" spans="1:34">
       <c r="A95" t="s">
         <v>113</v>
       </c>
@@ -9313,10 +9352,13 @@
       </c>
       <c r="O95" s="2"/>
       <c r="P95" s="7">
-        <f t="shared" ref="P95:P102" si="55">DAYS360(L95,W95)-(1)</f>
+        <f t="shared" ref="P95:P102" si="57">DAYS360(L95,W95)-(1)</f>
         <v>25</v>
       </c>
-      <c r="Q95" s="2"/>
+      <c r="Q95" s="66">
+        <f t="shared" si="56"/>
+        <v>825.17503561643844</v>
+      </c>
       <c r="R95" s="2"/>
       <c r="S95" s="2" t="s">
         <v>195</v>
@@ -9387,7 +9429,7 @@
       </c>
       <c r="O96" s="2"/>
       <c r="P96" s="7">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>26</v>
       </c>
       <c r="Q96" s="2"/>
@@ -9461,7 +9503,7 @@
       </c>
       <c r="O97" s="2"/>
       <c r="P97" s="7">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>26</v>
       </c>
       <c r="Q97" s="2"/>
@@ -9535,7 +9577,7 @@
       </c>
       <c r="O98" s="2"/>
       <c r="P98" s="7">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>26</v>
       </c>
       <c r="Q98" s="2"/>
@@ -9607,7 +9649,7 @@
       </c>
       <c r="O99" s="2"/>
       <c r="P99" s="7">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>-45451</v>
       </c>
       <c r="Q99" s="2"/>
@@ -9679,7 +9721,7 @@
       </c>
       <c r="O100" s="2"/>
       <c r="P100" s="7">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>41</v>
       </c>
       <c r="Q100" s="2"/>
@@ -9753,7 +9795,7 @@
       </c>
       <c r="O101" s="2"/>
       <c r="P101" s="7">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>28</v>
       </c>
       <c r="Q101" s="2"/>
@@ -9825,7 +9867,7 @@
       </c>
       <c r="O102" s="2"/>
       <c r="P102" s="7">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>-45466</v>
       </c>
       <c r="Q102" s="2"/>
@@ -10369,15 +10411,15 @@
         <v>140816.91399999999</v>
       </c>
       <c r="K115" s="4">
-        <f t="shared" ref="K115:K130" si="56">I115*1.12</f>
+        <f t="shared" ref="K115:K130" si="58">I115*1.12</f>
         <v>204.06399999999999</v>
       </c>
       <c r="L115" s="1">
-        <f t="shared" ref="L115:L126" si="57">D115+15</f>
+        <f t="shared" ref="L115:L126" si="59">D115+15</f>
         <v>45844</v>
       </c>
       <c r="M115" s="21">
-        <f t="shared" ref="M115:M130" si="58">H115*K115</f>
+        <f t="shared" ref="M115:M130" si="60">H115*K115</f>
         <v>157714.94368</v>
       </c>
       <c r="N115" s="22" t="s">
@@ -10389,7 +10431,7 @@
         <v>43</v>
       </c>
       <c r="Q115" s="66">
-        <f t="shared" ref="Q115" si="59">0.18*P115*M115/365</f>
+        <f t="shared" ref="Q115" si="61">0.18*P115*M115/365</f>
         <v>3344.4209974882187</v>
       </c>
       <c r="R115" s="2"/>
@@ -10419,7 +10461,7 @@
       <c r="AG115" s="2"/>
       <c r="AH115" s="23"/>
     </row>
-    <row r="116" spans="1:34" hidden="1">
+    <row r="116" spans="1:34">
       <c r="A116" t="s">
         <v>114</v>
       </c>
@@ -10452,7 +10494,7 @@
         <v>8525.8000000000011</v>
       </c>
       <c r="K116" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>263.20000000000005</v>
       </c>
       <c r="L116" s="1">
@@ -10460,7 +10502,7 @@
         <v>45848</v>
       </c>
       <c r="M116" s="21">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>9548.8960000000025</v>
       </c>
       <c r="N116" s="22" t="s">
@@ -10468,11 +10510,11 @@
       </c>
       <c r="O116" s="2"/>
       <c r="P116" s="7">
-        <f t="shared" ref="P116:P119" si="60">DAYS360(L116,W116)-(1)</f>
+        <f t="shared" ref="P116:P119" si="62">DAYS360(L116,W116)-(1)</f>
         <v>37</v>
       </c>
       <c r="Q116" s="66">
-        <f t="shared" ref="Q116:Q119" si="61">0.18*P116*M116/365</f>
+        <f t="shared" ref="Q116:Q119" si="63">0.18*P116*M116/365</f>
         <v>174.2346503013699</v>
       </c>
       <c r="S116" s="2">
@@ -10499,7 +10541,7 @@
       <c r="AG116" s="2"/>
       <c r="AH116" s="23"/>
     </row>
-    <row r="117" spans="1:34" hidden="1">
+    <row r="117" spans="1:34">
       <c r="A117" t="s">
         <v>114</v>
       </c>
@@ -10528,19 +10570,19 @@
         <v>272.32139999999998</v>
       </c>
       <c r="J117" s="4">
-        <f t="shared" ref="J117:J229" si="62">H117*I117</f>
+        <f t="shared" ref="J117:J229" si="64">H117*I117</f>
         <v>283905.95235599997</v>
       </c>
       <c r="K117" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>304.99996800000002</v>
       </c>
       <c r="L117" s="1">
-        <f t="shared" ref="L117:L119" si="63">D117+15</f>
+        <f t="shared" ref="L117:L119" si="65">D117+15</f>
         <v>45849</v>
       </c>
       <c r="M117" s="21">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>317974.66663872002</v>
       </c>
       <c r="N117" s="22" t="s">
@@ -10548,11 +10590,11 @@
       </c>
       <c r="O117" s="2"/>
       <c r="P117" s="7">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>36</v>
       </c>
       <c r="Q117" s="66">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>5645.1392871750841</v>
       </c>
       <c r="S117" s="2">
@@ -10579,7 +10621,7 @@
       <c r="AG117" s="2"/>
       <c r="AH117" s="23"/>
     </row>
-    <row r="118" spans="1:34" hidden="1">
+    <row r="118" spans="1:34">
       <c r="A118" t="s">
         <v>114</v>
       </c>
@@ -10608,19 +10650,19 @@
         <v>272.32139999999998</v>
       </c>
       <c r="J118" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>274870.32830399997</v>
       </c>
       <c r="K118" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>304.99996800000002</v>
       </c>
       <c r="L118" s="1">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>45849</v>
       </c>
       <c r="M118" s="21">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>307854.76770048001</v>
       </c>
       <c r="N118" s="22" t="s">
@@ -10628,11 +10670,11 @@
       </c>
       <c r="O118" s="2"/>
       <c r="P118" s="7">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>36</v>
       </c>
       <c r="Q118" s="66">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>5465.4764238331782</v>
       </c>
       <c r="S118" s="2">
@@ -10659,7 +10701,7 @@
       <c r="AG118" s="2"/>
       <c r="AH118" s="23"/>
     </row>
-    <row r="119" spans="1:34" hidden="1">
+    <row r="119" spans="1:34">
       <c r="A119" t="s">
         <v>114</v>
       </c>
@@ -10688,19 +10730,19 @@
         <v>214.28569999999999</v>
       </c>
       <c r="J119" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>115097.135184</v>
       </c>
       <c r="K119" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>239.99998400000001</v>
       </c>
       <c r="L119" s="1">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>45849</v>
       </c>
       <c r="M119" s="21">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>128908.79140608001</v>
       </c>
       <c r="N119" s="22" t="s">
@@ -10708,11 +10750,11 @@
       </c>
       <c r="O119" s="2"/>
       <c r="P119" s="7">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>36</v>
       </c>
       <c r="Q119" s="66">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>2288.5725159216395</v>
       </c>
       <c r="S119" s="2">
@@ -10766,19 +10808,19 @@
         <v>375.21699999999998</v>
       </c>
       <c r="J120" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>132376.5576</v>
       </c>
       <c r="K120" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>420.24304000000001</v>
       </c>
       <c r="L120" s="1">
-        <f t="shared" ref="L120:L121" si="64">D120+17</f>
+        <f t="shared" ref="L120:L121" si="66">D120+17</f>
         <v>45851</v>
       </c>
       <c r="M120" s="21">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>148261.744512</v>
       </c>
       <c r="N120" s="22" t="s">
@@ -10786,11 +10828,11 @@
       </c>
       <c r="O120" s="2"/>
       <c r="P120" s="7">
-        <f t="shared" ref="P120:P121" si="65">DAYS360(L120,W120)-(1)</f>
+        <f t="shared" ref="P120:P121" si="67">DAYS360(L120,W120)-(1)</f>
         <v>34</v>
       </c>
       <c r="Q120" s="66">
-        <f t="shared" ref="Q120:Q123" si="66">0.18*P120*M120/365</f>
+        <f t="shared" ref="Q120:Q123" si="68">0.18*P120*M120/365</f>
         <v>2485.922949077918</v>
       </c>
       <c r="R120" s="2">
@@ -10847,19 +10889,19 @@
         <v>375.154</v>
       </c>
       <c r="J121" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>67227.596799999999</v>
       </c>
       <c r="K121" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>420.17248000000006</v>
       </c>
       <c r="L121" s="1">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>45851</v>
       </c>
       <c r="M121" s="21">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>75294.908416000006</v>
       </c>
       <c r="N121" s="22" t="s">
@@ -10867,11 +10909,11 @@
       </c>
       <c r="O121" s="2"/>
       <c r="P121" s="7">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>34</v>
       </c>
       <c r="Q121" s="66">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>1262.4790123449866</v>
       </c>
       <c r="R121" s="2">
@@ -10901,7 +10943,7 @@
       <c r="AG121" s="2"/>
       <c r="AH121" s="23"/>
     </row>
-    <row r="122" spans="1:34" hidden="1">
+    <row r="122" spans="1:34">
       <c r="A122" t="s">
         <v>114</v>
       </c>
@@ -10930,11 +10972,11 @@
         <v>416.9</v>
       </c>
       <c r="J122" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>208450</v>
       </c>
       <c r="K122" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>466.928</v>
       </c>
       <c r="L122" s="1">
@@ -10942,7 +10984,7 @@
         <v>45850</v>
       </c>
       <c r="M122" s="21">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>233464</v>
       </c>
       <c r="N122" s="22" t="s">
@@ -10954,7 +10996,7 @@
         <v>35</v>
       </c>
       <c r="Q122" s="66">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>4029.6526027397258</v>
       </c>
       <c r="S122" s="2">
@@ -11010,19 +11052,19 @@
         <v>182.2</v>
       </c>
       <c r="J123" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>138473.82199999999</v>
       </c>
       <c r="K123" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>204.06399999999999</v>
       </c>
       <c r="L123" s="1">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>45850</v>
       </c>
       <c r="M123" s="21">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>155090.68064000001</v>
       </c>
       <c r="N123" s="22" t="s">
@@ -11034,7 +11076,7 @@
         <v>37</v>
       </c>
       <c r="Q123" s="66">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>2829.8737892120548</v>
       </c>
       <c r="R123" s="2"/>
@@ -11064,7 +11106,7 @@
       <c r="AG123" s="2"/>
       <c r="AH123" s="23"/>
     </row>
-    <row r="124" spans="1:34" hidden="1">
+    <row r="124" spans="1:34">
       <c r="A124" t="s">
         <v>114</v>
       </c>
@@ -11093,11 +11135,11 @@
         <v>133.9</v>
       </c>
       <c r="J124" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>58925.373</v>
       </c>
       <c r="K124" s="51">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>149.96800000000002</v>
       </c>
       <c r="L124" s="1">
@@ -11105,7 +11147,7 @@
         <v>45850</v>
       </c>
       <c r="M124" s="75">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>65996.417760000011</v>
       </c>
       <c r="N124" s="76" t="s">
@@ -11117,7 +11159,7 @@
         <v>95</v>
       </c>
       <c r="Q124" s="66">
-        <f t="shared" ref="Q124" si="67">0.18*P124*M124/365</f>
+        <f t="shared" ref="Q124" si="69">0.18*P124*M124/365</f>
         <v>3091.8869690301367</v>
       </c>
       <c r="R124" s="49"/>
@@ -11144,11 +11186,11 @@
         <v>133.9</v>
       </c>
       <c r="AE124" s="51">
-        <f t="shared" ref="AE124" si="68">AD124*1.12</f>
+        <f t="shared" ref="AE124" si="70">AD124*1.12</f>
         <v>149.96800000000002</v>
       </c>
       <c r="AF124" s="52">
-        <f t="shared" ref="AF124" si="69">AC124*AE124</f>
+        <f t="shared" ref="AF124" si="71">AC124*AE124</f>
         <v>65996.417760000011</v>
       </c>
       <c r="AG124" s="49"/>
@@ -11181,11 +11223,11 @@
         <v>375.09500000000003</v>
       </c>
       <c r="J125" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>136534.58000000002</v>
       </c>
       <c r="K125" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>420.10640000000006</v>
       </c>
       <c r="L125" s="1">
@@ -11193,7 +11235,7 @@
         <v>45854</v>
       </c>
       <c r="M125" s="21">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>152918.72960000002</v>
       </c>
       <c r="N125" s="22" t="s">
@@ -11205,7 +11247,7 @@
         <v>31</v>
       </c>
       <c r="Q125" s="66">
-        <f t="shared" ref="Q125:Q126" si="70">0.18*P125*M125/365</f>
+        <f t="shared" ref="Q125:Q126" si="72">0.18*P125*M125/365</f>
         <v>2337.7712634739732</v>
       </c>
       <c r="R125" s="2">
@@ -11264,19 +11306,19 @@
         <v>182.2</v>
       </c>
       <c r="J126" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>140969.962</v>
       </c>
       <c r="K126" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>204.06399999999999</v>
       </c>
       <c r="L126" s="1">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>45853</v>
       </c>
       <c r="M126" s="21">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>157886.35743999999</v>
       </c>
       <c r="N126" s="22" t="s">
@@ -11288,7 +11330,7 @@
         <v>34</v>
       </c>
       <c r="Q126" s="66">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>2647.3000206378083</v>
       </c>
       <c r="R126" s="2"/>
@@ -11345,19 +11387,19 @@
         <v>379.72300000000001</v>
       </c>
       <c r="J127" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>62730.239600000001</v>
       </c>
       <c r="K127" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>425.28976000000006</v>
       </c>
       <c r="L127" s="1">
-        <f t="shared" ref="L127:L131" si="71">D127+17</f>
+        <f t="shared" ref="L127:L131" si="73">D127+17</f>
         <v>45859</v>
       </c>
       <c r="M127" s="21">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>70257.868352000005</v>
       </c>
       <c r="N127" s="22" t="s">
@@ -11365,11 +11407,11 @@
       </c>
       <c r="O127" s="2"/>
       <c r="P127" s="7">
-        <f t="shared" ref="P127:P131" si="72">DAYS360(L127,W127)-(1)</f>
+        <f t="shared" ref="P127:P131" si="74">DAYS360(L127,W127)-(1)</f>
         <v>26</v>
       </c>
       <c r="Q127" s="66">
-        <f t="shared" ref="Q127:Q139" si="73">0.18*P127*M127/365</f>
+        <f t="shared" ref="Q127:Q139" si="75">0.18*P127*M127/365</f>
         <v>900.84061339002733</v>
       </c>
       <c r="R127" s="2">
@@ -11424,19 +11466,19 @@
         <v>379.72300000000001</v>
       </c>
       <c r="J128" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>62730.239600000001</v>
       </c>
       <c r="K128" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>425.28976000000006</v>
       </c>
       <c r="L128" s="1">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>45859</v>
       </c>
       <c r="M128" s="21">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>70257.868352000005</v>
       </c>
       <c r="N128" s="22" t="s">
@@ -11444,11 +11486,11 @@
       </c>
       <c r="O128" s="2"/>
       <c r="P128" s="7">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>26</v>
       </c>
       <c r="Q128" s="66">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>900.84061339002733</v>
       </c>
       <c r="R128" s="2">
@@ -11503,19 +11545,19 @@
         <v>379.72300000000001</v>
       </c>
       <c r="J129" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>62730.239600000001</v>
       </c>
       <c r="K129" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>425.28976000000006</v>
       </c>
       <c r="L129" s="1">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>45859</v>
       </c>
       <c r="M129" s="21">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>70257.868352000005</v>
       </c>
       <c r="N129" s="22" t="s">
@@ -11523,11 +11565,11 @@
       </c>
       <c r="O129" s="2"/>
       <c r="P129" s="7">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>26</v>
       </c>
       <c r="Q129" s="66">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>900.84061339002733</v>
       </c>
       <c r="R129" s="2">
@@ -11582,19 +11624,19 @@
         <v>379.72300000000001</v>
       </c>
       <c r="J130" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>62730.239600000001</v>
       </c>
       <c r="K130" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>425.28976000000006</v>
       </c>
       <c r="L130" s="1">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>45860</v>
       </c>
       <c r="M130" s="21">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>70257.868352000005</v>
       </c>
       <c r="N130" s="22" t="s">
@@ -11602,11 +11644,11 @@
       </c>
       <c r="O130" s="2"/>
       <c r="P130" s="7">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>25</v>
       </c>
       <c r="Q130" s="66">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>866.19289749041104</v>
       </c>
       <c r="R130" s="2">
@@ -11661,19 +11703,19 @@
         <v>379.72300000000001</v>
       </c>
       <c r="J131" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>62730.239600000001</v>
       </c>
       <c r="K131" s="4">
-        <f t="shared" ref="K131:K152" si="74">I131*1.12</f>
+        <f t="shared" ref="K131:K152" si="76">I131*1.12</f>
         <v>425.28976000000006</v>
       </c>
       <c r="L131" s="1">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>45860</v>
       </c>
       <c r="M131" s="21">
-        <f t="shared" ref="M131:M229" si="75">H131*K131</f>
+        <f t="shared" ref="M131:M229" si="77">H131*K131</f>
         <v>70257.868352000005</v>
       </c>
       <c r="N131" s="22" t="s">
@@ -11681,11 +11723,11 @@
       </c>
       <c r="O131" s="2"/>
       <c r="P131" s="7">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>25</v>
       </c>
       <c r="Q131" s="66">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>866.19289749041104</v>
       </c>
       <c r="R131" s="2">
@@ -11742,19 +11784,19 @@
         <v>182.2</v>
       </c>
       <c r="J132" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>141015.51199999999</v>
       </c>
       <c r="K132" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>204.06399999999999</v>
       </c>
       <c r="L132" s="1">
-        <f t="shared" ref="L132:L174" si="76">D132+15</f>
+        <f t="shared" ref="L132:L174" si="78">D132+15</f>
         <v>45861</v>
       </c>
       <c r="M132" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>157937.37344</v>
       </c>
       <c r="N132" s="22" t="s">
@@ -11766,7 +11808,7 @@
         <v>26</v>
       </c>
       <c r="Q132" s="66">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>2025.0600210936987</v>
       </c>
       <c r="R132" s="2"/>
@@ -11821,11 +11863,11 @@
         <v>378.71199999999999</v>
       </c>
       <c r="J133" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>71046.371199999994</v>
       </c>
       <c r="K133" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>424.15744000000001</v>
       </c>
       <c r="L133" s="1">
@@ -11833,7 +11875,7 @@
         <v>45866</v>
       </c>
       <c r="M133" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>79571.935744000002</v>
       </c>
       <c r="N133" s="22" t="s">
@@ -11845,7 +11887,7 @@
         <v>19</v>
       </c>
       <c r="Q133" s="66">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>745.57813765610956</v>
       </c>
       <c r="R133" s="2">
@@ -11873,7 +11915,7 @@
       <c r="AG133" s="2"/>
       <c r="AH133" s="23"/>
     </row>
-    <row r="134" spans="1:34" hidden="1">
+    <row r="134" spans="1:34">
       <c r="A134" t="s">
         <v>114</v>
       </c>
@@ -11900,11 +11942,11 @@
         <v>272.32139999999998</v>
       </c>
       <c r="J134" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>277539.07802399999</v>
       </c>
       <c r="K134" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>304.99996800000002</v>
       </c>
       <c r="L134" s="1">
@@ -11912,7 +11954,7 @@
         <v>45874</v>
       </c>
       <c r="M134" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>310843.76738688</v>
       </c>
       <c r="N134" s="22" t="s">
@@ -11924,7 +11966,7 @@
         <v>72</v>
       </c>
       <c r="Q134" s="66">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>11037.08280913415</v>
       </c>
       <c r="R134" s="2"/>
@@ -11977,11 +12019,11 @@
         <v>186.2</v>
       </c>
       <c r="J135" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>71904.853999999992</v>
       </c>
       <c r="K135" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>208.54400000000001</v>
       </c>
       <c r="L135" s="1">
@@ -11989,7 +12031,7 @@
         <v>45878</v>
       </c>
       <c r="M135" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>80533.436480000004</v>
       </c>
       <c r="N135" s="22" t="s">
@@ -11997,11 +12039,11 @@
       </c>
       <c r="O135" s="2"/>
       <c r="P135" s="7">
-        <f t="shared" ref="P135:P138" si="77">DAYS360(L135,W135)-(1)</f>
+        <f t="shared" ref="P135:P138" si="79">DAYS360(L135,W135)-(1)</f>
         <v>66</v>
       </c>
       <c r="Q135" s="66">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>2621.1978777599998</v>
       </c>
       <c r="R135" s="2"/>
@@ -12058,19 +12100,19 @@
         <v>185.3</v>
       </c>
       <c r="J136" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>143507.43800000002</v>
       </c>
       <c r="K136" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>207.53600000000003</v>
       </c>
       <c r="L136" s="1">
-        <f t="shared" ref="L136:L138" si="78">C136+16</f>
+        <f t="shared" ref="L136:L138" si="80">C136+16</f>
         <v>45878</v>
       </c>
       <c r="M136" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>160728.33056000003</v>
       </c>
       <c r="N136" s="22" t="s">
@@ -12078,11 +12120,11 @@
       </c>
       <c r="O136" s="2"/>
       <c r="P136" s="7">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>66</v>
       </c>
       <c r="Q136" s="66">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>5231.376896035069</v>
       </c>
       <c r="R136" s="2"/>
@@ -12139,19 +12181,19 @@
         <v>185.3</v>
       </c>
       <c r="J137" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>215114.77000000002</v>
       </c>
       <c r="K137" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>207.53600000000003</v>
       </c>
       <c r="L137" s="1">
-        <f t="shared" si="78"/>
+        <f t="shared" si="80"/>
         <v>45884</v>
       </c>
       <c r="M137" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>240928.54240000006</v>
       </c>
       <c r="N137" s="22" t="s">
@@ -12159,11 +12201,11 @@
       </c>
       <c r="O137" s="2"/>
       <c r="P137" s="7">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>60</v>
       </c>
       <c r="Q137" s="66">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>7128.8445422465757</v>
       </c>
       <c r="R137" s="2"/>
@@ -12220,19 +12262,19 @@
         <v>185.3</v>
       </c>
       <c r="J138" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>71592.508000000002</v>
       </c>
       <c r="K138" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>207.53600000000003</v>
       </c>
       <c r="L138" s="1">
-        <f t="shared" si="78"/>
+        <f t="shared" si="80"/>
         <v>45884</v>
       </c>
       <c r="M138" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>80183.608960000012</v>
       </c>
       <c r="N138" s="22" t="s">
@@ -12240,11 +12282,11 @@
       </c>
       <c r="O138" s="2"/>
       <c r="P138" s="7">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>60</v>
       </c>
       <c r="Q138" s="66">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>2372.5561007342467</v>
       </c>
       <c r="R138" s="2"/>
@@ -12272,7 +12314,7 @@
       <c r="AG138" s="2"/>
       <c r="AH138" s="23"/>
     </row>
-    <row r="139" spans="1:34">
+    <row r="139" spans="1:34" hidden="1">
       <c r="A139" t="s">
         <v>114</v>
       </c>
@@ -12301,11 +12343,11 @@
         <v>301.78570000000002</v>
       </c>
       <c r="J139" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>77257.139200000005</v>
       </c>
       <c r="K139" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>337.99998400000004</v>
       </c>
       <c r="L139" s="1">
@@ -12313,7 +12355,7 @@
         <v>45888</v>
       </c>
       <c r="M139" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>86527.99590400001</v>
       </c>
       <c r="N139" s="22" t="s">
@@ -12325,7 +12367,7 @@
         <v>20</v>
       </c>
       <c r="Q139" s="66">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>853.4268089161643</v>
       </c>
       <c r="R139" s="2"/>
@@ -12378,19 +12420,19 @@
         <v>378.38</v>
       </c>
       <c r="J140" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>37156.915999999997</v>
       </c>
       <c r="K140" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>423.78560000000004</v>
       </c>
       <c r="L140" s="1">
-        <f t="shared" ref="L140:L143" si="79">D140+17</f>
+        <f t="shared" ref="L140:L143" si="81">D140+17</f>
         <v>45888</v>
       </c>
       <c r="M140" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>41615.745920000008</v>
       </c>
       <c r="N140" s="22" t="s">
@@ -12398,11 +12440,11 @@
       </c>
       <c r="O140" s="2"/>
       <c r="P140" s="7">
-        <f t="shared" ref="P140:P147" si="80">DAYS360(L140,W140)-(1)</f>
+        <f t="shared" ref="P140:P147" si="82">DAYS360(L140,W140)-(1)</f>
         <v>132</v>
       </c>
       <c r="Q140" s="66">
-        <f t="shared" ref="Q140:Q146" si="81">0.18*P140*M140/365</f>
+        <f t="shared" ref="Q140:Q146" si="83">0.18*P140*M140/365</f>
         <v>2709.0140357786304</v>
       </c>
       <c r="R140" s="2"/>
@@ -12455,19 +12497,19 @@
         <v>378.38</v>
       </c>
       <c r="J141" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>74313.831999999995</v>
       </c>
       <c r="K141" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>423.78560000000004</v>
       </c>
       <c r="L141" s="1">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>45889</v>
       </c>
       <c r="M141" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>83231.491840000017</v>
       </c>
       <c r="N141" s="22" t="s">
@@ -12475,11 +12517,11 @@
       </c>
       <c r="O141" s="2"/>
       <c r="P141" s="7">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>131</v>
       </c>
       <c r="Q141" s="66">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>5376.9824043484941</v>
       </c>
       <c r="R141" s="2"/>
@@ -12532,19 +12574,19 @@
         <v>378.38</v>
       </c>
       <c r="J142" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>37156.915999999997</v>
       </c>
       <c r="K142" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>423.78560000000004</v>
       </c>
       <c r="L142" s="1">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>45889</v>
       </c>
       <c r="M142" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>41615.745920000008</v>
       </c>
       <c r="N142" s="22" t="s">
@@ -12552,11 +12594,11 @@
       </c>
       <c r="O142" s="2"/>
       <c r="P142" s="7">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>131</v>
       </c>
       <c r="Q142" s="66">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>2688.4912021742471</v>
       </c>
       <c r="R142" s="2"/>
@@ -12609,19 +12651,19 @@
         <v>378.38</v>
       </c>
       <c r="J143" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>37156.915999999997</v>
       </c>
       <c r="K143" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>423.78560000000004</v>
       </c>
       <c r="L143" s="1">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>45890</v>
       </c>
       <c r="M143" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>41615.745920000008</v>
       </c>
       <c r="N143" s="22" t="s">
@@ -12629,11 +12671,11 @@
       </c>
       <c r="O143" s="2"/>
       <c r="P143" s="7">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>130</v>
       </c>
       <c r="Q143" s="66">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>2667.9683685698633</v>
       </c>
       <c r="R143" s="2"/>
@@ -12688,19 +12730,19 @@
         <v>185.3</v>
       </c>
       <c r="J144" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>143487.05500000002</v>
       </c>
       <c r="K144" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>207.53600000000003</v>
       </c>
       <c r="L144" s="1">
-        <f t="shared" ref="L144:L146" si="82">C144+16</f>
+        <f t="shared" ref="L144:L146" si="84">C144+16</f>
         <v>45892</v>
       </c>
       <c r="M144" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>160705.50160000002</v>
       </c>
       <c r="N144" s="22" t="s">
@@ -12708,11 +12750,11 @@
       </c>
       <c r="O144" s="2"/>
       <c r="P144" s="7">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>58</v>
       </c>
       <c r="Q144" s="66">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>4596.6176348054796</v>
       </c>
       <c r="R144" s="2"/>
@@ -12769,19 +12811,19 @@
         <v>185.3</v>
       </c>
       <c r="J145" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>143342.52100000001</v>
       </c>
       <c r="K145" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>207.53600000000003</v>
       </c>
       <c r="L145" s="1">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>45895</v>
       </c>
       <c r="M145" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>160543.62352000002</v>
       </c>
       <c r="N145" s="22" t="s">
@@ -12789,11 +12831,11 @@
       </c>
       <c r="O145" s="2"/>
       <c r="P145" s="7">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>55</v>
       </c>
       <c r="Q145" s="66">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>4354.4708845150699</v>
       </c>
       <c r="R145" s="2"/>
@@ -12850,19 +12892,19 @@
         <v>185.3</v>
       </c>
       <c r="J146" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>143364.75700000001</v>
       </c>
       <c r="K146" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>207.53600000000003</v>
       </c>
       <c r="L146" s="1">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>45895</v>
       </c>
       <c r="M146" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>160568.52784000002</v>
       </c>
       <c r="N146" s="22" t="s">
@@ -12870,11 +12912,11 @@
       </c>
       <c r="O146" s="2"/>
       <c r="P146" s="7">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>55</v>
       </c>
       <c r="Q146" s="66">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>4355.1463715506861</v>
       </c>
       <c r="R146" s="2"/>
@@ -12931,11 +12973,11 @@
         <v>296</v>
       </c>
       <c r="J147" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>75776</v>
       </c>
       <c r="K147" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>331.52000000000004</v>
       </c>
       <c r="L147" s="1">
@@ -12943,7 +12985,7 @@
         <v>45909</v>
       </c>
       <c r="M147" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>84869.12000000001</v>
       </c>
       <c r="N147" s="22" t="s">
@@ -12951,7 +12993,7 @@
       </c>
       <c r="O147" s="2"/>
       <c r="P147" s="7">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>38</v>
       </c>
       <c r="Q147" s="66"/>
@@ -13005,19 +13047,19 @@
         <v>187.2</v>
       </c>
       <c r="J148" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>217406.59199999998</v>
       </c>
       <c r="K148" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>209.66400000000002</v>
       </c>
       <c r="L148" s="1">
-        <f t="shared" ref="L148:L149" si="83">C148+16</f>
+        <f t="shared" ref="L148:L149" si="85">C148+16</f>
         <v>45921</v>
       </c>
       <c r="M148" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>243495.38303999999</v>
       </c>
       <c r="N148" s="22" t="s">
@@ -13025,11 +13067,11 @@
       </c>
       <c r="O148" s="2"/>
       <c r="P148" s="7">
-        <f t="shared" ref="P148:P149" si="84">DAYS360(L148,W148)-(1)</f>
+        <f t="shared" ref="P148:P149" si="86">DAYS360(L148,W148)-(1)</f>
         <v>30</v>
       </c>
       <c r="Q148" s="66">
-        <f t="shared" ref="Q148:Q150" si="85">0.18*P148*M148/365</f>
+        <f t="shared" ref="Q148:Q150" si="87">0.18*P148*M148/365</f>
         <v>3602.3974477150682</v>
       </c>
       <c r="R148" s="2"/>
@@ -13086,19 +13128,19 @@
         <v>187.2</v>
       </c>
       <c r="J149" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>72551.231999999989</v>
       </c>
       <c r="K149" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>209.66400000000002</v>
       </c>
       <c r="L149" s="1">
-        <f t="shared" si="83"/>
+        <f t="shared" si="85"/>
         <v>45927</v>
       </c>
       <c r="M149" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>81257.379840000009</v>
       </c>
       <c r="N149" s="22" t="s">
@@ -13106,11 +13148,11 @@
       </c>
       <c r="O149" s="2"/>
       <c r="P149" s="7">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>24</v>
       </c>
       <c r="Q149" s="66">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>961.731180572055</v>
       </c>
       <c r="R149" s="2"/>
@@ -13138,7 +13180,7 @@
       <c r="AG149" s="2"/>
       <c r="AH149" s="23"/>
     </row>
-    <row r="150" spans="1:34">
+    <row r="150" spans="1:34" hidden="1">
       <c r="A150" t="s">
         <v>114</v>
       </c>
@@ -13167,11 +13209,11 @@
         <v>294.64</v>
       </c>
       <c r="J150" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>75427.839999999997</v>
       </c>
       <c r="K150" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>329.99680000000001</v>
       </c>
       <c r="L150" s="1">
@@ -13179,7 +13221,7 @@
         <v>45931</v>
       </c>
       <c r="M150" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>84479.180800000002</v>
       </c>
       <c r="N150" s="22" t="s">
@@ -13191,7 +13233,7 @@
         <v>14</v>
       </c>
       <c r="Q150" s="66">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>583.25352223561651</v>
       </c>
       <c r="R150" s="2"/>
@@ -13246,11 +13288,11 @@
         <v>186.3</v>
       </c>
       <c r="J151" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>72163.305000000008</v>
       </c>
       <c r="K151" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>208.65600000000003</v>
       </c>
       <c r="L151" s="1">
@@ -13258,7 +13300,7 @@
         <v>45931</v>
       </c>
       <c r="M151" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>80822.901600000012</v>
       </c>
       <c r="N151" s="22" t="s">
@@ -13270,7 +13312,7 @@
         <v>20</v>
       </c>
       <c r="Q151" s="66">
-        <f t="shared" ref="Q151" si="86">0.18*P151*M151/365</f>
+        <f t="shared" ref="Q151" si="88">0.18*P151*M151/365</f>
         <v>797.15738564383571</v>
       </c>
       <c r="R151" s="2"/>
@@ -13298,7 +13340,7 @@
       <c r="AG151" s="2"/>
       <c r="AH151" s="23"/>
     </row>
-    <row r="152" spans="1:34" ht="15.75" hidden="1" thickBot="1">
+    <row r="152" spans="1:34" ht="15.75" thickBot="1">
       <c r="A152" t="s">
         <v>114</v>
       </c>
@@ -13325,11 +13367,11 @@
         <v>299.709</v>
       </c>
       <c r="J152" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>152731.7064</v>
       </c>
       <c r="K152" s="32">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>335.67408000000006</v>
       </c>
       <c r="L152" s="28">
@@ -13337,7 +13379,7 @@
         <v>46068</v>
       </c>
       <c r="M152" s="74">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>171059.51116800003</v>
       </c>
       <c r="N152" s="80" t="s">
@@ -13399,11 +13441,11 @@
         <v>186.25</v>
       </c>
       <c r="J153" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>72114.137499999997</v>
       </c>
       <c r="K153" s="4">
-        <f t="shared" ref="K153:K229" si="87">I153*1.05</f>
+        <f t="shared" ref="K153:K229" si="89">I153*1.05</f>
         <v>195.5625</v>
       </c>
       <c r="L153" s="1">
@@ -13411,7 +13453,7 @@
         <v>45944</v>
       </c>
       <c r="M153" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>75719.844375000001</v>
       </c>
       <c r="N153" s="22" t="s">
@@ -13423,7 +13465,7 @@
         <v>7</v>
       </c>
       <c r="Q153" s="66">
-        <f t="shared" ref="Q153" si="88">0.18*P153*M153/365</f>
+        <f t="shared" ref="Q153" si="90">0.18*P153*M153/365</f>
         <v>261.38905181506851</v>
       </c>
       <c r="R153" s="2"/>
@@ -13478,19 +13520,19 @@
         <v>323.44900000000001</v>
       </c>
       <c r="J154" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>112527.9071</v>
       </c>
       <c r="K154" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>339.62145000000004</v>
       </c>
       <c r="L154" s="1">
-        <f t="shared" ref="L154:L155" si="89">D154+18</f>
+        <f t="shared" ref="L154:L155" si="91">D154+18</f>
         <v>45953</v>
       </c>
       <c r="M154" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>118154.30245500001</v>
       </c>
       <c r="N154" s="22" t="s">
@@ -13498,11 +13540,11 @@
       </c>
       <c r="O154" s="2"/>
       <c r="P154" s="7">
-        <f t="shared" ref="P154:P155" si="90">DAYS360(L154,W154)-(1)</f>
+        <f t="shared" ref="P154:P155" si="92">DAYS360(L154,W154)-(1)</f>
         <v>14</v>
       </c>
       <c r="Q154" s="66">
-        <f t="shared" ref="Q154:Q156" si="91">0.18*P154*M154/365</f>
+        <f t="shared" ref="Q154:Q156" si="93">0.18*P154*M154/365</f>
         <v>815.75025256602748</v>
       </c>
       <c r="R154" s="2"/>
@@ -13553,19 +13595,19 @@
         <v>323.44900000000001</v>
       </c>
       <c r="J155" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>56263.953549999998</v>
       </c>
       <c r="K155" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>339.62145000000004</v>
       </c>
       <c r="L155" s="1">
-        <f t="shared" si="89"/>
+        <f t="shared" si="91"/>
         <v>45953</v>
       </c>
       <c r="M155" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>59077.151227500006</v>
       </c>
       <c r="N155" s="22" t="s">
@@ -13573,11 +13615,11 @@
       </c>
       <c r="O155" s="2"/>
       <c r="P155" s="7">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>14</v>
       </c>
       <c r="Q155" s="66">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>407.87512628301374</v>
       </c>
       <c r="R155" s="2"/>
@@ -13601,7 +13643,7 @@
       <c r="AG155" s="2"/>
       <c r="AH155" s="23"/>
     </row>
-    <row r="156" spans="1:34">
+    <row r="156" spans="1:34" hidden="1">
       <c r="A156" t="s">
         <v>114</v>
       </c>
@@ -13630,11 +13672,11 @@
         <v>295</v>
       </c>
       <c r="J156" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>89680</v>
       </c>
       <c r="K156" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>309.75</v>
       </c>
       <c r="L156" s="1">
@@ -13642,7 +13684,7 @@
         <v>45957</v>
       </c>
       <c r="M156" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>94164</v>
       </c>
       <c r="N156" s="22" t="s">
@@ -13654,7 +13696,7 @@
         <v>-6</v>
       </c>
       <c r="Q156" s="66">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>-278.6222465753425</v>
       </c>
       <c r="R156" s="2"/>
@@ -13707,11 +13749,11 @@
         <v>323.29000000000002</v>
       </c>
       <c r="J157" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>117916.79460000001</v>
       </c>
       <c r="K157" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>339.45450000000005</v>
       </c>
       <c r="L157" s="1">
@@ -13719,7 +13761,7 @@
         <v>45959</v>
       </c>
       <c r="M157" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>123812.63433000002</v>
       </c>
       <c r="N157" s="22" t="s">
@@ -13727,11 +13769,11 @@
       </c>
       <c r="O157" s="2"/>
       <c r="P157" s="7">
-        <f t="shared" ref="P157:P161" si="92">DAYS360(L157,W157)-(1)</f>
+        <f t="shared" ref="P157:P161" si="94">DAYS360(L157,W157)-(1)</f>
         <v>8</v>
       </c>
       <c r="Q157" s="66">
-        <f t="shared" ref="Q157:Q161" si="93">0.18*P157*M157/365</f>
+        <f t="shared" ref="Q157:Q161" si="95">0.18*P157*M157/365</f>
         <v>488.46628338410966</v>
       </c>
       <c r="R157" s="2"/>
@@ -13784,19 +13826,19 @@
         <v>186.25</v>
       </c>
       <c r="J158" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>71998.662500000006</v>
       </c>
       <c r="K158" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>195.5625</v>
       </c>
       <c r="L158" s="1">
-        <f t="shared" ref="L158:L161" si="94">C158+16</f>
+        <f t="shared" ref="L158:L161" si="96">C158+16</f>
         <v>45959</v>
       </c>
       <c r="M158" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>75598.595625000002</v>
       </c>
       <c r="N158" s="22" t="s">
@@ -13804,11 +13846,11 @@
       </c>
       <c r="O158" s="2"/>
       <c r="P158" s="7">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>8</v>
       </c>
       <c r="Q158" s="66">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>298.25199369863014</v>
       </c>
       <c r="R158" s="2"/>
@@ -13865,19 +13907,19 @@
         <v>165.25</v>
       </c>
       <c r="J159" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>127926.63499999999</v>
       </c>
       <c r="K159" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>173.51250000000002</v>
       </c>
       <c r="L159" s="1">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>45960</v>
       </c>
       <c r="M159" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>134322.96675000002</v>
       </c>
       <c r="N159" s="22" t="s">
@@ -13885,11 +13927,11 @@
       </c>
       <c r="O159" s="2"/>
       <c r="P159" s="7">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>7</v>
       </c>
       <c r="Q159" s="66">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>463.69024138356173</v>
       </c>
       <c r="R159" s="2"/>
@@ -13946,19 +13988,19 @@
         <v>165.25</v>
       </c>
       <c r="J160" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>63736.924999999996</v>
       </c>
       <c r="K160" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>173.51250000000002</v>
       </c>
       <c r="L160" s="1">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>45960</v>
       </c>
       <c r="M160" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>66923.771250000005</v>
       </c>
       <c r="N160" s="22" t="s">
@@ -13966,11 +14008,11 @@
       </c>
       <c r="O160" s="2"/>
       <c r="P160" s="7">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>7</v>
       </c>
       <c r="Q160" s="66">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>231.02452541095892</v>
       </c>
       <c r="R160" s="2"/>
@@ -14027,19 +14069,19 @@
         <v>166.2</v>
       </c>
       <c r="J161" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>128143.52399999999</v>
       </c>
       <c r="K161" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>174.51</v>
       </c>
       <c r="L161" s="1">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>45963</v>
       </c>
       <c r="M161" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>134550.70019999999</v>
       </c>
       <c r="N161" s="22" t="s">
@@ -14047,11 +14089,11 @@
       </c>
       <c r="O161" s="2"/>
       <c r="P161" s="7">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>5</v>
       </c>
       <c r="Q161" s="66">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>331.7688498082191</v>
       </c>
       <c r="R161" s="2"/>
@@ -14106,19 +14148,19 @@
         <v>323.29000000000002</v>
       </c>
       <c r="J162" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>58958.397300000004</v>
       </c>
       <c r="K162" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>339.45450000000005</v>
       </c>
       <c r="L162" s="1">
-        <f t="shared" ref="L162:L163" si="95">D162+18</f>
+        <f t="shared" ref="L162:L163" si="97">D162+18</f>
         <v>45964</v>
       </c>
       <c r="M162" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>61906.317165000008</v>
       </c>
       <c r="N162" s="22" t="s">
@@ -14126,11 +14168,11 @@
       </c>
       <c r="O162" s="2"/>
       <c r="P162" s="7">
-        <f t="shared" ref="P162:P183" si="96">DAYS360(L162,W162)-(1)</f>
+        <f t="shared" ref="P162:P183" si="98">DAYS360(L162,W162)-(1)</f>
         <v>4</v>
       </c>
       <c r="Q162" s="66">
-        <f t="shared" ref="Q162:Q169" si="97">0.18*P162*M162/365</f>
+        <f t="shared" ref="Q162:Q169" si="99">0.18*P162*M162/365</f>
         <v>122.11657084602741</v>
       </c>
       <c r="R162" s="2"/>
@@ -14181,19 +14223,19 @@
         <v>323.29000000000002</v>
       </c>
       <c r="J163" s="32">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>58958.397300000004</v>
       </c>
       <c r="K163" s="32">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>339.45450000000005</v>
       </c>
       <c r="L163" s="35">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>45965</v>
       </c>
       <c r="M163" s="81">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>61906.317165000008</v>
       </c>
       <c r="N163" s="80" t="s">
@@ -14201,11 +14243,11 @@
       </c>
       <c r="O163" s="30"/>
       <c r="P163" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>3</v>
       </c>
       <c r="Q163" s="66">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>91.587428134520565</v>
       </c>
       <c r="R163" s="30"/>
@@ -14256,11 +14298,11 @@
         <v>323.2396</v>
       </c>
       <c r="J164" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>119708.553464</v>
       </c>
       <c r="K164" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>339.40158000000002</v>
       </c>
       <c r="L164" s="1">
@@ -14268,7 +14310,7 @@
         <v>45973</v>
       </c>
       <c r="M164" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>125693.9811372</v>
       </c>
       <c r="N164" s="22" t="s">
@@ -14276,11 +14318,11 @@
       </c>
       <c r="O164" s="2"/>
       <c r="P164" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>-2</v>
       </c>
       <c r="Q164" s="66">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>-123.97214577915615</v>
       </c>
       <c r="R164" s="2"/>
@@ -14331,11 +14373,11 @@
         <v>323.2396</v>
       </c>
       <c r="J165" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>119708.553464</v>
       </c>
       <c r="K165" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>339.40158000000002</v>
       </c>
       <c r="L165" s="1">
@@ -14343,7 +14385,7 @@
         <v>45973</v>
       </c>
       <c r="M165" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>125693.9811372</v>
       </c>
       <c r="N165" s="22" t="s">
@@ -14351,11 +14393,11 @@
       </c>
       <c r="O165" s="2"/>
       <c r="P165" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>-2</v>
       </c>
       <c r="Q165" s="66">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>-123.97214577915615</v>
       </c>
       <c r="R165" s="2"/>
@@ -14408,19 +14450,19 @@
         <v>166.2</v>
       </c>
       <c r="J166" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>127890.9</v>
       </c>
       <c r="K166" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>174.51</v>
       </c>
       <c r="L166" s="1">
-        <f t="shared" ref="L166:L169" si="98">C166+16</f>
+        <f t="shared" ref="L166:L169" si="100">C166+16</f>
         <v>45976</v>
       </c>
       <c r="M166" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>134285.44500000001</v>
       </c>
       <c r="N166" s="22" t="s">
@@ -14428,11 +14470,11 @@
       </c>
       <c r="O166" s="2"/>
       <c r="P166" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>3</v>
       </c>
       <c r="Q166" s="66">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>198.6688775342466</v>
       </c>
       <c r="R166" s="2"/>
@@ -14489,19 +14531,19 @@
         <v>166.2</v>
       </c>
       <c r="J167" s="91">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>63993.648000000001</v>
       </c>
       <c r="K167" s="91">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>174.51</v>
       </c>
       <c r="L167" s="87">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>45976</v>
       </c>
       <c r="M167" s="92">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>67193.330400000006</v>
       </c>
       <c r="N167" s="93" t="s">
@@ -14509,11 +14551,11 @@
       </c>
       <c r="O167" s="89"/>
       <c r="P167" s="94">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>3</v>
       </c>
       <c r="Q167" s="96">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>99.409310728767139</v>
       </c>
       <c r="R167" s="89"/>
@@ -14570,19 +14612,19 @@
         <v>317</v>
       </c>
       <c r="J168" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>10144</v>
       </c>
       <c r="K168" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>332.85</v>
       </c>
       <c r="L168" s="87">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>45978</v>
       </c>
       <c r="M168" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>10651.2</v>
       </c>
       <c r="N168" s="98" t="s">
@@ -14590,11 +14632,11 @@
       </c>
       <c r="O168" s="2"/>
       <c r="P168" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>86</v>
       </c>
       <c r="Q168" s="66">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>451.72760547945205</v>
       </c>
       <c r="R168" s="2"/>
@@ -14645,19 +14687,19 @@
         <v>165.25</v>
       </c>
       <c r="J169" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>63796.415000000001</v>
       </c>
       <c r="K169" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>173.51250000000002</v>
       </c>
       <c r="L169" s="1">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>45984</v>
       </c>
       <c r="M169" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>66986.235750000007</v>
       </c>
       <c r="N169" s="22" t="s">
@@ -14665,11 +14707,11 @@
       </c>
       <c r="O169" s="2"/>
       <c r="P169" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>-5</v>
       </c>
       <c r="Q169" s="66">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>-165.17154020547946</v>
       </c>
       <c r="R169" s="2"/>
@@ -14724,11 +14766,11 @@
         <v>335</v>
       </c>
       <c r="J170" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>13594.3</v>
       </c>
       <c r="K170" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>351.75</v>
       </c>
       <c r="L170" s="1">
@@ -14736,7 +14778,7 @@
         <v>46019</v>
       </c>
       <c r="M170" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>14274.014999999999</v>
       </c>
       <c r="N170" s="22" t="s">
@@ -14744,7 +14786,7 @@
       </c>
       <c r="O170" s="2"/>
       <c r="P170" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>2</v>
       </c>
       <c r="Q170" s="2"/>
@@ -14796,19 +14838,19 @@
         <v>323.28800000000001</v>
       </c>
       <c r="J171" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>58958.032560000007</v>
       </c>
       <c r="K171" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>339.45240000000001</v>
       </c>
       <c r="L171" s="1">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>45991</v>
       </c>
       <c r="M171" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>61905.934188000007</v>
       </c>
       <c r="N171" s="22" t="s">
@@ -14816,7 +14858,7 @@
       </c>
       <c r="O171" s="2"/>
       <c r="P171" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0</v>
       </c>
       <c r="Q171" s="2"/>
@@ -14868,19 +14910,19 @@
         <v>313.14400000000001</v>
       </c>
       <c r="J172" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>59744.743759999998</v>
       </c>
       <c r="K172" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>328.80119999999999</v>
       </c>
       <c r="L172" s="1">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>45991</v>
       </c>
       <c r="M172" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>62731.980947999997</v>
       </c>
       <c r="N172" s="22" t="s">
@@ -14888,7 +14930,7 @@
       </c>
       <c r="O172" s="2"/>
       <c r="P172" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0</v>
       </c>
       <c r="Q172" s="2"/>
@@ -14940,19 +14982,19 @@
         <v>313.14400000000001</v>
       </c>
       <c r="J173" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>119489.48752</v>
       </c>
       <c r="K173" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>328.80119999999999</v>
       </c>
       <c r="L173" s="1">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>45991</v>
       </c>
       <c r="M173" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>125463.96189599999</v>
       </c>
       <c r="N173" s="22" t="s">
@@ -14960,7 +15002,7 @@
       </c>
       <c r="O173" s="2"/>
       <c r="P173" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0</v>
       </c>
       <c r="Q173" s="2"/>
@@ -14985,7 +15027,7 @@
       <c r="AG173" s="2"/>
       <c r="AH173" s="23"/>
     </row>
-    <row r="174" spans="1:34">
+    <row r="174" spans="1:34" hidden="1">
       <c r="A174" t="s">
         <v>114</v>
       </c>
@@ -15012,19 +15054,19 @@
         <v>147.19999999999999</v>
       </c>
       <c r="J174" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>113863.61599999998</v>
       </c>
       <c r="K174" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>154.56</v>
       </c>
       <c r="L174" s="1">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>45991</v>
       </c>
       <c r="M174" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>119556.7968</v>
       </c>
       <c r="N174" s="22" t="s">
@@ -15032,7 +15074,7 @@
       </c>
       <c r="O174" s="2"/>
       <c r="P174" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>7</v>
       </c>
       <c r="Q174" s="66"/>
@@ -15059,7 +15101,7 @@
       <c r="AG174" s="2"/>
       <c r="AH174" s="23"/>
     </row>
-    <row r="175" spans="1:34">
+    <row r="175" spans="1:34" hidden="1">
       <c r="A175" t="s">
         <v>114</v>
       </c>
@@ -15086,11 +15128,11 @@
         <v>147.19999999999999</v>
       </c>
       <c r="J175" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>56939.903999999995</v>
       </c>
       <c r="K175" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>154.56</v>
       </c>
       <c r="L175" s="1">
@@ -15098,7 +15140,7 @@
         <v>45996</v>
       </c>
       <c r="M175" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>59786.8992</v>
       </c>
       <c r="N175" s="22" t="s">
@@ -15106,7 +15148,7 @@
       </c>
       <c r="O175" s="2"/>
       <c r="P175" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>2</v>
       </c>
       <c r="Q175" s="66"/>
@@ -15162,19 +15204,19 @@
         <v>164.25</v>
       </c>
       <c r="J176" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>63515.474999999999</v>
       </c>
       <c r="K176" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>172.46250000000001</v>
       </c>
       <c r="L176" s="1">
-        <f t="shared" ref="L176:L178" si="99">D176+18</f>
+        <f t="shared" ref="L176:L178" si="101">D176+18</f>
         <v>45995</v>
       </c>
       <c r="M176" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>66691.248749999999</v>
       </c>
       <c r="N176" s="22" t="s">
@@ -15182,11 +15224,11 @@
       </c>
       <c r="O176" s="2"/>
       <c r="P176" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>26</v>
       </c>
       <c r="Q176" s="66">
-        <f t="shared" ref="Q176:Q178" si="100">0.18*P176*M176/365</f>
+        <f t="shared" ref="Q176:Q178" si="102">0.18*P176*M176/365</f>
         <v>855.10970999999995</v>
       </c>
       <c r="R176" s="2"/>
@@ -15243,19 +15285,19 @@
         <v>165.2</v>
       </c>
       <c r="J177" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>63836.583999999995</v>
       </c>
       <c r="K177" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>173.46</v>
       </c>
       <c r="L177" s="1">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>45996</v>
       </c>
       <c r="M177" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>67028.41320000001</v>
       </c>
       <c r="N177" s="22" t="s">
@@ -15263,11 +15305,11 @@
       </c>
       <c r="O177" s="2"/>
       <c r="P177" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>25</v>
       </c>
       <c r="Q177" s="66">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>826.37769698630154</v>
       </c>
       <c r="R177" s="2"/>
@@ -15324,19 +15366,19 @@
         <v>165.2</v>
       </c>
       <c r="J178" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>63810.151999999995</v>
       </c>
       <c r="K178" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>173.46</v>
       </c>
       <c r="L178" s="1">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>45999</v>
       </c>
       <c r="M178" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>67000.659599999999</v>
       </c>
       <c r="N178" s="22" t="s">
@@ -15344,11 +15386,11 @@
       </c>
       <c r="O178" s="2"/>
       <c r="P178" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>22</v>
       </c>
       <c r="Q178" s="66">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>726.91126579726017</v>
       </c>
       <c r="R178" s="2"/>
@@ -15376,7 +15418,7 @@
       <c r="AG178" s="2"/>
       <c r="AH178" s="23"/>
     </row>
-    <row r="179" spans="1:34">
+    <row r="179" spans="1:34" hidden="1">
       <c r="A179" t="s">
         <v>114</v>
       </c>
@@ -15405,11 +15447,11 @@
         <v>294</v>
       </c>
       <c r="J179" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>75264</v>
       </c>
       <c r="K179" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>308.7</v>
       </c>
       <c r="L179" s="1">
@@ -15417,7 +15459,7 @@
         <v>46000</v>
       </c>
       <c r="M179" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>79027.199999999997</v>
       </c>
       <c r="N179" s="22" t="s">
@@ -15479,19 +15521,19 @@
         <v>165.2</v>
       </c>
       <c r="J180" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>64061.255999999994</v>
       </c>
       <c r="K180" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>173.46</v>
       </c>
       <c r="L180" s="1">
-        <f t="shared" ref="L180" si="101">D180+18</f>
+        <f t="shared" ref="L180" si="103">D180+18</f>
         <v>46001</v>
       </c>
       <c r="M180" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>67264.318799999994</v>
       </c>
       <c r="N180" s="22" t="s">
@@ -15499,11 +15541,11 @@
       </c>
       <c r="O180" s="2"/>
       <c r="P180" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>20</v>
       </c>
       <c r="Q180" s="66">
-        <f t="shared" ref="Q180" si="102">0.18*P180*M180/365</f>
+        <f t="shared" ref="Q180" si="104">0.18*P180*M180/365</f>
         <v>663.42889775342451</v>
       </c>
       <c r="R180" s="2"/>
@@ -15531,7 +15573,7 @@
       <c r="AG180" s="2"/>
       <c r="AH180" s="23"/>
     </row>
-    <row r="181" spans="1:34">
+    <row r="181" spans="1:34" hidden="1">
       <c r="A181" t="s">
         <v>114</v>
       </c>
@@ -15560,11 +15602,11 @@
         <v>185.71430000000001</v>
       </c>
       <c r="J181" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>143274.86816400001</v>
       </c>
       <c r="K181" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>195.00001500000002</v>
       </c>
       <c r="L181" s="1">
@@ -15572,7 +15614,7 @@
         <v>46003</v>
       </c>
       <c r="M181" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>150438.61157220002</v>
       </c>
       <c r="N181" s="22" t="s">
@@ -15580,7 +15622,7 @@
       </c>
       <c r="O181" s="2"/>
       <c r="P181" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>-2</v>
       </c>
       <c r="Q181" s="66"/>
@@ -15607,7 +15649,7 @@
       <c r="AG181" s="2"/>
       <c r="AH181" s="23"/>
     </row>
-    <row r="182" spans="1:34">
+    <row r="182" spans="1:34" hidden="1">
       <c r="A182" t="s">
         <v>114</v>
       </c>
@@ -15634,11 +15676,11 @@
         <v>153.33330000000001</v>
       </c>
       <c r="J182" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>177241.02813600001</v>
       </c>
       <c r="K182" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>160.999965</v>
       </c>
       <c r="L182" s="1">
@@ -15646,7 +15688,7 @@
         <v>46008</v>
       </c>
       <c r="M182" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>186103.07954280003</v>
       </c>
       <c r="N182" s="22" t="s">
@@ -15654,11 +15696,11 @@
       </c>
       <c r="O182" s="2"/>
       <c r="P182" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>11</v>
       </c>
       <c r="Q182" s="66">
-        <f t="shared" ref="Q182:Q183" si="103">0.18*P182*M182/365</f>
+        <f t="shared" ref="Q182:Q183" si="105">0.18*P182*M182/365</f>
         <v>1009.5454725883399</v>
       </c>
       <c r="R182" s="2"/>
@@ -15684,7 +15726,7 @@
       <c r="AG182" s="2"/>
       <c r="AH182" s="23"/>
     </row>
-    <row r="183" spans="1:34">
+    <row r="183" spans="1:34" hidden="1">
       <c r="A183" t="s">
         <v>114</v>
       </c>
@@ -15711,11 +15753,11 @@
         <v>294</v>
       </c>
       <c r="J183" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>74840.639999999999</v>
       </c>
       <c r="K183" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>308.7</v>
       </c>
       <c r="L183" s="1">
@@ -15723,7 +15765,7 @@
         <v>46009</v>
       </c>
       <c r="M183" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>78582.671999999991</v>
       </c>
       <c r="N183" s="22" t="s">
@@ -15731,11 +15773,11 @@
       </c>
       <c r="O183" s="2"/>
       <c r="P183" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>10</v>
       </c>
       <c r="Q183" s="66">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>387.5309852054794</v>
       </c>
       <c r="R183" s="2"/>
@@ -15788,16 +15830,16 @@
         <v>475</v>
       </c>
       <c r="J184" s="91">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>523188.75</v>
       </c>
       <c r="K184" s="91">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>498.75</v>
       </c>
       <c r="L184" s="87"/>
       <c r="M184" s="92">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>549348.1875</v>
       </c>
       <c r="N184" s="93" t="s">
@@ -15827,7 +15869,7 @@
       <c r="AG184" s="2"/>
       <c r="AH184" s="23"/>
     </row>
-    <row r="185" spans="1:34">
+    <row r="185" spans="1:34" hidden="1">
       <c r="A185" t="s">
         <v>114</v>
       </c>
@@ -15856,11 +15898,11 @@
         <v>317</v>
       </c>
       <c r="J185" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>82420</v>
       </c>
       <c r="K185" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>332.85</v>
       </c>
       <c r="L185" s="1">
@@ -15868,7 +15910,7 @@
         <v>46011</v>
       </c>
       <c r="M185" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>86541</v>
       </c>
       <c r="N185" s="22" t="s">
@@ -15880,7 +15922,7 @@
         <v>8</v>
       </c>
       <c r="Q185" s="66">
-        <f t="shared" ref="Q185" si="104">0.18*P185*M185/365</f>
+        <f t="shared" ref="Q185:Q187" si="106">0.18*P185*M185/365</f>
         <v>341.42202739726025</v>
       </c>
       <c r="R185" s="2"/>
@@ -15906,7 +15948,7 @@
       <c r="AG185" s="2"/>
       <c r="AH185" s="23"/>
     </row>
-    <row r="186" spans="1:34" hidden="1">
+    <row r="186" spans="1:34">
       <c r="A186" t="s">
         <v>114</v>
       </c>
@@ -15935,19 +15977,19 @@
         <v>264.76190000000003</v>
       </c>
       <c r="J186" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>198571.42500000002</v>
       </c>
       <c r="K186" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>277.99999500000001</v>
       </c>
       <c r="L186" s="1">
-        <f t="shared" ref="L186:L229" si="105">D186+16</f>
+        <f t="shared" ref="L186:L229" si="107">D186+16</f>
         <v>46009</v>
       </c>
       <c r="M186" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>208499.99625</v>
       </c>
       <c r="N186" s="22" t="s">
@@ -15955,10 +15997,13 @@
       </c>
       <c r="O186" s="2"/>
       <c r="P186" s="7">
-        <f t="shared" ref="P186:P190" si="106">DAYS360(L186,W186)-(1)</f>
+        <f t="shared" ref="P186:P190" si="108">DAYS360(L186,W186)-(1)</f>
         <v>-17</v>
       </c>
-      <c r="Q186" s="2"/>
+      <c r="Q186" s="66">
+        <f t="shared" si="106"/>
+        <v>-1747.97257130137</v>
+      </c>
       <c r="R186" s="2"/>
       <c r="S186" s="2">
         <v>22817</v>
@@ -15980,7 +16025,7 @@
       <c r="AG186" s="2"/>
       <c r="AH186" s="23"/>
     </row>
-    <row r="187" spans="1:34" hidden="1">
+    <row r="187" spans="1:34">
       <c r="A187" t="s">
         <v>114</v>
       </c>
@@ -16009,19 +16054,19 @@
         <v>264.76190000000003</v>
       </c>
       <c r="J187" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>65663.598819000006</v>
       </c>
       <c r="K187" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>277.99999500000001</v>
       </c>
       <c r="L187" s="1">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>46009</v>
       </c>
       <c r="M187" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>68946.778759950001</v>
       </c>
       <c r="N187" s="22" t="s">
@@ -16029,10 +16074,13 @@
       </c>
       <c r="O187" s="2"/>
       <c r="P187" s="7">
+        <f t="shared" si="108"/>
+        <v>-17</v>
+      </c>
+      <c r="Q187" s="66">
         <f t="shared" si="106"/>
-        <v>-17</v>
-      </c>
-      <c r="Q187" s="2"/>
+        <v>-578.01956987793699</v>
+      </c>
       <c r="R187" s="2"/>
       <c r="S187" s="2">
         <v>22818</v>
@@ -16054,7 +16102,7 @@
       <c r="AG187" s="2"/>
       <c r="AH187" s="23"/>
     </row>
-    <row r="188" spans="1:34">
+    <row r="188" spans="1:34" hidden="1">
       <c r="A188" t="s">
         <v>114</v>
       </c>
@@ -16083,11 +16131,11 @@
         <v>185.71430000000001</v>
       </c>
       <c r="J188" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>214108.15932700003</v>
       </c>
       <c r="K188" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>195.00001500000002</v>
       </c>
       <c r="L188" s="1">
@@ -16095,7 +16143,7 @@
         <v>46012</v>
       </c>
       <c r="M188" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>224813.56729335003</v>
       </c>
       <c r="N188" s="22" t="s">
@@ -16103,11 +16151,11 @@
       </c>
       <c r="O188" s="2"/>
       <c r="P188" s="7">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>39</v>
       </c>
       <c r="Q188" s="66">
-        <f t="shared" ref="Q188:Q190" si="107">0.18*P188*M188/365</f>
+        <f t="shared" ref="Q188:Q190" si="109">0.18*P188*M188/365</f>
         <v>4323.8116230118276</v>
       </c>
       <c r="R188" s="2"/>
@@ -16133,7 +16181,7 @@
       <c r="AG188" s="2"/>
       <c r="AH188" s="23"/>
     </row>
-    <row r="189" spans="1:34">
+    <row r="189" spans="1:34" hidden="1">
       <c r="A189" t="s">
         <v>114</v>
       </c>
@@ -16162,11 +16210,11 @@
         <v>291</v>
       </c>
       <c r="J189" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>73425.119999999995</v>
       </c>
       <c r="K189" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>305.55</v>
       </c>
       <c r="L189" s="1">
@@ -16174,7 +16222,7 @@
         <v>46015</v>
       </c>
       <c r="M189" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>77096.376000000004</v>
       </c>
       <c r="N189" s="22" t="s">
@@ -16182,11 +16230,11 @@
       </c>
       <c r="O189" s="2"/>
       <c r="P189" s="7">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>36</v>
       </c>
       <c r="Q189" s="66">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>1368.7247026849316</v>
       </c>
       <c r="R189" s="2"/>
@@ -16241,19 +16289,19 @@
         <v>146.19999999999999</v>
       </c>
       <c r="J190" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>169602.23399999997</v>
       </c>
       <c r="K190" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>153.51</v>
       </c>
       <c r="L190" s="1">
-        <f t="shared" ref="L190" si="108">D190+18</f>
+        <f t="shared" ref="L190" si="110">D190+18</f>
         <v>46015</v>
       </c>
       <c r="M190" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>178082.34569999998</v>
       </c>
       <c r="N190" s="22" t="s">
@@ -16261,11 +16309,11 @@
       </c>
       <c r="O190" s="2"/>
       <c r="P190" s="7">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>54</v>
       </c>
       <c r="Q190" s="66">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>4742.3572608328759</v>
       </c>
       <c r="R190" s="2"/>
@@ -16293,7 +16341,7 @@
       <c r="AG190" s="2"/>
       <c r="AH190" s="23"/>
     </row>
-    <row r="191" spans="1:34">
+    <row r="191" spans="1:34" hidden="1">
       <c r="A191" t="s">
         <v>114</v>
       </c>
@@ -16322,11 +16370,11 @@
         <v>317</v>
       </c>
       <c r="J191" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>82420</v>
       </c>
       <c r="K191" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>332.85</v>
       </c>
       <c r="L191" s="1">
@@ -16334,7 +16382,7 @@
         <v>46020</v>
       </c>
       <c r="M191" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>86541</v>
       </c>
       <c r="N191" s="22" t="s">
@@ -16346,7 +16394,7 @@
         <v>31</v>
       </c>
       <c r="Q191" s="66">
-        <f t="shared" ref="Q191:Q192" si="109">0.18*P191*M191/365</f>
+        <f t="shared" ref="Q191:Q192" si="111">0.18*P191*M191/365</f>
         <v>1323.0103561643837</v>
       </c>
       <c r="R191" s="2"/>
@@ -16401,19 +16449,19 @@
         <v>146.19999999999999</v>
       </c>
       <c r="J192" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>112728.97199999998</v>
       </c>
       <c r="K192" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>153.51</v>
       </c>
       <c r="L192" s="1">
-        <f t="shared" ref="L192" si="110">D192+18</f>
+        <f t="shared" ref="L192" si="112">D192+18</f>
         <v>46021</v>
       </c>
       <c r="M192" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>118365.42059999998</v>
       </c>
       <c r="N192" s="22" t="s">
@@ -16421,11 +16469,11 @@
       </c>
       <c r="O192" s="2"/>
       <c r="P192" s="7">
-        <f t="shared" ref="P192" si="111">DAYS360(L192,W192)-(1)</f>
+        <f t="shared" ref="P192" si="113">DAYS360(L192,W192)-(1)</f>
         <v>48</v>
       </c>
       <c r="Q192" s="66">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>2801.8554355726023</v>
       </c>
       <c r="R192" s="2"/>
@@ -16453,7 +16501,7 @@
       <c r="AG192" s="2"/>
       <c r="AH192" s="23"/>
     </row>
-    <row r="193" spans="1:34">
+    <row r="193" spans="1:34" hidden="1">
       <c r="A193" t="s">
         <v>114</v>
       </c>
@@ -16482,11 +16530,11 @@
         <v>180.95240000000001</v>
       </c>
       <c r="J193" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>210205.16498400003</v>
       </c>
       <c r="K193" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>190.00002000000001</v>
       </c>
       <c r="L193" s="1">
@@ -16494,7 +16542,7 @@
         <v>46022</v>
       </c>
       <c r="M193" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>220715.42323320001</v>
       </c>
       <c r="N193" s="22" t="s">
@@ -16502,11 +16550,11 @@
       </c>
       <c r="O193" s="2"/>
       <c r="P193" s="7">
-        <f t="shared" ref="P193:P195" si="112">DAYS360(L193,W193)-(1)</f>
+        <f t="shared" ref="P193:P195" si="114">DAYS360(L193,W193)-(1)</f>
         <v>40</v>
       </c>
       <c r="Q193" s="66">
-        <f t="shared" ref="Q193:Q195" si="113">0.18*P193*M193/365</f>
+        <f t="shared" ref="Q193:Q195" si="115">0.18*P193*M193/365</f>
         <v>4353.8384856959992</v>
       </c>
       <c r="R193" s="2"/>
@@ -16532,7 +16580,7 @@
       <c r="AG193" s="2"/>
       <c r="AH193" s="23"/>
     </row>
-    <row r="194" spans="1:34">
+    <row r="194" spans="1:34" hidden="1">
       <c r="A194" t="s">
         <v>114</v>
       </c>
@@ -16561,11 +16609,11 @@
         <v>292</v>
       </c>
       <c r="J194" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>73619.040000000008</v>
       </c>
       <c r="K194" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>306.60000000000002</v>
       </c>
       <c r="L194" s="1">
@@ -16573,7 +16621,7 @@
         <v>46026</v>
       </c>
       <c r="M194" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>77299.992000000013</v>
       </c>
       <c r="N194" s="22" t="s">
@@ -16581,11 +16629,11 @@
       </c>
       <c r="O194" s="2"/>
       <c r="P194" s="7">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>37</v>
       </c>
       <c r="Q194" s="66">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>1410.4601280000004</v>
       </c>
       <c r="R194" s="2"/>
@@ -16611,7 +16659,7 @@
       <c r="AG194" s="2"/>
       <c r="AH194" s="23"/>
     </row>
-    <row r="195" spans="1:34">
+    <row r="195" spans="1:34" hidden="1">
       <c r="A195" t="s">
         <v>114</v>
       </c>
@@ -16640,11 +16688,11 @@
         <v>292</v>
       </c>
       <c r="J195" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>147787.04</v>
       </c>
       <c r="K195" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>306.60000000000002</v>
       </c>
       <c r="L195" s="1">
@@ -16652,7 +16700,7 @@
         <v>46039</v>
       </c>
       <c r="M195" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>155176.39200000002</v>
       </c>
       <c r="N195" s="22" t="s">
@@ -16660,11 +16708,11 @@
       </c>
       <c r="O195" s="2"/>
       <c r="P195" s="7">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>24</v>
       </c>
       <c r="Q195" s="66">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>1836.6082560000004</v>
       </c>
       <c r="R195" s="2"/>
@@ -16719,19 +16767,19 @@
         <v>465</v>
       </c>
       <c r="J196" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>54493.35</v>
       </c>
       <c r="K196" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>488.25</v>
       </c>
       <c r="L196" s="1">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>46038</v>
       </c>
       <c r="M196" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>57218.017500000002</v>
       </c>
       <c r="N196" s="22" t="s">
@@ -16739,8 +16787,8 @@
       </c>
       <c r="O196" s="2"/>
       <c r="P196" s="7">
-        <f t="shared" ref="P196:P229" ca="1" si="114">DAYS360(L196,TODAY())-(1)</f>
-        <v>149</v>
+        <f t="shared" ref="P196:P229" ca="1" si="116">DAYS360(L196,TODAY())-(1)</f>
+        <v>150</v>
       </c>
       <c r="Q196" s="2"/>
       <c r="R196" s="2"/>
@@ -16762,7 +16810,7 @@
       <c r="AG196" s="2"/>
       <c r="AH196" s="23"/>
     </row>
-    <row r="197" spans="1:34">
+    <row r="197" spans="1:34" hidden="1">
       <c r="A197" t="s">
         <v>114</v>
       </c>
@@ -16791,11 +16839,11 @@
         <v>180</v>
       </c>
       <c r="J197" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>208738.80000000002</v>
       </c>
       <c r="K197" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>189</v>
       </c>
       <c r="L197" s="1">
@@ -16803,7 +16851,7 @@
         <v>46043</v>
       </c>
       <c r="M197" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>219175.74000000002</v>
       </c>
       <c r="N197" s="22" t="s">
@@ -16811,11 +16859,11 @@
       </c>
       <c r="O197" s="2"/>
       <c r="P197" s="7">
-        <f t="shared" ref="P197:P201" si="115">DAYS360(L197,W197)-(1)</f>
+        <f t="shared" ref="P197:P201" si="117">DAYS360(L197,W197)-(1)</f>
         <v>20</v>
       </c>
       <c r="Q197" s="66">
-        <f t="shared" ref="Q197:Q199" si="116">0.18*P197*M197/365</f>
+        <f t="shared" ref="Q197:Q201" si="118">0.18*P197*M197/365</f>
         <v>2161.7333260273972</v>
       </c>
       <c r="R197" s="2"/>
@@ -16841,7 +16889,7 @@
       <c r="AG197" s="2"/>
       <c r="AH197" s="23"/>
     </row>
-    <row r="198" spans="1:34">
+    <row r="198" spans="1:34" hidden="1">
       <c r="A198" t="s">
         <v>114</v>
       </c>
@@ -16870,11 +16918,11 @@
         <v>180</v>
       </c>
       <c r="J198" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>139158</v>
       </c>
       <c r="K198" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>189</v>
       </c>
       <c r="L198" s="1">
@@ -16882,7 +16930,7 @@
         <v>46043</v>
       </c>
       <c r="M198" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>146115.9</v>
       </c>
       <c r="N198" s="22" t="s">
@@ -16890,11 +16938,11 @@
       </c>
       <c r="O198" s="2"/>
       <c r="P198" s="7">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>22</v>
       </c>
       <c r="Q198" s="66">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>1585.2574356164382</v>
       </c>
       <c r="R198" s="2"/>
@@ -16920,7 +16968,7 @@
       <c r="AG198" s="2"/>
       <c r="AH198" s="23"/>
     </row>
-    <row r="199" spans="1:34">
+    <row r="199" spans="1:34" hidden="1">
       <c r="A199" t="s">
         <v>114</v>
       </c>
@@ -16949,11 +16997,11 @@
         <v>180</v>
       </c>
       <c r="J199" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>139114.79999999999</v>
       </c>
       <c r="K199" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>189</v>
       </c>
       <c r="L199" s="1">
@@ -16961,7 +17009,7 @@
         <v>46043</v>
       </c>
       <c r="M199" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>146070.54</v>
       </c>
       <c r="N199" s="22" t="s">
@@ -16969,11 +17017,11 @@
       </c>
       <c r="O199" s="2"/>
       <c r="P199" s="7">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>22</v>
       </c>
       <c r="Q199" s="66">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>1584.7653106849316</v>
       </c>
       <c r="R199" s="2"/>
@@ -16999,7 +17047,7 @@
       <c r="AG199" s="2"/>
       <c r="AH199" s="23"/>
     </row>
-    <row r="200" spans="1:34" hidden="1">
+    <row r="200" spans="1:34">
       <c r="A200" t="s">
         <v>114</v>
       </c>
@@ -17028,19 +17076,19 @@
         <v>264.76190000000003</v>
       </c>
       <c r="J200" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>267541.89995000005</v>
       </c>
       <c r="K200" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>277.99999500000001</v>
       </c>
       <c r="L200" s="1">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>46043</v>
       </c>
       <c r="M200" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>280918.9949475</v>
       </c>
       <c r="N200" s="22" t="s">
@@ -17048,10 +17096,13 @@
       </c>
       <c r="O200" s="2"/>
       <c r="P200" s="7">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>27</v>
       </c>
-      <c r="Q200" s="2"/>
+      <c r="Q200" s="66">
+        <f t="shared" si="118"/>
+        <v>3740.4556587530133</v>
+      </c>
       <c r="R200" s="2"/>
       <c r="S200" s="2">
         <v>25905</v>
@@ -17073,7 +17124,7 @@
       <c r="AG200" s="2"/>
       <c r="AH200" s="23"/>
     </row>
-    <row r="201" spans="1:34" hidden="1">
+    <row r="201" spans="1:34">
       <c r="A201" t="s">
         <v>114</v>
       </c>
@@ -17100,19 +17151,19 @@
         <v>122</v>
       </c>
       <c r="J201" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>37527.200000000004</v>
       </c>
       <c r="K201" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>128.1</v>
       </c>
       <c r="L201" s="1">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>46045</v>
       </c>
       <c r="M201" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>39403.56</v>
       </c>
       <c r="N201" s="22" t="s">
@@ -17120,10 +17171,13 @@
       </c>
       <c r="O201" s="2"/>
       <c r="P201" s="7">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>42</v>
       </c>
-      <c r="Q201" s="2"/>
+      <c r="Q201" s="66">
+        <f t="shared" si="118"/>
+        <v>816.13948931506843</v>
+      </c>
       <c r="R201" s="2"/>
       <c r="S201" s="2">
         <v>26089</v>
@@ -17145,7 +17199,7 @@
       <c r="AG201" s="2"/>
       <c r="AH201" s="23"/>
     </row>
-    <row r="202" spans="1:34">
+    <row r="202" spans="1:34" hidden="1">
       <c r="A202" t="s">
         <v>114</v>
       </c>
@@ -17172,11 +17226,11 @@
         <v>190</v>
       </c>
       <c r="J202" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>36039.200000000004</v>
       </c>
       <c r="K202" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>199.5</v>
       </c>
       <c r="L202" s="1">
@@ -17184,7 +17238,7 @@
         <v>46053</v>
       </c>
       <c r="M202" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>37841.160000000003</v>
       </c>
       <c r="N202" s="22" t="s">
@@ -17196,7 +17250,7 @@
         <v>27</v>
       </c>
       <c r="Q202" s="66">
-        <f t="shared" ref="Q202:Q204" si="117">0.18*P202*M202/365</f>
+        <f t="shared" ref="Q202:Q207" si="119">0.18*P202*M202/365</f>
         <v>503.85763726027392</v>
       </c>
       <c r="R202" s="2"/>
@@ -17222,7 +17276,7 @@
       <c r="AG202" s="2"/>
       <c r="AH202" s="23"/>
     </row>
-    <row r="203" spans="1:34">
+    <row r="203" spans="1:34" hidden="1">
       <c r="A203" t="s">
         <v>114</v>
       </c>
@@ -17249,11 +17303,11 @@
         <v>294.28570000000002</v>
       </c>
       <c r="J203" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>234133.70292000001</v>
       </c>
       <c r="K203" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>308.99998500000004</v>
       </c>
       <c r="L203" s="1">
@@ -17261,7 +17315,7 @@
         <v>46053</v>
       </c>
       <c r="M203" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>245840.38806600004</v>
       </c>
       <c r="N203" s="22" t="s">
@@ -17269,11 +17323,11 @@
       </c>
       <c r="O203" s="2"/>
       <c r="P203" s="7">
-        <f t="shared" ref="P203:P207" si="118">DAYS360(L203,W203)-(1)</f>
+        <f t="shared" ref="P203:P207" si="120">DAYS360(L203,W203)-(1)</f>
         <v>27</v>
       </c>
       <c r="Q203" s="66">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>3273.3816054815343</v>
       </c>
       <c r="R203" s="2"/>
@@ -17299,7 +17353,7 @@
       <c r="AG203" s="2"/>
       <c r="AH203" s="23"/>
     </row>
-    <row r="204" spans="1:34">
+    <row r="204" spans="1:34" hidden="1">
       <c r="A204" t="s">
         <v>114</v>
       </c>
@@ -17326,11 +17380,11 @@
         <v>294</v>
       </c>
       <c r="J204" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>141120</v>
       </c>
       <c r="K204" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>308.7</v>
       </c>
       <c r="L204" s="1">
@@ -17338,7 +17392,7 @@
         <v>46056</v>
       </c>
       <c r="M204" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>148176</v>
       </c>
       <c r="N204" s="22" t="s">
@@ -17346,11 +17400,11 @@
       </c>
       <c r="O204" s="2"/>
       <c r="P204" s="7">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>24</v>
       </c>
       <c r="Q204" s="66">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>1753.7543013698632</v>
       </c>
       <c r="R204" s="2"/>
@@ -17376,7 +17430,7 @@
       <c r="AG204" s="2"/>
       <c r="AH204" s="23"/>
     </row>
-    <row r="205" spans="1:34" hidden="1">
+    <row r="205" spans="1:34">
       <c r="A205" t="s">
         <v>114</v>
       </c>
@@ -17403,19 +17457,19 @@
         <v>302</v>
       </c>
       <c r="J205" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>90600</v>
       </c>
       <c r="K205" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>317.10000000000002</v>
       </c>
       <c r="L205" s="1">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>46054</v>
       </c>
       <c r="M205" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>95130</v>
       </c>
       <c r="N205" s="22" t="s">
@@ -17423,10 +17477,13 @@
       </c>
       <c r="O205" s="2"/>
       <c r="P205" s="7">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>34</v>
       </c>
-      <c r="Q205" s="2"/>
+      <c r="Q205" s="66">
+        <f t="shared" si="119"/>
+        <v>1595.0564383561643</v>
+      </c>
       <c r="R205" s="2"/>
       <c r="S205" s="2">
         <v>26998</v>
@@ -17448,7 +17505,7 @@
       <c r="AG205" s="2"/>
       <c r="AH205" s="23"/>
     </row>
-    <row r="206" spans="1:34" hidden="1">
+    <row r="206" spans="1:34">
       <c r="A206" t="s">
         <v>114</v>
       </c>
@@ -17475,19 +17532,19 @@
         <v>264.76190000000003</v>
       </c>
       <c r="J206" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>50145.903860000006</v>
       </c>
       <c r="K206" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>277.99999500000001</v>
       </c>
       <c r="L206" s="1">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>46055</v>
       </c>
       <c r="M206" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>52653.199053000004</v>
       </c>
       <c r="N206" s="22" t="s">
@@ -17495,10 +17552,13 @@
       </c>
       <c r="O206" s="2"/>
       <c r="P206" s="7">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>33</v>
       </c>
-      <c r="Q206" s="2"/>
+      <c r="Q206" s="66">
+        <f t="shared" si="119"/>
+        <v>856.87671883512326</v>
+      </c>
       <c r="R206" s="2"/>
       <c r="S206" s="2">
         <v>27136</v>
@@ -17520,7 +17580,7 @@
       <c r="AG206" s="2"/>
       <c r="AH206" s="23"/>
     </row>
-    <row r="207" spans="1:34" hidden="1">
+    <row r="207" spans="1:34">
       <c r="A207" t="s">
         <v>114</v>
       </c>
@@ -17547,19 +17607,19 @@
         <v>264.76190000000003</v>
       </c>
       <c r="J207" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>209214.85338000004</v>
       </c>
       <c r="K207" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>277.99999500000001</v>
       </c>
       <c r="L207" s="1">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>46055</v>
       </c>
       <c r="M207" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>219675.59604900001</v>
       </c>
       <c r="N207" s="22" t="s">
@@ -17567,10 +17627,13 @@
       </c>
       <c r="O207" s="2"/>
       <c r="P207" s="7">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>33</v>
       </c>
-      <c r="Q207" s="2"/>
+      <c r="Q207" s="66">
+        <f t="shared" si="119"/>
+        <v>3574.9946315919451</v>
+      </c>
       <c r="R207" s="2"/>
       <c r="S207" s="2">
         <v>27137</v>
@@ -17592,7 +17655,7 @@
       <c r="AG207" s="2"/>
       <c r="AH207" s="23"/>
     </row>
-    <row r="208" spans="1:34">
+    <row r="208" spans="1:34" hidden="1">
       <c r="A208" t="s">
         <v>114</v>
       </c>
@@ -17619,11 +17682,11 @@
         <v>294</v>
       </c>
       <c r="J208" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>117035.51999999999</v>
       </c>
       <c r="K208" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>308.7</v>
       </c>
       <c r="L208" s="1">
@@ -17631,7 +17694,7 @@
         <v>46061</v>
       </c>
       <c r="M208" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>122887.29599999999</v>
       </c>
       <c r="N208" s="22" t="s">
@@ -17639,11 +17702,11 @@
       </c>
       <c r="O208" s="2"/>
       <c r="P208" s="7">
-        <f t="shared" ref="P208:P219" si="119">DAYS360(L208,W208)-(1)</f>
+        <f t="shared" ref="P208:P219" si="121">DAYS360(L208,W208)-(1)</f>
         <v>19</v>
       </c>
       <c r="Q208" s="66">
-        <f t="shared" ref="Q208:Q209" si="120">0.18*P208*M208/365</f>
+        <f t="shared" ref="Q208:Q211" si="122">0.18*P208*M208/365</f>
         <v>1151.4371296438355</v>
       </c>
       <c r="R208" s="2"/>
@@ -17669,7 +17732,7 @@
       <c r="AG208" s="2"/>
       <c r="AH208" s="23"/>
     </row>
-    <row r="209" spans="1:34">
+    <row r="209" spans="1:34" hidden="1">
       <c r="A209" t="s">
         <v>114</v>
       </c>
@@ -17696,11 +17759,11 @@
         <v>294</v>
       </c>
       <c r="J209" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>93444.959999999992</v>
       </c>
       <c r="K209" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>308.7</v>
       </c>
       <c r="L209" s="1">
@@ -17708,7 +17771,7 @@
         <v>46062</v>
       </c>
       <c r="M209" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>98117.207999999984</v>
       </c>
       <c r="N209" s="22" t="s">
@@ -17716,11 +17779,11 @@
       </c>
       <c r="O209" s="2"/>
       <c r="P209" s="7">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>18</v>
       </c>
       <c r="Q209" s="66">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>870.95822991780801</v>
       </c>
       <c r="R209" s="2"/>
@@ -17746,7 +17809,7 @@
       <c r="AG209" s="2"/>
       <c r="AH209" s="23"/>
     </row>
-    <row r="210" spans="1:34" hidden="1">
+    <row r="210" spans="1:34">
       <c r="A210" t="s">
         <v>114</v>
       </c>
@@ -17773,19 +17836,19 @@
         <v>285.70999999999998</v>
       </c>
       <c r="J210" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>144397.83399999997</v>
       </c>
       <c r="K210" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>299.99549999999999</v>
       </c>
       <c r="L210" s="1">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>46064</v>
       </c>
       <c r="M210" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>151617.72569999998</v>
       </c>
       <c r="N210" s="22" t="s">
@@ -17793,10 +17856,13 @@
       </c>
       <c r="O210" s="2"/>
       <c r="P210" s="7">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>32</v>
       </c>
-      <c r="Q210" s="2"/>
+      <c r="Q210" s="66">
+        <f t="shared" si="122"/>
+        <v>2392.6523288547942</v>
+      </c>
       <c r="R210" s="2"/>
       <c r="S210" s="2">
         <v>28149</v>
@@ -17818,7 +17884,7 @@
       <c r="AG210" s="2"/>
       <c r="AH210" s="23"/>
     </row>
-    <row r="211" spans="1:34" hidden="1">
+    <row r="211" spans="1:34">
       <c r="A211" t="s">
         <v>114</v>
       </c>
@@ -17845,19 +17911,19 @@
         <v>285.70999999999998</v>
       </c>
       <c r="J211" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>144589.2597</v>
       </c>
       <c r="K211" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>299.99549999999999</v>
       </c>
       <c r="L211" s="1">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>46067</v>
       </c>
       <c r="M211" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>151818.72268499999</v>
       </c>
       <c r="N211" s="22" t="s">
@@ -17865,10 +17931,13 @@
       </c>
       <c r="O211" s="2"/>
       <c r="P211" s="7">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>29</v>
       </c>
-      <c r="Q211" s="2"/>
+      <c r="Q211" s="66">
+        <f t="shared" si="122"/>
+        <v>2171.2157052484927</v>
+      </c>
       <c r="R211" s="2"/>
       <c r="S211" s="2">
         <v>28465</v>
@@ -17917,19 +17986,19 @@
         <v>192</v>
       </c>
       <c r="J212" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>9216</v>
       </c>
       <c r="K212" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>201.60000000000002</v>
       </c>
       <c r="L212" s="1">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>46071</v>
       </c>
       <c r="M212" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>9676.8000000000011</v>
       </c>
       <c r="N212" s="22" t="s">
@@ -17937,8 +18006,8 @@
       </c>
       <c r="O212" s="2"/>
       <c r="P212" s="7">
-        <f t="shared" ca="1" si="114"/>
-        <v>117</v>
+        <f t="shared" ca="1" si="116"/>
+        <v>118</v>
       </c>
       <c r="Q212" s="2"/>
       <c r="R212" s="2"/>
@@ -17962,7 +18031,7 @@
       <c r="AG212" s="2"/>
       <c r="AH212" s="23"/>
     </row>
-    <row r="213" spans="1:34" hidden="1">
+    <row r="213" spans="1:34">
       <c r="A213" t="s">
         <v>114</v>
       </c>
@@ -17989,19 +18058,19 @@
         <v>285.70999999999998</v>
       </c>
       <c r="J213" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>141520.73429999998</v>
       </c>
       <c r="K213" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>299.99549999999999</v>
       </c>
       <c r="L213" s="1">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>46071</v>
       </c>
       <c r="M213" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>148596.77101500001</v>
       </c>
       <c r="N213" s="22" t="s">
@@ -18009,10 +18078,13 @@
       </c>
       <c r="O213" s="2"/>
       <c r="P213" s="7">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>25</v>
       </c>
-      <c r="Q213" s="2"/>
+      <c r="Q213" s="66">
+        <f t="shared" ref="Q213:Q219" si="123">0.18*P213*M213/365</f>
+        <v>1832.0149851164385</v>
+      </c>
       <c r="R213" s="2"/>
       <c r="S213" s="2">
         <v>28842</v>
@@ -18034,7 +18106,7 @@
       <c r="AG213" s="2"/>
       <c r="AH213" s="23"/>
     </row>
-    <row r="214" spans="1:34" hidden="1">
+    <row r="214" spans="1:34">
       <c r="A214" t="s">
         <v>114</v>
       </c>
@@ -18061,19 +18133,19 @@
         <v>285.70999999999998</v>
       </c>
       <c r="J214" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>281367.20799999998</v>
       </c>
       <c r="K214" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>299.99549999999999</v>
       </c>
       <c r="L214" s="1">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>46078</v>
       </c>
       <c r="M214" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>295435.56839999999</v>
       </c>
       <c r="N214" s="22" t="s">
@@ -18081,10 +18153,13 @@
       </c>
       <c r="O214" s="2"/>
       <c r="P214" s="7">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>22</v>
       </c>
-      <c r="Q214" s="2"/>
+      <c r="Q214" s="66">
+        <f t="shared" si="123"/>
+        <v>3205.2735640109586</v>
+      </c>
       <c r="R214" s="2"/>
       <c r="S214" s="2">
         <v>29741</v>
@@ -18106,7 +18181,7 @@
       <c r="AG214" s="2"/>
       <c r="AH214" s="23"/>
     </row>
-    <row r="215" spans="1:34" hidden="1">
+    <row r="215" spans="1:34">
       <c r="A215" t="s">
         <v>114</v>
       </c>
@@ -18135,19 +18210,19 @@
         <v>219.04759999999999</v>
       </c>
       <c r="J215" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>217360.93347999998</v>
       </c>
       <c r="K215" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>229.99997999999999</v>
       </c>
       <c r="L215" s="1">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>46083</v>
       </c>
       <c r="M215" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>228228.98015399999</v>
       </c>
       <c r="N215" s="22" t="s">
@@ -18155,10 +18230,13 @@
       </c>
       <c r="O215" s="2"/>
       <c r="P215" s="7">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>26</v>
       </c>
-      <c r="Q215" s="2"/>
+      <c r="Q215" s="66">
+        <f t="shared" si="123"/>
+        <v>2926.3332249882737</v>
+      </c>
       <c r="R215" s="2"/>
       <c r="S215" s="2">
         <v>30305</v>
@@ -18180,7 +18258,7 @@
       <c r="AG215" s="2"/>
       <c r="AH215" s="23"/>
     </row>
-    <row r="216" spans="1:34" hidden="1">
+    <row r="216" spans="1:34">
       <c r="A216" t="s">
         <v>114</v>
       </c>
@@ -18209,19 +18287,19 @@
         <v>181.02099999999999</v>
       </c>
       <c r="J216" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>65312.376799999998</v>
       </c>
       <c r="K216" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>190.07204999999999</v>
       </c>
       <c r="L216" s="1">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>46086</v>
       </c>
       <c r="M216" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>68577.995639999994</v>
       </c>
       <c r="N216" s="22" t="s">
@@ -18229,10 +18307,13 @@
       </c>
       <c r="O216" s="2"/>
       <c r="P216" s="7">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>23</v>
       </c>
-      <c r="Q216" s="2"/>
+      <c r="Q216" s="66">
+        <f t="shared" si="123"/>
+        <v>777.84356698520537</v>
+      </c>
       <c r="R216" s="2"/>
       <c r="S216" s="2" t="s">
         <v>172</v>
@@ -18254,7 +18335,7 @@
       <c r="AG216" s="2"/>
       <c r="AH216" s="23"/>
     </row>
-    <row r="217" spans="1:34" hidden="1">
+    <row r="217" spans="1:34">
       <c r="A217" t="s">
         <v>114</v>
       </c>
@@ -18283,19 +18364,19 @@
         <v>181.09</v>
       </c>
       <c r="J217" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>63743.68</v>
       </c>
       <c r="K217" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>190.14450000000002</v>
       </c>
       <c r="L217" s="1">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>46086</v>
       </c>
       <c r="M217" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>66930.864000000001</v>
       </c>
       <c r="N217" s="22" t="s">
@@ -18303,10 +18384,13 @@
       </c>
       <c r="O217" s="2"/>
       <c r="P217" s="7">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>23</v>
       </c>
-      <c r="Q217" s="2"/>
+      <c r="Q217" s="66">
+        <f t="shared" si="123"/>
+        <v>759.16103276712329</v>
+      </c>
       <c r="R217" s="2"/>
       <c r="S217" s="2" t="s">
         <v>173</v>
@@ -18328,7 +18412,7 @@
       <c r="AG217" s="2"/>
       <c r="AH217" s="23"/>
     </row>
-    <row r="218" spans="1:34" hidden="1">
+    <row r="218" spans="1:34">
       <c r="A218" t="s">
         <v>114</v>
       </c>
@@ -18357,19 +18441,19 @@
         <v>181.09</v>
       </c>
       <c r="J218" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>63743.68</v>
       </c>
       <c r="K218" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>190.14450000000002</v>
       </c>
       <c r="L218" s="1">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>46086</v>
       </c>
       <c r="M218" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>66930.864000000001</v>
       </c>
       <c r="N218" s="22" t="s">
@@ -18377,10 +18461,13 @@
       </c>
       <c r="O218" s="2"/>
       <c r="P218" s="7">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>23</v>
       </c>
-      <c r="Q218" s="2"/>
+      <c r="Q218" s="66">
+        <f t="shared" si="123"/>
+        <v>759.16103276712329</v>
+      </c>
       <c r="R218" s="2"/>
       <c r="S218" s="2" t="s">
         <v>174</v>
@@ -18402,7 +18489,7 @@
       <c r="AG218" s="2"/>
       <c r="AH218" s="23"/>
     </row>
-    <row r="219" spans="1:34" hidden="1">
+    <row r="219" spans="1:34">
       <c r="A219" t="s">
         <v>114</v>
       </c>
@@ -18431,19 +18518,19 @@
         <v>181.09</v>
       </c>
       <c r="J219" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>63743.68</v>
       </c>
       <c r="K219" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>190.14450000000002</v>
       </c>
       <c r="L219" s="1">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>46086</v>
       </c>
       <c r="M219" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>66930.864000000001</v>
       </c>
       <c r="N219" s="22" t="s">
@@ -18451,10 +18538,13 @@
       </c>
       <c r="O219" s="2"/>
       <c r="P219" s="7">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>23</v>
       </c>
-      <c r="Q219" s="2"/>
+      <c r="Q219" s="66">
+        <f t="shared" si="123"/>
+        <v>759.16103276712329</v>
+      </c>
       <c r="R219" s="2"/>
       <c r="S219" s="2" t="s">
         <v>175</v>
@@ -18505,19 +18595,19 @@
         <v>149.25</v>
       </c>
       <c r="J220" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>172213.60499999998</v>
       </c>
       <c r="K220" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>156.71250000000001</v>
       </c>
       <c r="L220" s="1">
-        <f t="shared" ref="L220" si="121">D220+18</f>
+        <f t="shared" ref="L220" si="124">D220+18</f>
         <v>46091</v>
       </c>
       <c r="M220" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>180824.28524999999</v>
       </c>
       <c r="N220" s="22" t="s">
@@ -18525,11 +18615,11 @@
       </c>
       <c r="O220" s="2"/>
       <c r="P220" s="7">
-        <f t="shared" ref="P220" si="122">DAYS360(L220,W220)-(1)</f>
+        <f t="shared" ref="P220" si="125">DAYS360(L220,W220)-(1)</f>
         <v>9</v>
       </c>
       <c r="Q220" s="66">
-        <f t="shared" ref="Q220" si="123">0.18*P220*M220/365</f>
+        <f t="shared" ref="Q220" si="126">0.18*P220*M220/365</f>
         <v>802.5625811095889</v>
       </c>
       <c r="R220" s="2"/>
@@ -18586,19 +18676,19 @@
         <v>259</v>
       </c>
       <c r="J221" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>174048</v>
       </c>
       <c r="K221" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>271.95</v>
       </c>
       <c r="L221" s="1">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>46096</v>
       </c>
       <c r="M221" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>182750.4</v>
       </c>
       <c r="N221" s="22" t="s">
@@ -18606,8 +18696,8 @@
       </c>
       <c r="O221" s="2"/>
       <c r="P221" s="7">
-        <f t="shared" ca="1" si="114"/>
-        <v>90</v>
+        <f t="shared" ca="1" si="116"/>
+        <v>91</v>
       </c>
       <c r="Q221" s="2"/>
       <c r="R221" s="2"/>
@@ -18631,7 +18721,7 @@
       <c r="AG221" s="2"/>
       <c r="AH221" s="23"/>
     </row>
-    <row r="222" spans="1:34" hidden="1">
+    <row r="222" spans="1:34">
       <c r="A222" t="s">
         <v>114</v>
       </c>
@@ -18660,19 +18750,19 @@
         <v>285.71420000000001</v>
       </c>
       <c r="J222" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>285882.77137800003</v>
       </c>
       <c r="K222" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>299.99991</v>
       </c>
       <c r="L222" s="1">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>46102</v>
       </c>
       <c r="M222" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>300176.90994690004</v>
       </c>
       <c r="N222" s="22" t="s">
@@ -18680,10 +18770,13 @@
       </c>
       <c r="O222" s="2"/>
       <c r="P222" s="7">
-        <f t="shared" ref="P222" si="124">DAYS360(L222,W222)-(1)</f>
+        <f t="shared" ref="P222" si="127">DAYS360(L222,W222)-(1)</f>
         <v>9</v>
       </c>
-      <c r="Q222" s="2"/>
+      <c r="Q222" s="66">
+        <f t="shared" ref="Q222" si="128">0.18*P222*M222/365</f>
+        <v>1332.292038668433</v>
+      </c>
       <c r="R222" s="2"/>
       <c r="S222" s="2">
         <v>31752</v>
@@ -18734,19 +18827,19 @@
         <v>148.25</v>
       </c>
       <c r="J223" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>114176.22</v>
       </c>
       <c r="K223" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>155.66249999999999</v>
       </c>
       <c r="L223" s="1">
-        <f t="shared" ref="L223:L224" si="125">D223+18</f>
+        <f t="shared" ref="L223:L224" si="129">D223+18</f>
         <v>46106</v>
       </c>
       <c r="M223" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>119885.03099999999</v>
       </c>
       <c r="N223" s="22" t="s">
@@ -18754,7 +18847,7 @@
       </c>
       <c r="O223" s="2"/>
       <c r="P223" s="7">
-        <f t="shared" ref="P223:P224" si="126">DAYS360(L223,W223)-(1)</f>
+        <f t="shared" ref="P223:P224" si="130">DAYS360(L223,W223)-(1)</f>
         <v>0</v>
       </c>
       <c r="Q223" s="2">
@@ -18814,19 +18907,19 @@
         <v>148.25</v>
       </c>
       <c r="J224" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>57037.705000000002</v>
       </c>
       <c r="K224" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>155.66249999999999</v>
       </c>
       <c r="L224" s="1">
-        <f t="shared" si="125"/>
+        <f t="shared" si="129"/>
         <v>46106</v>
       </c>
       <c r="M224" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>59889.590250000001</v>
       </c>
       <c r="N224" s="22" t="s">
@@ -18834,7 +18927,7 @@
       </c>
       <c r="O224" s="2"/>
       <c r="P224" s="7">
-        <f t="shared" si="126"/>
+        <f t="shared" si="130"/>
         <v>0</v>
       </c>
       <c r="Q224" s="2">
@@ -18894,19 +18987,19 @@
         <v>287</v>
       </c>
       <c r="J225" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>195274.8</v>
       </c>
       <c r="K225" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>301.35000000000002</v>
       </c>
       <c r="L225" s="1">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>46110</v>
       </c>
       <c r="M225" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>205038.54</v>
       </c>
       <c r="N225" s="22" t="s">
@@ -18914,8 +19007,8 @@
       </c>
       <c r="O225" s="2"/>
       <c r="P225" s="7">
-        <f t="shared" ca="1" si="114"/>
-        <v>76</v>
+        <f t="shared" ca="1" si="116"/>
+        <v>77</v>
       </c>
       <c r="Q225" s="2"/>
       <c r="R225" s="2"/>
@@ -18966,19 +19059,19 @@
         <v>315</v>
       </c>
       <c r="J226" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>18900</v>
       </c>
       <c r="K226" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>330.75</v>
       </c>
       <c r="L226" s="1">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>46127</v>
       </c>
       <c r="M226" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>19845</v>
       </c>
       <c r="N226" s="22" t="s">
@@ -18986,8 +19079,8 @@
       </c>
       <c r="O226" s="2"/>
       <c r="P226" s="7">
-        <f t="shared" ca="1" si="114"/>
-        <v>60</v>
+        <f t="shared" ca="1" si="116"/>
+        <v>61</v>
       </c>
       <c r="Q226" s="2"/>
       <c r="R226" s="2"/>
@@ -19038,19 +19131,19 @@
         <v>333.33</v>
       </c>
       <c r="J227" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>333746.66249999998</v>
       </c>
       <c r="K227" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>349.99650000000003</v>
       </c>
       <c r="L227" s="1">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>46127</v>
       </c>
       <c r="M227" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>350433.99562500004</v>
       </c>
       <c r="N227" s="22" t="s">
@@ -19058,8 +19151,8 @@
       </c>
       <c r="O227" s="2"/>
       <c r="P227" s="7">
-        <f t="shared" ca="1" si="114"/>
-        <v>60</v>
+        <f t="shared" ca="1" si="116"/>
+        <v>61</v>
       </c>
       <c r="Q227" s="2"/>
       <c r="R227" s="2"/>
@@ -19110,19 +19203,19 @@
         <v>476.76</v>
       </c>
       <c r="J228" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>238380</v>
       </c>
       <c r="K228" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>500.59800000000001</v>
       </c>
       <c r="L228" s="1">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>46128</v>
       </c>
       <c r="M228" s="21">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>250299</v>
       </c>
       <c r="N228" s="22" t="s">
@@ -19130,8 +19223,8 @@
       </c>
       <c r="O228" s="2"/>
       <c r="P228" s="7">
-        <f t="shared" ca="1" si="114"/>
-        <v>59</v>
+        <f t="shared" ca="1" si="116"/>
+        <v>60</v>
       </c>
       <c r="Q228" s="2"/>
       <c r="R228" s="2"/>
@@ -19182,19 +19275,19 @@
         <v>315</v>
       </c>
       <c r="J229" s="4">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>650541.15</v>
       </c>
       <c r="K229" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>330.75</v>
       </c>
       <c r="L229" s="1">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>46128</v>
       </c>
       <c r="M229" s="24">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>683068.20750000002</v>
       </c>
       <c r="N229" s="25">
@@ -19202,8 +19295,8 @@
       </c>
       <c r="O229" s="2"/>
       <c r="P229" s="7">
-        <f t="shared" ca="1" si="114"/>
-        <v>59</v>
+        <f t="shared" ca="1" si="116"/>
+        <v>60</v>
       </c>
       <c r="Q229" s="2"/>
       <c r="R229" s="2"/>
@@ -19684,11 +19777,11 @@
         <v>416.9</v>
       </c>
       <c r="L241" s="1">
-        <f t="shared" ref="L241:L244" si="127">D241+15</f>
+        <f t="shared" ref="L241:L244" si="131">D241+15</f>
         <v>45956</v>
       </c>
       <c r="M241" s="21">
-        <f t="shared" ref="M241:M244" si="128">H241*K241</f>
+        <f t="shared" ref="M241:M244" si="132">H241*K241</f>
         <v>208450</v>
       </c>
       <c r="N241" s="22" t="s">
@@ -19696,8 +19789,8 @@
       </c>
       <c r="O241" s="2"/>
       <c r="P241" s="7">
-        <f t="shared" ref="P241" ca="1" si="129">DAYS360(L241,TODAY())-(1)</f>
-        <v>229</v>
+        <f t="shared" ref="P241" ca="1" si="133">DAYS360(L241,TODAY())-(1)</f>
+        <v>230</v>
       </c>
       <c r="Q241" s="2"/>
       <c r="R241" s="2"/>
@@ -19754,11 +19847,11 @@
         <v>241.07140000000001</v>
       </c>
       <c r="L242" s="1">
-        <f t="shared" si="127"/>
+        <f t="shared" si="131"/>
         <v>45956</v>
       </c>
       <c r="M242" s="21">
-        <f t="shared" si="128"/>
+        <f t="shared" si="132"/>
         <v>91607.131999999998</v>
       </c>
       <c r="N242" s="22" t="s">
@@ -19815,7 +19908,7 @@
         <v>185.97</v>
       </c>
       <c r="J243" s="4">
-        <f t="shared" ref="J243:J244" si="130">H243*I243</f>
+        <f t="shared" ref="J243:J244" si="134">H243*I243</f>
         <v>62599.361700000001</v>
       </c>
       <c r="K243" s="4">
@@ -19823,11 +19916,11 @@
         <v>185.97</v>
       </c>
       <c r="L243" s="1">
-        <f t="shared" si="127"/>
+        <f t="shared" si="131"/>
         <v>45956</v>
       </c>
       <c r="M243" s="21">
-        <f t="shared" si="128"/>
+        <f t="shared" si="132"/>
         <v>62599.361700000001</v>
       </c>
       <c r="N243" s="22" t="s">
@@ -19881,7 +19974,7 @@
         <v>175.57</v>
       </c>
       <c r="J244" s="4">
-        <f t="shared" si="130"/>
+        <f t="shared" si="134"/>
         <v>120089.87999999999</v>
       </c>
       <c r="K244" s="4">
@@ -19889,11 +19982,11 @@
         <v>175.57</v>
       </c>
       <c r="L244" s="1">
-        <f t="shared" si="127"/>
+        <f t="shared" si="131"/>
         <v>15</v>
       </c>
       <c r="M244" s="21">
-        <f t="shared" si="128"/>
+        <f t="shared" si="132"/>
         <v>120089.87999999999</v>
       </c>
       <c r="N244" s="22" t="s">
@@ -20221,15 +20314,15 @@
       <c r="G254" s="68"/>
       <c r="H254" s="12">
         <f>SUBTOTAL(9,H5:H109)+SUBTOTAL(9,H115:H235)+SUBTOTAL(9,H241:H249)</f>
-        <v>22347.4</v>
+        <v>25542.439999999995</v>
       </c>
       <c r="I254" s="10">
         <f>J254/H254</f>
-        <v>216.35448642866731</v>
+        <v>258.73299412800827</v>
       </c>
       <c r="J254" s="12">
         <f>SUBTOTAL(9,J5:J109)+SUBTOTAL(9,J115:J235)+SUBTOTAL(9,J241:J249)</f>
-        <v>4834960.2500160001</v>
+        <v>6608671.9785350021</v>
       </c>
       <c r="K254" s="68"/>
       <c r="L254" s="68"/>
@@ -20253,7 +20346,7 @@
     <filterColumn colId="1" showButton="0"/>
     <filterColumn colId="4">
       <filters>
-        <filter val="KRISHNAYASH YARN PVT LTD"/>
+        <filter val="SHREE RAM YARN TRADING CO"/>
       </filters>
     </filterColumn>
     <filterColumn colId="6"/>
@@ -24734,8 +24827,8 @@
       </c>
       <c r="O5" s="2"/>
       <c r="P5" s="7">
-        <f ca="1">DAYS360(L5,TODAY())-(1)</f>
-        <v>57</v>
+        <f>DAYS360(L5,W5)-(1)</f>
+        <v>25</v>
       </c>
       <c r="Q5" s="66"/>
       <c r="R5" s="2"/>
@@ -24807,7 +24900,7 @@
       <c r="O6" s="2"/>
       <c r="P6" s="7">
         <f t="shared" ref="P6:P27" ca="1" si="5">DAYS360(L6,TODAY())-(1)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
@@ -24875,7 +24968,7 @@
       <c r="O7" s="2"/>
       <c r="P7" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
@@ -24943,7 +25036,7 @@
       <c r="O8" s="2"/>
       <c r="P8" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
@@ -25081,7 +25174,7 @@
       <c r="O10" s="2"/>
       <c r="P10" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
@@ -25222,7 +25315,7 @@
       <c r="O12" s="2"/>
       <c r="P12" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
@@ -25290,7 +25383,7 @@
       <c r="O13" s="2"/>
       <c r="P13" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
@@ -25358,7 +25451,7 @@
       <c r="O14" s="2"/>
       <c r="P14" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
@@ -25426,7 +25519,7 @@
       <c r="O15" s="2"/>
       <c r="P15" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
@@ -25494,7 +25587,7 @@
       <c r="O16" s="2"/>
       <c r="P16" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
@@ -25562,7 +25655,7 @@
       <c r="O17" s="2"/>
       <c r="P17" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
@@ -25630,7 +25723,7 @@
       <c r="O18" s="2"/>
       <c r="P18" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
@@ -25698,7 +25791,7 @@
       <c r="O19" s="2"/>
       <c r="P19" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
@@ -25766,7 +25859,7 @@
       <c r="O20" s="2"/>
       <c r="P20" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
@@ -25834,7 +25927,7 @@
       <c r="O21" s="2"/>
       <c r="P21" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
@@ -25902,7 +25995,7 @@
       <c r="O22" s="2"/>
       <c r="P22" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
@@ -25970,7 +26063,7 @@
       <c r="O23" s="2"/>
       <c r="P23" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
@@ -26038,7 +26131,7 @@
       <c r="O24" s="130"/>
       <c r="P24" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q24" s="130"/>
       <c r="R24" s="130"/>
@@ -26106,7 +26199,7 @@
       <c r="O25" s="130"/>
       <c r="P25" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q25" s="130"/>
       <c r="R25" s="130"/>
@@ -26174,7 +26267,7 @@
       <c r="O26" s="130"/>
       <c r="P26" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q26" s="130"/>
       <c r="R26" s="130"/>
@@ -26242,7 +26335,7 @@
       <c r="O27" s="130"/>
       <c r="P27" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q27" s="130"/>
       <c r="R27" s="130"/>
@@ -26310,7 +26403,7 @@
       <c r="O28" s="130"/>
       <c r="P28" s="7">
         <f t="shared" ref="P28:P35" ca="1" si="18">DAYS360(L28,TODAY())-(1)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q28" s="130"/>
       <c r="R28" s="130"/>
@@ -26378,7 +26471,7 @@
       <c r="O29" s="130"/>
       <c r="P29" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q29" s="130"/>
       <c r="R29" s="130"/>
@@ -26446,7 +26539,7 @@
       <c r="O30" s="130"/>
       <c r="P30" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q30" s="130"/>
       <c r="R30" s="130"/>
@@ -26514,7 +26607,7 @@
       <c r="O31" s="130"/>
       <c r="P31" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q31" s="130"/>
       <c r="R31" s="130"/>
@@ -26582,7 +26675,7 @@
       <c r="O32" s="130"/>
       <c r="P32" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q32" s="130"/>
       <c r="R32" s="130"/>
@@ -26650,7 +26743,7 @@
       <c r="O33" s="130"/>
       <c r="P33" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q33" s="130"/>
       <c r="R33" s="130"/>
@@ -26718,7 +26811,7 @@
       <c r="O34" s="130"/>
       <c r="P34" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q34" s="130"/>
       <c r="R34" s="130"/>
@@ -26786,7 +26879,7 @@
       <c r="O35" s="130"/>
       <c r="P35" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q35" s="130"/>
       <c r="R35" s="130"/>
@@ -27569,7 +27662,7 @@
         <v>17</v>
       </c>
       <c r="Q54" s="66">
-        <f t="shared" ref="Q54" si="20">0.18*P54*M54/365</f>
+        <f t="shared" ref="Q54:Q56" si="20">0.18*P54*M54/365</f>
         <v>850.09377945205483</v>
       </c>
       <c r="R54" s="2"/>
@@ -27640,10 +27733,13 @@
       </c>
       <c r="O55" s="2"/>
       <c r="P55" s="7">
-        <f t="shared" ref="P55:P79" ca="1" si="22">DAYS360(L55,TODAY())-(1)</f>
-        <v>49</v>
-      </c>
-      <c r="Q55" s="2"/>
+        <f>DAYS360(L55,W55)-(1)</f>
+        <v>15</v>
+      </c>
+      <c r="Q55" s="66">
+        <f t="shared" si="20"/>
+        <v>1797.834559068493</v>
+      </c>
       <c r="R55" s="2"/>
       <c r="S55" s="116" t="s">
         <v>217</v>
@@ -27694,7 +27790,7 @@
         <v>228828.59999999998</v>
       </c>
       <c r="K56" s="4">
-        <f t="shared" ref="K56:K73" si="23">I56*1.05</f>
+        <f t="shared" ref="K56:K73" si="22">I56*1.05</f>
         <v>210.21</v>
       </c>
       <c r="L56" s="1">
@@ -27710,10 +27806,13 @@
       </c>
       <c r="O56" s="2"/>
       <c r="P56" s="7">
-        <f t="shared" ca="1" si="22"/>
-        <v>49</v>
-      </c>
-      <c r="Q56" s="2"/>
+        <f>DAYS360(L56,W56)-(1)</f>
+        <v>15</v>
+      </c>
+      <c r="Q56" s="66">
+        <f t="shared" si="20"/>
+        <v>1777.3399479452053</v>
+      </c>
       <c r="R56" s="2"/>
       <c r="S56" s="116" t="s">
         <v>218</v>
@@ -27760,11 +27859,11 @@
         <v>285</v>
       </c>
       <c r="J57" s="4">
-        <f t="shared" ref="J57" si="24">H57*I57</f>
+        <f t="shared" ref="J57" si="23">H57*I57</f>
         <v>119061.59999999999</v>
       </c>
       <c r="K57" s="4">
-        <f t="shared" ref="K57" si="25">I57*1.05</f>
+        <f t="shared" ref="K57" si="24">I57*1.05</f>
         <v>299.25</v>
       </c>
       <c r="L57" s="1">
@@ -27780,8 +27879,8 @@
       </c>
       <c r="O57" s="2"/>
       <c r="P57" s="7">
-        <f t="shared" ca="1" si="22"/>
-        <v>45</v>
+        <f t="shared" ref="P55:P79" ca="1" si="25">DAYS360(L57,TODAY())-(1)</f>
+        <v>46</v>
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" s="2"/>
@@ -27832,7 +27931,7 @@
         <v>239880</v>
       </c>
       <c r="K58" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>503.74799999999999</v>
       </c>
       <c r="L58" s="1">
@@ -27848,8 +27947,8 @@
       </c>
       <c r="O58" s="2"/>
       <c r="P58" s="7">
-        <f t="shared" ca="1" si="22"/>
-        <v>43</v>
+        <f t="shared" ca="1" si="25"/>
+        <v>44</v>
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" s="2"/>
@@ -27902,7 +28001,7 @@
         <v>20673.624400000001</v>
       </c>
       <c r="K59" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>344.99850000000004</v>
       </c>
       <c r="L59" s="1">
@@ -27918,8 +28017,8 @@
       </c>
       <c r="O59" s="2"/>
       <c r="P59" s="7">
-        <f t="shared" ca="1" si="22"/>
-        <v>11</v>
+        <f t="shared" ca="1" si="25"/>
+        <v>12</v>
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" s="2"/>
@@ -27970,7 +28069,7 @@
         <v>20909.558400000002</v>
       </c>
       <c r="K60" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>344.988</v>
       </c>
       <c r="L60" s="1">
@@ -27986,8 +28085,8 @@
       </c>
       <c r="O60" s="2"/>
       <c r="P60" s="7">
-        <f t="shared" ca="1" si="22"/>
-        <v>10</v>
+        <f t="shared" ca="1" si="25"/>
+        <v>11</v>
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" s="2"/>
@@ -28038,7 +28137,7 @@
         <v>153959.68799999999</v>
       </c>
       <c r="K61" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>209.16</v>
       </c>
       <c r="L61" s="1">
@@ -28054,8 +28153,8 @@
       </c>
       <c r="O61" s="2"/>
       <c r="P61" s="7">
-        <f t="shared" ca="1" si="22"/>
-        <v>35</v>
+        <f t="shared" ca="1" si="25"/>
+        <v>36</v>
       </c>
       <c r="Q61" s="2"/>
       <c r="R61" s="2"/>
@@ -28108,7 +28207,7 @@
         <v>77148.168000000005</v>
       </c>
       <c r="K62" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>209.16</v>
       </c>
       <c r="L62" s="1">
@@ -28124,8 +28223,8 @@
       </c>
       <c r="O62" s="2"/>
       <c r="P62" s="7">
-        <f t="shared" ca="1" si="22"/>
-        <v>35</v>
+        <f t="shared" ca="1" si="25"/>
+        <v>36</v>
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" s="2"/>
@@ -28178,7 +28277,7 @@
         <v>32203.145700000001</v>
       </c>
       <c r="K63" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>344.99850000000004</v>
       </c>
       <c r="L63" s="1">
@@ -28194,8 +28293,8 @@
       </c>
       <c r="O63" s="2"/>
       <c r="P63" s="7">
-        <f t="shared" ca="1" si="22"/>
-        <v>9</v>
+        <f t="shared" ca="1" si="25"/>
+        <v>10</v>
       </c>
       <c r="Q63" s="2"/>
       <c r="R63" s="2"/>
@@ -28246,7 +28345,7 @@
         <v>229134.6648</v>
       </c>
       <c r="K64" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>207.99450000000002</v>
       </c>
       <c r="L64" s="1">
@@ -28316,7 +28415,7 @@
         <v>31089.293400000002</v>
       </c>
       <c r="K65" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>344.99850000000004</v>
       </c>
       <c r="L65" s="1">
@@ -28332,8 +28431,8 @@
       </c>
       <c r="O65" s="2"/>
       <c r="P65" s="7">
-        <f t="shared" ca="1" si="22"/>
-        <v>8</v>
+        <f t="shared" ca="1" si="25"/>
+        <v>9</v>
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" s="2"/>
@@ -28384,7 +28483,7 @@
         <v>308747.60000000003</v>
       </c>
       <c r="K66" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>325.5</v>
       </c>
       <c r="L66" s="1">
@@ -28470,8 +28569,8 @@
       </c>
       <c r="O67" s="2"/>
       <c r="P67" s="7">
-        <f t="shared" ca="1" si="22"/>
-        <v>32</v>
+        <f t="shared" ca="1" si="25"/>
+        <v>33</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" s="2"/>
@@ -28522,7 +28621,7 @@
         <v>346851.38521500002</v>
       </c>
       <c r="K68" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>359.999955</v>
       </c>
       <c r="L68" s="1">
@@ -28538,8 +28637,8 @@
       </c>
       <c r="O68" s="2"/>
       <c r="P68" s="7">
-        <f t="shared" ca="1" si="22"/>
-        <v>30</v>
+        <f t="shared" ca="1" si="25"/>
+        <v>31</v>
       </c>
       <c r="Q68" s="2"/>
       <c r="R68" s="2"/>
@@ -28590,7 +28689,7 @@
         <v>137999.4</v>
       </c>
       <c r="K69" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>344.99850000000004</v>
       </c>
       <c r="L69" s="1">
@@ -28606,8 +28705,8 @@
       </c>
       <c r="O69" s="2"/>
       <c r="P69" s="7">
-        <f t="shared" ca="1" si="22"/>
-        <v>29</v>
+        <f t="shared" ca="1" si="25"/>
+        <v>30</v>
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" s="2"/>
@@ -28658,7 +28757,7 @@
         <v>335096.33157000004</v>
       </c>
       <c r="K70" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>349.99965000000003</v>
       </c>
       <c r="L70" s="1">
@@ -28674,8 +28773,8 @@
       </c>
       <c r="O70" s="2"/>
       <c r="P70" s="7">
-        <f t="shared" ca="1" si="22"/>
-        <v>21</v>
+        <f t="shared" ca="1" si="25"/>
+        <v>22</v>
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" s="2"/>
@@ -28726,7 +28825,7 @@
         <v>332889.66711000004</v>
       </c>
       <c r="K71" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>349.99965000000003</v>
       </c>
       <c r="L71" s="1">
@@ -28742,8 +28841,8 @@
       </c>
       <c r="O71" s="2"/>
       <c r="P71" s="7">
-        <f t="shared" ca="1" si="22"/>
-        <v>21</v>
+        <f t="shared" ca="1" si="25"/>
+        <v>22</v>
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" s="2"/>
@@ -28794,7 +28893,7 @@
         <v>339370.24329300004</v>
       </c>
       <c r="K72" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>359.999955</v>
       </c>
       <c r="L72" s="1">
@@ -28810,8 +28909,8 @@
       </c>
       <c r="O72" s="2"/>
       <c r="P72" s="7">
-        <f t="shared" ca="1" si="22"/>
-        <v>26</v>
+        <f t="shared" ca="1" si="25"/>
+        <v>27</v>
       </c>
       <c r="Q72" s="2"/>
       <c r="R72" s="2"/>
@@ -28862,7 +28961,7 @@
         <v>169803.16353000002</v>
       </c>
       <c r="K73" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>349.99965000000003</v>
       </c>
       <c r="L73" s="1">
@@ -28878,8 +28977,8 @@
       </c>
       <c r="O73" s="2"/>
       <c r="P73" s="7">
-        <f t="shared" ca="1" si="22"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="25"/>
+        <v>16</v>
       </c>
       <c r="Q73" s="2"/>
       <c r="R73" s="2"/>
@@ -28946,8 +29045,8 @@
       </c>
       <c r="O74" s="130"/>
       <c r="P74" s="131">
-        <f t="shared" ca="1" si="22"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="25"/>
+        <v>16</v>
       </c>
       <c r="Q74" s="130"/>
       <c r="R74" s="130"/>
@@ -29014,8 +29113,8 @@
       </c>
       <c r="O75" s="130"/>
       <c r="P75" s="131">
-        <f t="shared" ca="1" si="22"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="25"/>
+        <v>16</v>
       </c>
       <c r="Q75" s="130"/>
       <c r="R75" s="130"/>
@@ -29082,8 +29181,8 @@
       </c>
       <c r="O76" s="130"/>
       <c r="P76" s="131">
-        <f t="shared" ca="1" si="22"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="25"/>
+        <v>16</v>
       </c>
       <c r="Q76" s="130"/>
       <c r="R76" s="130"/>
@@ -29150,8 +29249,8 @@
       </c>
       <c r="O77" s="130"/>
       <c r="P77" s="131">
-        <f t="shared" ca="1" si="22"/>
-        <v>9</v>
+        <f t="shared" ca="1" si="25"/>
+        <v>10</v>
       </c>
       <c r="Q77" s="130"/>
       <c r="R77" s="130"/>
@@ -29218,8 +29317,8 @@
       </c>
       <c r="O78" s="130"/>
       <c r="P78" s="131">
-        <f t="shared" ca="1" si="22"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="25"/>
+        <v>16</v>
       </c>
       <c r="Q78" s="130"/>
       <c r="R78" s="130"/>
@@ -29286,8 +29385,8 @@
       </c>
       <c r="O79" s="130"/>
       <c r="P79" s="131">
-        <f t="shared" ca="1" si="22"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="25"/>
+        <v>16</v>
       </c>
       <c r="Q79" s="130"/>
       <c r="R79" s="130"/>
@@ -31610,18 +31709,18 @@
     <filterColumn colId="24" showButton="0"/>
   </autoFilter>
   <mergeCells count="12">
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="Y52:Z52"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="Y120:Z120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="Y121:Z121"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="Y2:Z2"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="Y3:Z3"/>
     <mergeCell ref="B51:C51"/>
     <mergeCell ref="Y51:Z51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="Y52:Z52"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="Y120:Z120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="Y121:Z121"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/YarnBook-TEX WEAVES.xlsx
+++ b/YarnBook-TEX WEAVES.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="90" windowWidth="28755" windowHeight="12090"/>
+    <workbookView xWindow="0" yWindow="90" windowWidth="28755" windowHeight="12090" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="25-26" sheetId="1" r:id="rId1"/>
@@ -12,6 +12,7 @@
     <sheet name="SHEET" sheetId="2" r:id="rId3"/>
     <sheet name="26-27" sheetId="5" r:id="rId4"/>
     <sheet name="26-27 JW" sheetId="6" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="7" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'25-26'!$A$2:$AH$251</definedName>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2064" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2179" uniqueCount="315">
   <si>
     <t>H NO</t>
   </si>
@@ -1324,7 +1325,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="151">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1723,6 +1724,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="1" fontId="3" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2063,10 +2070,10 @@
   <sheetData>
     <row r="1" spans="1:34" ht="15.75" thickBot="1"/>
     <row r="2" spans="1:34" ht="15.75" thickBot="1">
-      <c r="B2" s="147" t="s">
+      <c r="B2" s="149" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="147"/>
+      <c r="C2" s="149"/>
       <c r="D2" s="9" t="s">
         <v>2</v>
       </c>
@@ -2123,19 +2130,19 @@
       <c r="W2" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="Y2" s="147" t="s">
+      <c r="Y2" s="149" t="s">
         <v>39</v>
       </c>
-      <c r="Z2" s="147"/>
+      <c r="Z2" s="149"/>
     </row>
     <row r="3" spans="1:34" ht="15.75" hidden="1" thickBot="1">
       <c r="A3" t="s">
         <v>113</v>
       </c>
-      <c r="B3" s="148" t="s">
+      <c r="B3" s="150" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="148"/>
+      <c r="C3" s="150"/>
       <c r="D3" s="1"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -2158,10 +2165,10 @@
       <c r="U3" s="2"/>
       <c r="V3" s="2"/>
       <c r="W3" s="1"/>
-      <c r="Y3" s="148" t="s">
+      <c r="Y3" s="150" t="s">
         <v>33</v>
       </c>
-      <c r="Z3" s="148"/>
+      <c r="Z3" s="150"/>
       <c r="AA3" s="1"/>
       <c r="AB3" s="2"/>
       <c r="AC3" s="3"/>
@@ -3222,7 +3229,7 @@
       <c r="O16" s="2"/>
       <c r="P16" s="7">
         <f t="shared" ref="P16:P17" ca="1" si="9">DAYS360(L16,TODAY())-(1)</f>
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
@@ -3294,11 +3301,11 @@
       <c r="O17" s="49"/>
       <c r="P17" s="53">
         <f t="shared" ca="1" si="9"/>
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="Q17" s="66">
         <f t="shared" ref="Q17:Q26" ca="1" si="10">0.18*P17*M17/365</f>
-        <v>10968.062195401646</v>
+        <v>11195.885445751233</v>
       </c>
       <c r="R17" s="49"/>
       <c r="S17" s="49">
@@ -10253,27 +10260,27 @@
       <c r="A112" t="s">
         <v>114</v>
       </c>
-      <c r="B112" s="147" t="s">
+      <c r="B112" s="149" t="s">
         <v>40</v>
       </c>
-      <c r="C112" s="147"/>
-      <c r="Y112" s="147" t="s">
+      <c r="C112" s="149"/>
+      <c r="Y112" s="149" t="s">
         <v>39</v>
       </c>
-      <c r="Z112" s="147"/>
+      <c r="Z112" s="149"/>
     </row>
     <row r="113" spans="1:34" ht="15.75" hidden="1" thickBot="1">
       <c r="A113" t="s">
         <v>114</v>
       </c>
-      <c r="B113" s="148" t="s">
+      <c r="B113" s="150" t="s">
         <v>34</v>
       </c>
-      <c r="C113" s="148"/>
-      <c r="Y113" s="148" t="s">
+      <c r="C113" s="150"/>
+      <c r="Y113" s="150" t="s">
         <v>34</v>
       </c>
-      <c r="Z113" s="148"/>
+      <c r="Z113" s="150"/>
       <c r="AA113" s="1"/>
       <c r="AB113" s="2"/>
       <c r="AC113" s="3"/>
@@ -16788,7 +16795,7 @@
       <c r="O196" s="2"/>
       <c r="P196" s="7">
         <f t="shared" ref="P196:P229" ca="1" si="116">DAYS360(L196,TODAY())-(1)</f>
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="Q196" s="2"/>
       <c r="R196" s="2"/>
@@ -18007,7 +18014,7 @@
       <c r="O212" s="2"/>
       <c r="P212" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="Q212" s="2"/>
       <c r="R212" s="2"/>
@@ -18697,7 +18704,7 @@
       <c r="O221" s="2"/>
       <c r="P221" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="Q221" s="2"/>
       <c r="R221" s="2"/>
@@ -19008,7 +19015,7 @@
       <c r="O225" s="2"/>
       <c r="P225" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="Q225" s="2"/>
       <c r="R225" s="2"/>
@@ -19080,7 +19087,7 @@
       <c r="O226" s="2"/>
       <c r="P226" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="Q226" s="2"/>
       <c r="R226" s="2"/>
@@ -19152,7 +19159,7 @@
       <c r="O227" s="2"/>
       <c r="P227" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="Q227" s="2"/>
       <c r="R227" s="2"/>
@@ -19224,7 +19231,7 @@
       <c r="O228" s="2"/>
       <c r="P228" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="Q228" s="2"/>
       <c r="R228" s="2"/>
@@ -19296,7 +19303,7 @@
       <c r="O229" s="2"/>
       <c r="P229" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="Q229" s="2"/>
       <c r="R229" s="2"/>
@@ -19617,27 +19624,27 @@
       <c r="A238" t="s">
         <v>56</v>
       </c>
-      <c r="B238" s="147" t="s">
+      <c r="B238" s="149" t="s">
         <v>109</v>
       </c>
-      <c r="C238" s="147"/>
-      <c r="Y238" s="147" t="s">
+      <c r="C238" s="149"/>
+      <c r="Y238" s="149" t="s">
         <v>39</v>
       </c>
-      <c r="Z238" s="147"/>
+      <c r="Z238" s="149"/>
     </row>
     <row r="239" spans="1:34" ht="15.75" hidden="1" thickBot="1">
       <c r="A239" t="s">
         <v>56</v>
       </c>
-      <c r="B239" s="148" t="s">
+      <c r="B239" s="150" t="s">
         <v>108</v>
       </c>
-      <c r="C239" s="148"/>
-      <c r="Y239" s="148" t="s">
+      <c r="C239" s="150"/>
+      <c r="Y239" s="150" t="s">
         <v>34</v>
       </c>
-      <c r="Z239" s="148"/>
+      <c r="Z239" s="150"/>
       <c r="AA239" s="1"/>
       <c r="AB239" s="2"/>
       <c r="AC239" s="3"/>
@@ -19790,7 +19797,7 @@
       <c r="O241" s="2"/>
       <c r="P241" s="7">
         <f t="shared" ref="P241" ca="1" si="133">DAYS360(L241,TODAY())-(1)</f>
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="Q241" s="2"/>
       <c r="R241" s="2"/>
@@ -24540,6 +24547,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AH135"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
@@ -24579,10 +24587,10 @@
   <sheetData>
     <row r="1" spans="1:34" ht="15.75" thickBot="1"/>
     <row r="2" spans="1:34" ht="15.75" thickBot="1">
-      <c r="B2" s="147" t="s">
+      <c r="B2" s="149" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="147"/>
+      <c r="C2" s="149"/>
       <c r="D2" s="9" t="s">
         <v>2</v>
       </c>
@@ -24639,19 +24647,19 @@
       <c r="W2" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="Y2" s="147" t="s">
+      <c r="Y2" s="149" t="s">
         <v>39</v>
       </c>
-      <c r="Z2" s="147"/>
-    </row>
-    <row r="3" spans="1:34" ht="15.75" thickBot="1">
+      <c r="Z2" s="149"/>
+    </row>
+    <row r="3" spans="1:34" ht="15.75" hidden="1" thickBot="1">
       <c r="A3" t="s">
         <v>113</v>
       </c>
-      <c r="B3" s="148" t="s">
+      <c r="B3" s="150" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="148"/>
+      <c r="C3" s="150"/>
       <c r="D3" s="1"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -24674,10 +24682,10 @@
       <c r="U3" s="2"/>
       <c r="V3" s="2"/>
       <c r="W3" s="1"/>
-      <c r="Y3" s="148" t="s">
+      <c r="Y3" s="150" t="s">
         <v>33</v>
       </c>
-      <c r="Z3" s="148"/>
+      <c r="Z3" s="150"/>
       <c r="AA3" s="1"/>
       <c r="AB3" s="2"/>
       <c r="AC3" s="3"/>
@@ -24687,7 +24695,7 @@
       <c r="AG3" s="2"/>
       <c r="AH3" s="1"/>
     </row>
-    <row r="4" spans="1:34" ht="15.75" thickBot="1">
+    <row r="4" spans="1:34" ht="15.75" hidden="1" thickBot="1">
       <c r="A4" t="s">
         <v>113</v>
       </c>
@@ -24854,7 +24862,7 @@
       <c r="AG5" s="2"/>
       <c r="AH5" s="23"/>
     </row>
-    <row r="6" spans="1:34">
+    <row r="6" spans="1:34" hidden="1">
       <c r="A6" t="s">
         <v>113</v>
       </c>
@@ -24900,7 +24908,7 @@
       <c r="O6" s="2"/>
       <c r="P6" s="7">
         <f t="shared" ref="P6:P27" ca="1" si="5">DAYS360(L6,TODAY())-(1)</f>
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
@@ -24922,7 +24930,7 @@
       <c r="AG6" s="2"/>
       <c r="AH6" s="23"/>
     </row>
-    <row r="7" spans="1:34">
+    <row r="7" spans="1:34" hidden="1">
       <c r="A7" t="s">
         <v>113</v>
       </c>
@@ -24968,7 +24976,7 @@
       <c r="O7" s="2"/>
       <c r="P7" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
@@ -24990,7 +24998,7 @@
       <c r="AG7" s="2"/>
       <c r="AH7" s="23"/>
     </row>
-    <row r="8" spans="1:34">
+    <row r="8" spans="1:34" hidden="1">
       <c r="A8" t="s">
         <v>113</v>
       </c>
@@ -25036,7 +25044,7 @@
       <c r="O8" s="2"/>
       <c r="P8" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
@@ -25058,7 +25066,7 @@
       <c r="AG8" s="2"/>
       <c r="AH8" s="23"/>
     </row>
-    <row r="9" spans="1:34">
+    <row r="9" spans="1:34" hidden="1">
       <c r="A9" t="s">
         <v>113</v>
       </c>
@@ -25128,7 +25136,7 @@
       <c r="AG9" s="2"/>
       <c r="AH9" s="23"/>
     </row>
-    <row r="10" spans="1:34">
+    <row r="10" spans="1:34" hidden="1">
       <c r="A10" t="s">
         <v>113</v>
       </c>
@@ -25174,7 +25182,7 @@
       <c r="O10" s="2"/>
       <c r="P10" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
@@ -25196,7 +25204,7 @@
       <c r="AG10" s="2"/>
       <c r="AH10" s="23"/>
     </row>
-    <row r="11" spans="1:34">
+    <row r="11" spans="1:34" hidden="1">
       <c r="A11" t="s">
         <v>113</v>
       </c>
@@ -25269,7 +25277,7 @@
       <c r="AG11" s="2"/>
       <c r="AH11" s="23"/>
     </row>
-    <row r="12" spans="1:34">
+    <row r="12" spans="1:34" hidden="1">
       <c r="A12" t="s">
         <v>113</v>
       </c>
@@ -25315,7 +25323,7 @@
       <c r="O12" s="2"/>
       <c r="P12" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
@@ -25337,7 +25345,7 @@
       <c r="AG12" s="2"/>
       <c r="AH12" s="23"/>
     </row>
-    <row r="13" spans="1:34">
+    <row r="13" spans="1:34" hidden="1">
       <c r="A13" t="s">
         <v>270</v>
       </c>
@@ -25383,7 +25391,7 @@
       <c r="O13" s="2"/>
       <c r="P13" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
@@ -25405,7 +25413,7 @@
       <c r="AG13" s="2"/>
       <c r="AH13" s="23"/>
     </row>
-    <row r="14" spans="1:34">
+    <row r="14" spans="1:34" hidden="1">
       <c r="A14" t="s">
         <v>113</v>
       </c>
@@ -25451,7 +25459,7 @@
       <c r="O14" s="2"/>
       <c r="P14" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
@@ -25473,7 +25481,7 @@
       <c r="AG14" s="2"/>
       <c r="AH14" s="23"/>
     </row>
-    <row r="15" spans="1:34">
+    <row r="15" spans="1:34" hidden="1">
       <c r="A15" t="s">
         <v>113</v>
       </c>
@@ -25519,7 +25527,7 @@
       <c r="O15" s="2"/>
       <c r="P15" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
@@ -25541,7 +25549,7 @@
       <c r="AG15" s="2"/>
       <c r="AH15" s="23"/>
     </row>
-    <row r="16" spans="1:34">
+    <row r="16" spans="1:34" hidden="1">
       <c r="A16" t="s">
         <v>113</v>
       </c>
@@ -25587,7 +25595,7 @@
       <c r="O16" s="2"/>
       <c r="P16" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
@@ -25609,7 +25617,7 @@
       <c r="AG16" s="2"/>
       <c r="AH16" s="23"/>
     </row>
-    <row r="17" spans="1:34">
+    <row r="17" spans="1:34" hidden="1">
       <c r="A17" t="s">
         <v>113</v>
       </c>
@@ -25655,7 +25663,7 @@
       <c r="O17" s="2"/>
       <c r="P17" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
@@ -25677,7 +25685,7 @@
       <c r="AG17" s="2"/>
       <c r="AH17" s="23"/>
     </row>
-    <row r="18" spans="1:34">
+    <row r="18" spans="1:34" hidden="1">
       <c r="A18" t="s">
         <v>113</v>
       </c>
@@ -25723,7 +25731,7 @@
       <c r="O18" s="2"/>
       <c r="P18" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
@@ -25745,7 +25753,7 @@
       <c r="AG18" s="2"/>
       <c r="AH18" s="23"/>
     </row>
-    <row r="19" spans="1:34">
+    <row r="19" spans="1:34" hidden="1">
       <c r="A19" t="s">
         <v>113</v>
       </c>
@@ -25791,7 +25799,7 @@
       <c r="O19" s="2"/>
       <c r="P19" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
@@ -25813,7 +25821,7 @@
       <c r="AG19" s="2"/>
       <c r="AH19" s="23"/>
     </row>
-    <row r="20" spans="1:34">
+    <row r="20" spans="1:34" hidden="1">
       <c r="A20" t="s">
         <v>113</v>
       </c>
@@ -25859,7 +25867,7 @@
       <c r="O20" s="2"/>
       <c r="P20" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
@@ -25881,7 +25889,7 @@
       <c r="AG20" s="2"/>
       <c r="AH20" s="23"/>
     </row>
-    <row r="21" spans="1:34">
+    <row r="21" spans="1:34" hidden="1">
       <c r="A21" t="s">
         <v>113</v>
       </c>
@@ -25927,7 +25935,7 @@
       <c r="O21" s="2"/>
       <c r="P21" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
@@ -25949,7 +25957,7 @@
       <c r="AG21" s="2"/>
       <c r="AH21" s="23"/>
     </row>
-    <row r="22" spans="1:34">
+    <row r="22" spans="1:34" hidden="1">
       <c r="A22" t="s">
         <v>113</v>
       </c>
@@ -25995,7 +26003,7 @@
       <c r="O22" s="2"/>
       <c r="P22" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
@@ -26017,7 +26025,7 @@
       <c r="AG22" s="2"/>
       <c r="AH22" s="23"/>
     </row>
-    <row r="23" spans="1:34">
+    <row r="23" spans="1:34" hidden="1">
       <c r="A23" t="s">
         <v>113</v>
       </c>
@@ -26063,7 +26071,7 @@
       <c r="O23" s="2"/>
       <c r="P23" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
@@ -26085,7 +26093,7 @@
       <c r="AG23" s="2"/>
       <c r="AH23" s="23"/>
     </row>
-    <row r="24" spans="1:34">
+    <row r="24" spans="1:34" hidden="1">
       <c r="A24" t="s">
         <v>113</v>
       </c>
@@ -26131,7 +26139,7 @@
       <c r="O24" s="130"/>
       <c r="P24" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="Q24" s="130"/>
       <c r="R24" s="130"/>
@@ -26153,7 +26161,7 @@
       <c r="AG24" s="2"/>
       <c r="AH24" s="23"/>
     </row>
-    <row r="25" spans="1:34">
+    <row r="25" spans="1:34" hidden="1">
       <c r="A25" t="s">
         <v>113</v>
       </c>
@@ -26199,7 +26207,7 @@
       <c r="O25" s="130"/>
       <c r="P25" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="Q25" s="130"/>
       <c r="R25" s="130"/>
@@ -26221,7 +26229,7 @@
       <c r="AG25" s="2"/>
       <c r="AH25" s="23"/>
     </row>
-    <row r="26" spans="1:34">
+    <row r="26" spans="1:34" hidden="1">
       <c r="A26" t="s">
         <v>113</v>
       </c>
@@ -26267,7 +26275,7 @@
       <c r="O26" s="130"/>
       <c r="P26" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="Q26" s="130"/>
       <c r="R26" s="130"/>
@@ -26289,7 +26297,7 @@
       <c r="AG26" s="2"/>
       <c r="AH26" s="23"/>
     </row>
-    <row r="27" spans="1:34">
+    <row r="27" spans="1:34" hidden="1">
       <c r="A27" t="s">
         <v>113</v>
       </c>
@@ -26335,7 +26343,7 @@
       <c r="O27" s="130"/>
       <c r="P27" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="Q27" s="130"/>
       <c r="R27" s="130"/>
@@ -26357,7 +26365,7 @@
       <c r="AG27" s="2"/>
       <c r="AH27" s="23"/>
     </row>
-    <row r="28" spans="1:34">
+    <row r="28" spans="1:34" hidden="1">
       <c r="A28" s="133" t="s">
         <v>113</v>
       </c>
@@ -26403,7 +26411,7 @@
       <c r="O28" s="130"/>
       <c r="P28" s="7">
         <f t="shared" ref="P28:P35" ca="1" si="18">DAYS360(L28,TODAY())-(1)</f>
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="Q28" s="130"/>
       <c r="R28" s="130"/>
@@ -26425,7 +26433,7 @@
       <c r="AG28" s="2"/>
       <c r="AH28" s="23"/>
     </row>
-    <row r="29" spans="1:34">
+    <row r="29" spans="1:34" hidden="1">
       <c r="A29" s="133" t="s">
         <v>113</v>
       </c>
@@ -26471,7 +26479,7 @@
       <c r="O29" s="130"/>
       <c r="P29" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="Q29" s="130"/>
       <c r="R29" s="130"/>
@@ -26493,7 +26501,7 @@
       <c r="AG29" s="2"/>
       <c r="AH29" s="23"/>
     </row>
-    <row r="30" spans="1:34">
+    <row r="30" spans="1:34" hidden="1">
       <c r="A30" s="133" t="s">
         <v>113</v>
       </c>
@@ -26539,7 +26547,7 @@
       <c r="O30" s="130"/>
       <c r="P30" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q30" s="130"/>
       <c r="R30" s="130"/>
@@ -26561,7 +26569,7 @@
       <c r="AG30" s="2"/>
       <c r="AH30" s="23"/>
     </row>
-    <row r="31" spans="1:34">
+    <row r="31" spans="1:34" hidden="1">
       <c r="A31" s="133" t="s">
         <v>113</v>
       </c>
@@ -26607,7 +26615,7 @@
       <c r="O31" s="130"/>
       <c r="P31" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Q31" s="130"/>
       <c r="R31" s="130"/>
@@ -26629,7 +26637,7 @@
       <c r="AG31" s="2"/>
       <c r="AH31" s="23"/>
     </row>
-    <row r="32" spans="1:34">
+    <row r="32" spans="1:34" hidden="1">
       <c r="A32" s="133" t="s">
         <v>113</v>
       </c>
@@ -26675,7 +26683,7 @@
       <c r="O32" s="130"/>
       <c r="P32" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="Q32" s="130"/>
       <c r="R32" s="130"/>
@@ -26697,7 +26705,7 @@
       <c r="AG32" s="2"/>
       <c r="AH32" s="23"/>
     </row>
-    <row r="33" spans="1:34">
+    <row r="33" spans="1:34" hidden="1">
       <c r="A33" s="133" t="s">
         <v>113</v>
       </c>
@@ -26743,7 +26751,7 @@
       <c r="O33" s="130"/>
       <c r="P33" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Q33" s="130"/>
       <c r="R33" s="130"/>
@@ -26811,7 +26819,7 @@
       <c r="O34" s="130"/>
       <c r="P34" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Q34" s="130"/>
       <c r="R34" s="130"/>
@@ -26879,7 +26887,7 @@
       <c r="O35" s="130"/>
       <c r="P35" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Q35" s="130"/>
       <c r="R35" s="130"/>
@@ -26901,7 +26909,7 @@
       <c r="AG35" s="2"/>
       <c r="AH35" s="23"/>
     </row>
-    <row r="36" spans="1:34">
+    <row r="36" spans="1:34" hidden="1">
       <c r="A36" t="s">
         <v>113</v>
       </c>
@@ -26938,7 +26946,7 @@
       <c r="AG36" s="2"/>
       <c r="AH36" s="23"/>
     </row>
-    <row r="37" spans="1:34">
+    <row r="37" spans="1:34" hidden="1">
       <c r="A37" t="s">
         <v>113</v>
       </c>
@@ -26975,7 +26983,7 @@
       <c r="AG37" s="2"/>
       <c r="AH37" s="23"/>
     </row>
-    <row r="38" spans="1:34">
+    <row r="38" spans="1:34" hidden="1">
       <c r="A38" t="s">
         <v>113</v>
       </c>
@@ -27012,7 +27020,7 @@
       <c r="AG38" s="2"/>
       <c r="AH38" s="23"/>
     </row>
-    <row r="39" spans="1:34">
+    <row r="39" spans="1:34" hidden="1">
       <c r="A39" t="s">
         <v>113</v>
       </c>
@@ -27049,7 +27057,7 @@
       <c r="AG39" s="2"/>
       <c r="AH39" s="23"/>
     </row>
-    <row r="40" spans="1:34">
+    <row r="40" spans="1:34" hidden="1">
       <c r="A40" t="s">
         <v>113</v>
       </c>
@@ -27086,7 +27094,7 @@
       <c r="AG40" s="2"/>
       <c r="AH40" s="23"/>
     </row>
-    <row r="41" spans="1:34">
+    <row r="41" spans="1:34" hidden="1">
       <c r="A41" t="s">
         <v>113</v>
       </c>
@@ -27123,7 +27131,7 @@
       <c r="AG41" s="2"/>
       <c r="AH41" s="23"/>
     </row>
-    <row r="42" spans="1:34">
+    <row r="42" spans="1:34" hidden="1">
       <c r="A42" t="s">
         <v>113</v>
       </c>
@@ -27160,7 +27168,7 @@
       <c r="AG42" s="2"/>
       <c r="AH42" s="23"/>
     </row>
-    <row r="43" spans="1:34">
+    <row r="43" spans="1:34" hidden="1">
       <c r="A43" t="s">
         <v>113</v>
       </c>
@@ -27197,7 +27205,7 @@
       <c r="AG43" s="2"/>
       <c r="AH43" s="23"/>
     </row>
-    <row r="44" spans="1:34">
+    <row r="44" spans="1:34" hidden="1">
       <c r="A44" t="s">
         <v>113</v>
       </c>
@@ -27234,7 +27242,7 @@
       <c r="AG44" s="2"/>
       <c r="AH44" s="23"/>
     </row>
-    <row r="45" spans="1:34">
+    <row r="45" spans="1:34" hidden="1">
       <c r="A45" t="s">
         <v>113</v>
       </c>
@@ -27271,7 +27279,7 @@
       <c r="AG45" s="2"/>
       <c r="AH45" s="23"/>
     </row>
-    <row r="46" spans="1:34">
+    <row r="46" spans="1:34" hidden="1">
       <c r="A46" t="s">
         <v>113</v>
       </c>
@@ -27308,7 +27316,7 @@
       <c r="AG46" s="2"/>
       <c r="AH46" s="23"/>
     </row>
-    <row r="47" spans="1:34" ht="15.75" thickBot="1">
+    <row r="47" spans="1:34" ht="15.75" hidden="1" thickBot="1">
       <c r="A47" t="s">
         <v>113</v>
       </c>
@@ -27345,7 +27353,7 @@
       <c r="AG47" s="30"/>
       <c r="AH47" s="35"/>
     </row>
-    <row r="48" spans="1:34" ht="15.75" thickBot="1">
+    <row r="48" spans="1:34" ht="15.75" hidden="1" thickBot="1">
       <c r="A48" t="s">
         <v>113</v>
       </c>
@@ -27382,7 +27390,7 @@
       <c r="AG48" s="2"/>
       <c r="AH48" s="23"/>
     </row>
-    <row r="49" spans="1:34" ht="15.75" thickBot="1">
+    <row r="49" spans="1:34" ht="15.75" hidden="1" thickBot="1">
       <c r="A49" t="s">
         <v>113</v>
       </c>
@@ -27446,7 +27454,7 @@
       <c r="AG49" s="10"/>
       <c r="AH49" s="17"/>
     </row>
-    <row r="50" spans="1:34">
+    <row r="50" spans="1:34" hidden="1">
       <c r="A50" t="s">
         <v>114</v>
       </c>
@@ -27482,33 +27490,33 @@
       <c r="AG50" s="2"/>
       <c r="AH50" s="1"/>
     </row>
-    <row r="51" spans="1:34">
+    <row r="51" spans="1:34" hidden="1">
       <c r="A51" t="s">
         <v>114</v>
       </c>
-      <c r="B51" s="147" t="s">
+      <c r="B51" s="149" t="s">
         <v>40</v>
       </c>
-      <c r="C51" s="147"/>
+      <c r="C51" s="149"/>
       <c r="H51" s="109"/>
-      <c r="Y51" s="147" t="s">
+      <c r="Y51" s="149" t="s">
         <v>39</v>
       </c>
-      <c r="Z51" s="147"/>
-    </row>
-    <row r="52" spans="1:34" ht="15.75" thickBot="1">
+      <c r="Z51" s="149"/>
+    </row>
+    <row r="52" spans="1:34" ht="15.75" hidden="1" thickBot="1">
       <c r="A52" t="s">
         <v>114</v>
       </c>
-      <c r="B52" s="148" t="s">
+      <c r="B52" s="150" t="s">
         <v>34</v>
       </c>
-      <c r="C52" s="148"/>
+      <c r="C52" s="150"/>
       <c r="H52" s="109"/>
-      <c r="Y52" s="148" t="s">
+      <c r="Y52" s="150" t="s">
         <v>34</v>
       </c>
-      <c r="Z52" s="148"/>
+      <c r="Z52" s="150"/>
       <c r="AA52" s="1"/>
       <c r="AB52" s="2"/>
       <c r="AC52" s="3"/>
@@ -27518,7 +27526,7 @@
       <c r="AG52" s="2"/>
       <c r="AH52" s="1"/>
     </row>
-    <row r="53" spans="1:34" ht="15.75" thickBot="1">
+    <row r="53" spans="1:34" ht="15.75" hidden="1" thickBot="1">
       <c r="A53" t="s">
         <v>114</v>
       </c>
@@ -27613,7 +27621,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:34">
+    <row r="54" spans="1:34" hidden="1">
       <c r="A54" t="s">
         <v>114</v>
       </c>
@@ -27834,7 +27842,7 @@
       <c r="AG56" s="2"/>
       <c r="AH56" s="23"/>
     </row>
-    <row r="57" spans="1:34">
+    <row r="57" spans="1:34" hidden="1">
       <c r="A57" t="s">
         <v>114</v>
       </c>
@@ -27879,8 +27887,8 @@
       </c>
       <c r="O57" s="2"/>
       <c r="P57" s="7">
-        <f t="shared" ref="P55:P79" ca="1" si="25">DAYS360(L57,TODAY())-(1)</f>
-        <v>46</v>
+        <f t="shared" ref="P57:P79" ca="1" si="25">DAYS360(L57,TODAY())-(1)</f>
+        <v>53</v>
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" s="2"/>
@@ -27902,7 +27910,7 @@
       <c r="AG57" s="2"/>
       <c r="AH57" s="23"/>
     </row>
-    <row r="58" spans="1:34">
+    <row r="58" spans="1:34" hidden="1">
       <c r="A58" t="s">
         <v>114</v>
       </c>
@@ -27948,7 +27956,7 @@
       <c r="O58" s="2"/>
       <c r="P58" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" s="2"/>
@@ -27972,7 +27980,7 @@
       <c r="AG58" s="2"/>
       <c r="AH58" s="23"/>
     </row>
-    <row r="59" spans="1:34">
+    <row r="59" spans="1:34" hidden="1">
       <c r="A59" t="s">
         <v>114</v>
       </c>
@@ -28018,7 +28026,7 @@
       <c r="O59" s="2"/>
       <c r="P59" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" s="2"/>
@@ -28040,7 +28048,7 @@
       <c r="AG59" s="2"/>
       <c r="AH59" s="23"/>
     </row>
-    <row r="60" spans="1:34">
+    <row r="60" spans="1:34" hidden="1">
       <c r="A60" t="s">
         <v>114</v>
       </c>
@@ -28086,7 +28094,7 @@
       <c r="O60" s="2"/>
       <c r="P60" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" s="2"/>
@@ -28108,7 +28116,7 @@
       <c r="AG60" s="2"/>
       <c r="AH60" s="23"/>
     </row>
-    <row r="61" spans="1:34">
+    <row r="61" spans="1:34" hidden="1">
       <c r="A61" t="s">
         <v>114</v>
       </c>
@@ -28154,7 +28162,7 @@
       <c r="O61" s="2"/>
       <c r="P61" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="Q61" s="2"/>
       <c r="R61" s="2"/>
@@ -28178,7 +28186,7 @@
       <c r="AG61" s="2"/>
       <c r="AH61" s="23"/>
     </row>
-    <row r="62" spans="1:34">
+    <row r="62" spans="1:34" hidden="1">
       <c r="A62" t="s">
         <v>114</v>
       </c>
@@ -28224,7 +28232,7 @@
       <c r="O62" s="2"/>
       <c r="P62" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" s="2"/>
@@ -28248,7 +28256,7 @@
       <c r="AG62" s="2"/>
       <c r="AH62" s="23"/>
     </row>
-    <row r="63" spans="1:34">
+    <row r="63" spans="1:34" hidden="1">
       <c r="A63" t="s">
         <v>114</v>
       </c>
@@ -28294,7 +28302,7 @@
       <c r="O63" s="2"/>
       <c r="P63" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Q63" s="2"/>
       <c r="R63" s="2"/>
@@ -28316,7 +28324,7 @@
       <c r="AG63" s="2"/>
       <c r="AH63" s="23"/>
     </row>
-    <row r="64" spans="1:34">
+    <row r="64" spans="1:34" hidden="1">
       <c r="A64" t="s">
         <v>114</v>
       </c>
@@ -28386,7 +28394,7 @@
       <c r="AG64" s="2"/>
       <c r="AH64" s="23"/>
     </row>
-    <row r="65" spans="1:34">
+    <row r="65" spans="1:34" hidden="1">
       <c r="A65" t="s">
         <v>114</v>
       </c>
@@ -28432,7 +28440,7 @@
       <c r="O65" s="2"/>
       <c r="P65" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" s="2"/>
@@ -28454,7 +28462,7 @@
       <c r="AG65" s="2"/>
       <c r="AH65" s="23"/>
     </row>
-    <row r="66" spans="1:34">
+    <row r="66" spans="1:34" hidden="1">
       <c r="A66" t="s">
         <v>114</v>
       </c>
@@ -28524,7 +28532,7 @@
       <c r="AG66" s="2"/>
       <c r="AH66" s="23"/>
     </row>
-    <row r="67" spans="1:34">
+    <row r="67" spans="1:34" hidden="1">
       <c r="A67" t="s">
         <v>114</v>
       </c>
@@ -28570,7 +28578,7 @@
       <c r="O67" s="2"/>
       <c r="P67" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" s="2"/>
@@ -28638,7 +28646,7 @@
       <c r="O68" s="2"/>
       <c r="P68" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="Q68" s="2"/>
       <c r="R68" s="2"/>
@@ -28660,7 +28668,7 @@
       <c r="AG68" s="2"/>
       <c r="AH68" s="23"/>
     </row>
-    <row r="69" spans="1:34">
+    <row r="69" spans="1:34" hidden="1">
       <c r="A69" t="s">
         <v>114</v>
       </c>
@@ -28706,7 +28714,7 @@
       <c r="O69" s="2"/>
       <c r="P69" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" s="2"/>
@@ -28728,7 +28736,7 @@
       <c r="AG69" s="2"/>
       <c r="AH69" s="23"/>
     </row>
-    <row r="70" spans="1:34">
+    <row r="70" spans="1:34" hidden="1">
       <c r="A70" t="s">
         <v>114</v>
       </c>
@@ -28774,7 +28782,7 @@
       <c r="O70" s="2"/>
       <c r="P70" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" s="2"/>
@@ -28796,7 +28804,7 @@
       <c r="AG70" s="2"/>
       <c r="AH70" s="23"/>
     </row>
-    <row r="71" spans="1:34">
+    <row r="71" spans="1:34" hidden="1">
       <c r="A71" t="s">
         <v>114</v>
       </c>
@@ -28842,7 +28850,7 @@
       <c r="O71" s="2"/>
       <c r="P71" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" s="2"/>
@@ -28910,7 +28918,7 @@
       <c r="O72" s="2"/>
       <c r="P72" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="Q72" s="2"/>
       <c r="R72" s="2"/>
@@ -28932,7 +28940,7 @@
       <c r="AG72" s="2"/>
       <c r="AH72" s="23"/>
     </row>
-    <row r="73" spans="1:34">
+    <row r="73" spans="1:34" hidden="1">
       <c r="A73" t="s">
         <v>114</v>
       </c>
@@ -28978,7 +28986,7 @@
       <c r="O73" s="2"/>
       <c r="P73" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="Q73" s="2"/>
       <c r="R73" s="2"/>
@@ -29000,7 +29008,7 @@
       <c r="AG73" s="2"/>
       <c r="AH73" s="23"/>
     </row>
-    <row r="74" spans="1:34">
+    <row r="74" spans="1:34" hidden="1">
       <c r="A74" t="s">
         <v>114</v>
       </c>
@@ -29046,7 +29054,7 @@
       <c r="O74" s="130"/>
       <c r="P74" s="131">
         <f t="shared" ca="1" si="25"/>
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="Q74" s="130"/>
       <c r="R74" s="130"/>
@@ -29068,7 +29076,7 @@
       <c r="AG74" s="2"/>
       <c r="AH74" s="23"/>
     </row>
-    <row r="75" spans="1:34">
+    <row r="75" spans="1:34" hidden="1">
       <c r="A75" t="s">
         <v>114</v>
       </c>
@@ -29114,7 +29122,7 @@
       <c r="O75" s="130"/>
       <c r="P75" s="131">
         <f t="shared" ca="1" si="25"/>
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="Q75" s="130"/>
       <c r="R75" s="130"/>
@@ -29136,7 +29144,7 @@
       <c r="AG75" s="2"/>
       <c r="AH75" s="23"/>
     </row>
-    <row r="76" spans="1:34">
+    <row r="76" spans="1:34" hidden="1">
       <c r="A76" t="s">
         <v>114</v>
       </c>
@@ -29182,7 +29190,7 @@
       <c r="O76" s="130"/>
       <c r="P76" s="131">
         <f t="shared" ca="1" si="25"/>
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="Q76" s="130"/>
       <c r="R76" s="130"/>
@@ -29204,7 +29212,7 @@
       <c r="AG76" s="2"/>
       <c r="AH76" s="23"/>
     </row>
-    <row r="77" spans="1:34">
+    <row r="77" spans="1:34" hidden="1">
       <c r="A77" t="s">
         <v>114</v>
       </c>
@@ -29250,7 +29258,7 @@
       <c r="O77" s="130"/>
       <c r="P77" s="131">
         <f t="shared" ca="1" si="25"/>
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Q77" s="130"/>
       <c r="R77" s="130"/>
@@ -29272,7 +29280,7 @@
       <c r="AG77" s="2"/>
       <c r="AH77" s="23"/>
     </row>
-    <row r="78" spans="1:34">
+    <row r="78" spans="1:34" hidden="1">
       <c r="A78" t="s">
         <v>114</v>
       </c>
@@ -29318,7 +29326,7 @@
       <c r="O78" s="130"/>
       <c r="P78" s="131">
         <f t="shared" ca="1" si="25"/>
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="Q78" s="130"/>
       <c r="R78" s="130"/>
@@ -29340,7 +29348,7 @@
       <c r="AG78" s="2"/>
       <c r="AH78" s="23"/>
     </row>
-    <row r="79" spans="1:34" s="133" customFormat="1">
+    <row r="79" spans="1:34" s="133" customFormat="1" hidden="1">
       <c r="A79" s="133" t="s">
         <v>114</v>
       </c>
@@ -29386,7 +29394,7 @@
       <c r="O79" s="130"/>
       <c r="P79" s="131">
         <f t="shared" ca="1" si="25"/>
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="Q79" s="130"/>
       <c r="R79" s="130"/>
@@ -29408,7 +29416,7 @@
       <c r="AG79" s="130"/>
       <c r="AH79" s="139"/>
     </row>
-    <row r="80" spans="1:34" s="133" customFormat="1">
+    <row r="80" spans="1:34" s="133" customFormat="1" hidden="1">
       <c r="A80" s="133" t="s">
         <v>114</v>
       </c>
@@ -29444,12 +29452,12 @@
         <f t="shared" ref="L80:L87" si="38">D80+18</f>
         <v>46178</v>
       </c>
-      <c r="M80" s="128">
+      <c r="M80" s="121">
         <f t="shared" ref="M80:M87" si="39">H80*K80</f>
         <v>154332.23232000001</v>
       </c>
-      <c r="N80" s="135">
-        <v>154338</v>
+      <c r="N80" s="148" t="s">
+        <v>99</v>
       </c>
       <c r="O80" s="130"/>
       <c r="P80" s="131"/>
@@ -29461,7 +29469,9 @@
       <c r="T80" s="130"/>
       <c r="U80" s="130"/>
       <c r="V80" s="130"/>
-      <c r="W80" s="139"/>
+      <c r="W80" s="139">
+        <v>46196</v>
+      </c>
       <c r="Y80" s="134"/>
       <c r="Z80" s="127"/>
       <c r="AA80" s="127"/>
@@ -29473,7 +29483,7 @@
       <c r="AG80" s="130"/>
       <c r="AH80" s="139"/>
     </row>
-    <row r="81" spans="1:34" s="133" customFormat="1">
+    <row r="81" spans="1:34" s="133" customFormat="1" hidden="1">
       <c r="A81" s="133" t="s">
         <v>114</v>
       </c>
@@ -29538,7 +29548,7 @@
       <c r="AG81" s="130"/>
       <c r="AH81" s="139"/>
     </row>
-    <row r="82" spans="1:34" s="133" customFormat="1">
+    <row r="82" spans="1:34" s="133" customFormat="1" hidden="1">
       <c r="A82" s="133" t="s">
         <v>114</v>
       </c>
@@ -29574,12 +29584,12 @@
         <f t="shared" si="38"/>
         <v>46185</v>
       </c>
-      <c r="M82" s="128">
+      <c r="M82" s="121">
         <f t="shared" si="39"/>
         <v>162151.8192</v>
       </c>
-      <c r="N82" s="135">
-        <v>162152</v>
+      <c r="N82" s="148" t="s">
+        <v>99</v>
       </c>
       <c r="O82" s="130"/>
       <c r="P82" s="131"/>
@@ -29591,7 +29601,9 @@
       <c r="T82" s="130"/>
       <c r="U82" s="130"/>
       <c r="V82" s="130"/>
-      <c r="W82" s="139"/>
+      <c r="W82" s="139">
+        <v>46196</v>
+      </c>
       <c r="Y82" s="134"/>
       <c r="Z82" s="127"/>
       <c r="AA82" s="127"/>
@@ -29603,7 +29615,7 @@
       <c r="AG82" s="130"/>
       <c r="AH82" s="139"/>
     </row>
-    <row r="83" spans="1:34" s="133" customFormat="1">
+    <row r="83" spans="1:34" s="133" customFormat="1" hidden="1">
       <c r="A83" s="133" t="s">
         <v>114</v>
       </c>
@@ -29670,7 +29682,7 @@
       <c r="AG83" s="130"/>
       <c r="AH83" s="139"/>
     </row>
-    <row r="84" spans="1:34" s="133" customFormat="1">
+    <row r="84" spans="1:34" s="133" customFormat="1" hidden="1">
       <c r="A84" s="133" t="s">
         <v>114</v>
       </c>
@@ -29737,7 +29749,7 @@
       <c r="AG84" s="130"/>
       <c r="AH84" s="139"/>
     </row>
-    <row r="85" spans="1:34" s="133" customFormat="1">
+    <row r="85" spans="1:34" s="133" customFormat="1" hidden="1">
       <c r="A85" s="133" t="s">
         <v>114</v>
       </c>
@@ -29804,7 +29816,7 @@
       <c r="AG85" s="130"/>
       <c r="AH85" s="139"/>
     </row>
-    <row r="86" spans="1:34" s="133" customFormat="1">
+    <row r="86" spans="1:34" s="133" customFormat="1" hidden="1">
       <c r="A86" s="133" t="s">
         <v>114</v>
       </c>
@@ -29934,7 +29946,7 @@
       <c r="AG87" s="130"/>
       <c r="AH87" s="139"/>
     </row>
-    <row r="88" spans="1:34">
+    <row r="88" spans="1:34" hidden="1">
       <c r="A88" t="s">
         <v>114</v>
       </c>
@@ -29971,7 +29983,7 @@
       <c r="AG88" s="2"/>
       <c r="AH88" s="23"/>
     </row>
-    <row r="89" spans="1:34">
+    <row r="89" spans="1:34" hidden="1">
       <c r="A89" t="s">
         <v>114</v>
       </c>
@@ -30008,7 +30020,7 @@
       <c r="AG89" s="2"/>
       <c r="AH89" s="23"/>
     </row>
-    <row r="90" spans="1:34">
+    <row r="90" spans="1:34" hidden="1">
       <c r="A90" t="s">
         <v>114</v>
       </c>
@@ -30045,7 +30057,7 @@
       <c r="AG90" s="2"/>
       <c r="AH90" s="23"/>
     </row>
-    <row r="91" spans="1:34">
+    <row r="91" spans="1:34" hidden="1">
       <c r="A91" t="s">
         <v>114</v>
       </c>
@@ -30082,7 +30094,7 @@
       <c r="AG91" s="2"/>
       <c r="AH91" s="23"/>
     </row>
-    <row r="92" spans="1:34">
+    <row r="92" spans="1:34" hidden="1">
       <c r="A92" t="s">
         <v>114</v>
       </c>
@@ -30119,7 +30131,7 @@
       <c r="AG92" s="2"/>
       <c r="AH92" s="23"/>
     </row>
-    <row r="93" spans="1:34">
+    <row r="93" spans="1:34" hidden="1">
       <c r="A93" t="s">
         <v>114</v>
       </c>
@@ -30156,7 +30168,7 @@
       <c r="AG93" s="2"/>
       <c r="AH93" s="23"/>
     </row>
-    <row r="94" spans="1:34">
+    <row r="94" spans="1:34" hidden="1">
       <c r="A94" t="s">
         <v>114</v>
       </c>
@@ -30193,7 +30205,7 @@
       <c r="AG94" s="2"/>
       <c r="AH94" s="23"/>
     </row>
-    <row r="95" spans="1:34">
+    <row r="95" spans="1:34" hidden="1">
       <c r="A95" t="s">
         <v>114</v>
       </c>
@@ -30230,7 +30242,7 @@
       <c r="AG95" s="2"/>
       <c r="AH95" s="23"/>
     </row>
-    <row r="96" spans="1:34">
+    <row r="96" spans="1:34" hidden="1">
       <c r="A96" t="s">
         <v>114</v>
       </c>
@@ -30267,7 +30279,7 @@
       <c r="AG96" s="2"/>
       <c r="AH96" s="23"/>
     </row>
-    <row r="97" spans="1:34">
+    <row r="97" spans="1:34" hidden="1">
       <c r="A97" t="s">
         <v>114</v>
       </c>
@@ -30304,7 +30316,7 @@
       <c r="AG97" s="2"/>
       <c r="AH97" s="23"/>
     </row>
-    <row r="98" spans="1:34">
+    <row r="98" spans="1:34" hidden="1">
       <c r="A98" t="s">
         <v>114</v>
       </c>
@@ -30341,7 +30353,7 @@
       <c r="AG98" s="2"/>
       <c r="AH98" s="23"/>
     </row>
-    <row r="99" spans="1:34">
+    <row r="99" spans="1:34" hidden="1">
       <c r="A99" t="s">
         <v>114</v>
       </c>
@@ -30378,7 +30390,7 @@
       <c r="AG99" s="2"/>
       <c r="AH99" s="23"/>
     </row>
-    <row r="100" spans="1:34">
+    <row r="100" spans="1:34" hidden="1">
       <c r="A100" t="s">
         <v>114</v>
       </c>
@@ -30415,7 +30427,7 @@
       <c r="AG100" s="2"/>
       <c r="AH100" s="23"/>
     </row>
-    <row r="101" spans="1:34">
+    <row r="101" spans="1:34" hidden="1">
       <c r="A101" t="s">
         <v>114</v>
       </c>
@@ -30452,7 +30464,7 @@
       <c r="AG101" s="2"/>
       <c r="AH101" s="23"/>
     </row>
-    <row r="102" spans="1:34">
+    <row r="102" spans="1:34" hidden="1">
       <c r="A102" t="s">
         <v>114</v>
       </c>
@@ -30489,7 +30501,7 @@
       <c r="AG102" s="2"/>
       <c r="AH102" s="23"/>
     </row>
-    <row r="103" spans="1:34">
+    <row r="103" spans="1:34" hidden="1">
       <c r="A103" t="s">
         <v>114</v>
       </c>
@@ -30526,7 +30538,7 @@
       <c r="AG103" s="2"/>
       <c r="AH103" s="23"/>
     </row>
-    <row r="104" spans="1:34">
+    <row r="104" spans="1:34" hidden="1">
       <c r="A104" t="s">
         <v>114</v>
       </c>
@@ -30563,7 +30575,7 @@
       <c r="AG104" s="2"/>
       <c r="AH104" s="23"/>
     </row>
-    <row r="105" spans="1:34">
+    <row r="105" spans="1:34" hidden="1">
       <c r="A105" t="s">
         <v>114</v>
       </c>
@@ -30600,7 +30612,7 @@
       <c r="AG105" s="2"/>
       <c r="AH105" s="23"/>
     </row>
-    <row r="106" spans="1:34">
+    <row r="106" spans="1:34" hidden="1">
       <c r="A106" t="s">
         <v>114</v>
       </c>
@@ -30637,7 +30649,7 @@
       <c r="AG106" s="2"/>
       <c r="AH106" s="23"/>
     </row>
-    <row r="107" spans="1:34">
+    <row r="107" spans="1:34" hidden="1">
       <c r="A107" t="s">
         <v>114</v>
       </c>
@@ -30674,7 +30686,7 @@
       <c r="AG107" s="2"/>
       <c r="AH107" s="23"/>
     </row>
-    <row r="108" spans="1:34">
+    <row r="108" spans="1:34" hidden="1">
       <c r="A108" t="s">
         <v>114</v>
       </c>
@@ -30711,7 +30723,7 @@
       <c r="AG108" s="2"/>
       <c r="AH108" s="23"/>
     </row>
-    <row r="109" spans="1:34">
+    <row r="109" spans="1:34" hidden="1">
       <c r="A109" t="s">
         <v>114</v>
       </c>
@@ -30748,7 +30760,7 @@
       <c r="AG109" s="2"/>
       <c r="AH109" s="23"/>
     </row>
-    <row r="110" spans="1:34">
+    <row r="110" spans="1:34" hidden="1">
       <c r="A110" t="s">
         <v>114</v>
       </c>
@@ -30785,7 +30797,7 @@
       <c r="AG110" s="2"/>
       <c r="AH110" s="23"/>
     </row>
-    <row r="111" spans="1:34">
+    <row r="111" spans="1:34" hidden="1">
       <c r="A111" t="s">
         <v>114</v>
       </c>
@@ -30822,7 +30834,7 @@
       <c r="AG111" s="2"/>
       <c r="AH111" s="23"/>
     </row>
-    <row r="112" spans="1:34">
+    <row r="112" spans="1:34" hidden="1">
       <c r="A112" t="s">
         <v>114</v>
       </c>
@@ -30859,7 +30871,7 @@
       <c r="AG112" s="2"/>
       <c r="AH112" s="23"/>
     </row>
-    <row r="113" spans="1:34">
+    <row r="113" spans="1:34" hidden="1">
       <c r="A113" t="s">
         <v>114</v>
       </c>
@@ -30896,7 +30908,7 @@
       <c r="AG113" s="2"/>
       <c r="AH113" s="23"/>
     </row>
-    <row r="114" spans="1:34">
+    <row r="114" spans="1:34" hidden="1">
       <c r="A114" t="s">
         <v>114</v>
       </c>
@@ -30933,7 +30945,7 @@
       <c r="AG114" s="2"/>
       <c r="AH114" s="23"/>
     </row>
-    <row r="115" spans="1:34">
+    <row r="115" spans="1:34" hidden="1">
       <c r="A115" t="s">
         <v>114</v>
       </c>
@@ -30970,7 +30982,7 @@
       <c r="AG115" s="2"/>
       <c r="AH115" s="23"/>
     </row>
-    <row r="116" spans="1:34" ht="15.75" thickBot="1">
+    <row r="116" spans="1:34" ht="15.75" hidden="1" thickBot="1">
       <c r="A116" t="s">
         <v>114</v>
       </c>
@@ -31007,7 +31019,7 @@
       <c r="AG116" s="30"/>
       <c r="AH116" s="35"/>
     </row>
-    <row r="117" spans="1:34" ht="15.75" thickBot="1">
+    <row r="117" spans="1:34" ht="15.75" hidden="1" thickBot="1">
       <c r="A117" t="s">
         <v>114</v>
       </c>
@@ -31044,7 +31056,7 @@
       <c r="AG117" s="2"/>
       <c r="AH117" s="23"/>
     </row>
-    <row r="118" spans="1:34" ht="15.75" thickBot="1">
+    <row r="118" spans="1:34" ht="15.75" hidden="1" thickBot="1">
       <c r="A118" t="s">
         <v>114</v>
       </c>
@@ -31074,7 +31086,7 @@
       </c>
       <c r="N118" s="38">
         <f>SUM(N54:N117)</f>
-        <v>4223050</v>
+        <v>3906560</v>
       </c>
       <c r="O118" s="10"/>
       <c r="P118" s="39"/>
@@ -31108,7 +31120,7 @@
       <c r="AG118" s="10"/>
       <c r="AH118" s="17"/>
     </row>
-    <row r="119" spans="1:34">
+    <row r="119" spans="1:34" hidden="1">
       <c r="A119" t="s">
         <v>56</v>
       </c>
@@ -31117,33 +31129,33 @@
         <v>34014.763000000006</v>
       </c>
     </row>
-    <row r="120" spans="1:34">
+    <row r="120" spans="1:34" hidden="1">
       <c r="A120" t="s">
         <v>56</v>
       </c>
-      <c r="B120" s="147" t="s">
+      <c r="B120" s="149" t="s">
         <v>109</v>
       </c>
-      <c r="C120" s="147"/>
+      <c r="C120" s="149"/>
       <c r="H120" s="109"/>
-      <c r="Y120" s="147" t="s">
+      <c r="Y120" s="149" t="s">
         <v>39</v>
       </c>
-      <c r="Z120" s="147"/>
-    </row>
-    <row r="121" spans="1:34" ht="15.75" thickBot="1">
+      <c r="Z120" s="149"/>
+    </row>
+    <row r="121" spans="1:34" ht="15.75" hidden="1" thickBot="1">
       <c r="A121" t="s">
         <v>56</v>
       </c>
-      <c r="B121" s="148" t="s">
+      <c r="B121" s="150" t="s">
         <v>108</v>
       </c>
-      <c r="C121" s="148"/>
+      <c r="C121" s="150"/>
       <c r="H121" s="109"/>
-      <c r="Y121" s="148" t="s">
+      <c r="Y121" s="150" t="s">
         <v>34</v>
       </c>
-      <c r="Z121" s="148"/>
+      <c r="Z121" s="150"/>
       <c r="AA121" s="1"/>
       <c r="AB121" s="2"/>
       <c r="AC121" s="3"/>
@@ -31153,7 +31165,7 @@
       <c r="AG121" s="2"/>
       <c r="AH121" s="1"/>
     </row>
-    <row r="122" spans="1:34" ht="15.75" thickBot="1">
+    <row r="122" spans="1:34" ht="15.75" hidden="1" thickBot="1">
       <c r="A122" t="s">
         <v>56</v>
       </c>
@@ -31248,7 +31260,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="123" spans="1:34">
+    <row r="123" spans="1:34" hidden="1">
       <c r="A123" t="s">
         <v>56</v>
       </c>
@@ -31301,7 +31313,7 @@
       <c r="AG123" s="2"/>
       <c r="AH123" s="23"/>
     </row>
-    <row r="124" spans="1:34">
+    <row r="124" spans="1:34" hidden="1">
       <c r="A124" t="s">
         <v>56</v>
       </c>
@@ -31338,7 +31350,7 @@
       <c r="AG124" s="2"/>
       <c r="AH124" s="23"/>
     </row>
-    <row r="125" spans="1:34">
+    <row r="125" spans="1:34" hidden="1">
       <c r="A125" t="s">
         <v>56</v>
       </c>
@@ -31375,7 +31387,7 @@
       <c r="AG125" s="2"/>
       <c r="AH125" s="23"/>
     </row>
-    <row r="126" spans="1:34">
+    <row r="126" spans="1:34" hidden="1">
       <c r="A126" t="s">
         <v>56</v>
       </c>
@@ -31412,7 +31424,7 @@
       <c r="AG126" s="2"/>
       <c r="AH126" s="23"/>
     </row>
-    <row r="127" spans="1:34">
+    <row r="127" spans="1:34" hidden="1">
       <c r="A127" t="s">
         <v>56</v>
       </c>
@@ -31449,7 +31461,7 @@
       <c r="AG127" s="2"/>
       <c r="AH127" s="23"/>
     </row>
-    <row r="128" spans="1:34">
+    <row r="128" spans="1:34" hidden="1">
       <c r="A128" t="s">
         <v>56</v>
       </c>
@@ -31486,7 +31498,7 @@
       <c r="AG128" s="2"/>
       <c r="AH128" s="23"/>
     </row>
-    <row r="129" spans="1:34">
+    <row r="129" spans="1:34" hidden="1">
       <c r="A129" t="s">
         <v>56</v>
       </c>
@@ -31523,7 +31535,7 @@
       <c r="AG129" s="2"/>
       <c r="AH129" s="23"/>
     </row>
-    <row r="130" spans="1:34" ht="15.75" thickBot="1">
+    <row r="130" spans="1:34" ht="15.75" hidden="1" thickBot="1">
       <c r="A130" t="s">
         <v>56</v>
       </c>
@@ -31560,7 +31572,7 @@
       <c r="AG130" s="30"/>
       <c r="AH130" s="35"/>
     </row>
-    <row r="131" spans="1:34" ht="15.75" thickBot="1">
+    <row r="131" spans="1:34" ht="15.75" hidden="1" thickBot="1">
       <c r="A131" t="s">
         <v>56</v>
       </c>
@@ -31597,7 +31609,7 @@
       <c r="AG131" s="2"/>
       <c r="AH131" s="23"/>
     </row>
-    <row r="132" spans="1:34" ht="15.75" thickBot="1">
+    <row r="132" spans="1:34" ht="15.75" hidden="1" thickBot="1">
       <c r="A132" t="s">
         <v>56</v>
       </c>
@@ -31674,15 +31686,15 @@
       <c r="G135" s="68"/>
       <c r="H135" s="12">
         <f>SUBTOTAL(9,H5:H48)+SUBTOTAL(9,H54:H117)+SUBTOTAL(9,H123:H130)</f>
-        <v>34014.763000000006</v>
+        <v>5607.83</v>
       </c>
       <c r="I135" s="12">
         <f>J135/H135</f>
-        <v>271.82960129644289</v>
+        <v>271.16253449337802</v>
       </c>
       <c r="J135" s="12">
         <f>SUBTOTAL(9,J5:J48)+SUBTOTAL(9,J54:J117)+SUBTOTAL(9,J123:J130)</f>
-        <v>9246219.4644829985</v>
+        <v>1520633.3958080001</v>
       </c>
       <c r="K135" s="68"/>
       <c r="L135" s="68"/>
@@ -31704,7 +31716,11 @@
   </sheetData>
   <autoFilter ref="A2:AH132">
     <filterColumn colId="1" showButton="0"/>
-    <filterColumn colId="4"/>
+    <filterColumn colId="4">
+      <filters>
+        <filter val="SHREE RAM YARN TRADING CO."/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="6"/>
     <filterColumn colId="24" showButton="0"/>
   </autoFilter>
@@ -31734,4 +31750,1727 @@
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B12:W48"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="8.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" customWidth="1"/>
+    <col min="5" max="5" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.85546875" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="2.7109375" customWidth="1"/>
+    <col min="16" max="16" width="13" customWidth="1"/>
+    <col min="17" max="17" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="12" spans="2:23">
+      <c r="B12" s="18">
+        <v>72</v>
+      </c>
+      <c r="C12" s="1">
+        <v>45993</v>
+      </c>
+      <c r="D12" s="1">
+        <v>45993</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="147" t="s">
+        <v>167</v>
+      </c>
+      <c r="H12" s="3">
+        <v>750</v>
+      </c>
+      <c r="I12" s="4">
+        <v>264.76190000000003</v>
+      </c>
+      <c r="J12" s="4">
+        <v>198571.42500000002</v>
+      </c>
+      <c r="K12" s="4">
+        <v>277.99999500000001</v>
+      </c>
+      <c r="L12" s="1">
+        <v>46009</v>
+      </c>
+      <c r="M12" s="21">
+        <v>208499.99625</v>
+      </c>
+      <c r="N12" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="O12" s="2"/>
+      <c r="P12" s="7">
+        <v>-17</v>
+      </c>
+      <c r="Q12" s="66">
+        <v>-1747.97257130137</v>
+      </c>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2">
+        <v>22817</v>
+      </c>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2"/>
+      <c r="W12" s="23">
+        <v>45993</v>
+      </c>
+    </row>
+    <row r="13" spans="2:23">
+      <c r="B13" s="18">
+        <v>73</v>
+      </c>
+      <c r="C13" s="1">
+        <v>45993</v>
+      </c>
+      <c r="D13" s="1">
+        <v>45993</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="147" t="s">
+        <v>167</v>
+      </c>
+      <c r="H13" s="3">
+        <v>248.01</v>
+      </c>
+      <c r="I13" s="4">
+        <v>264.76190000000003</v>
+      </c>
+      <c r="J13" s="4">
+        <v>65663.598819000006</v>
+      </c>
+      <c r="K13" s="4">
+        <v>277.99999500000001</v>
+      </c>
+      <c r="L13" s="1">
+        <v>46009</v>
+      </c>
+      <c r="M13" s="21">
+        <v>68946.778759950001</v>
+      </c>
+      <c r="N13" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="O13" s="2"/>
+      <c r="P13" s="7">
+        <v>-17</v>
+      </c>
+      <c r="Q13" s="66">
+        <v>-578.01956987793699</v>
+      </c>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2">
+        <v>22818</v>
+      </c>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
+      <c r="V13" s="2"/>
+      <c r="W13" s="23">
+        <v>45993</v>
+      </c>
+    </row>
+    <row r="14" spans="2:23">
+      <c r="B14" s="18">
+        <v>86</v>
+      </c>
+      <c r="C14" s="1">
+        <v>46027</v>
+      </c>
+      <c r="D14" s="1">
+        <v>46027</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" s="147" t="s">
+        <v>167</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1010.5</v>
+      </c>
+      <c r="I14" s="4">
+        <v>264.76190000000003</v>
+      </c>
+      <c r="J14" s="4">
+        <v>267541.89995000005</v>
+      </c>
+      <c r="K14" s="4">
+        <v>277.99999500000001</v>
+      </c>
+      <c r="L14" s="1">
+        <v>46043</v>
+      </c>
+      <c r="M14" s="21">
+        <v>280918.9949475</v>
+      </c>
+      <c r="N14" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="O14" s="2"/>
+      <c r="P14" s="7">
+        <v>27</v>
+      </c>
+      <c r="Q14" s="66">
+        <v>3740.4556587530133</v>
+      </c>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2">
+        <v>25905</v>
+      </c>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2"/>
+      <c r="W14" s="23">
+        <v>46072</v>
+      </c>
+    </row>
+    <row r="15" spans="2:23">
+      <c r="B15" s="18">
+        <v>87</v>
+      </c>
+      <c r="C15" s="1">
+        <v>46029</v>
+      </c>
+      <c r="D15" s="1">
+        <v>46029</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="19"/>
+      <c r="G15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H15" s="3">
+        <v>307.60000000000002</v>
+      </c>
+      <c r="I15" s="4">
+        <v>122</v>
+      </c>
+      <c r="J15" s="4">
+        <v>37527.200000000004</v>
+      </c>
+      <c r="K15" s="4">
+        <v>128.1</v>
+      </c>
+      <c r="L15" s="1">
+        <v>46045</v>
+      </c>
+      <c r="M15" s="21">
+        <v>39403.56</v>
+      </c>
+      <c r="N15" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="O15" s="2"/>
+      <c r="P15" s="7">
+        <v>42</v>
+      </c>
+      <c r="Q15" s="66">
+        <v>816.13948931506843</v>
+      </c>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2">
+        <v>26089</v>
+      </c>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="23">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="16" spans="2:23">
+      <c r="B16" s="18">
+        <v>91</v>
+      </c>
+      <c r="C16" s="1">
+        <v>46038</v>
+      </c>
+      <c r="D16" s="1">
+        <v>46038</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="19"/>
+      <c r="G16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" s="3">
+        <v>300</v>
+      </c>
+      <c r="I16" s="4">
+        <v>302</v>
+      </c>
+      <c r="J16" s="4">
+        <v>90600</v>
+      </c>
+      <c r="K16" s="4">
+        <v>317.10000000000002</v>
+      </c>
+      <c r="L16" s="1">
+        <v>46054</v>
+      </c>
+      <c r="M16" s="21">
+        <v>95130</v>
+      </c>
+      <c r="N16" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="O16" s="2"/>
+      <c r="P16" s="7">
+        <v>34</v>
+      </c>
+      <c r="Q16" s="66">
+        <v>1595.0564383561643</v>
+      </c>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2">
+        <v>26998</v>
+      </c>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
+      <c r="W16" s="23">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="17" spans="2:23">
+      <c r="B17" s="18">
+        <v>92</v>
+      </c>
+      <c r="C17" s="1">
+        <v>46033</v>
+      </c>
+      <c r="D17" s="1">
+        <v>46039</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="19"/>
+      <c r="G17" s="147" t="s">
+        <v>167</v>
+      </c>
+      <c r="H17" s="3">
+        <v>189.4</v>
+      </c>
+      <c r="I17" s="4">
+        <v>264.76190000000003</v>
+      </c>
+      <c r="J17" s="4">
+        <v>50145.903860000006</v>
+      </c>
+      <c r="K17" s="4">
+        <v>277.99999500000001</v>
+      </c>
+      <c r="L17" s="1">
+        <v>46055</v>
+      </c>
+      <c r="M17" s="21">
+        <v>52653.199053000004</v>
+      </c>
+      <c r="N17" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="O17" s="2"/>
+      <c r="P17" s="7">
+        <v>33</v>
+      </c>
+      <c r="Q17" s="66">
+        <v>856.87671883512326</v>
+      </c>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2">
+        <v>27136</v>
+      </c>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
+      <c r="W17" s="23">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="18" spans="2:23">
+      <c r="B18" s="18">
+        <v>93</v>
+      </c>
+      <c r="C18" s="1">
+        <v>46033</v>
+      </c>
+      <c r="D18" s="1">
+        <v>46039</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" s="19"/>
+      <c r="G18" s="147" t="s">
+        <v>167</v>
+      </c>
+      <c r="H18" s="3">
+        <v>790.2</v>
+      </c>
+      <c r="I18" s="4">
+        <v>264.76190000000003</v>
+      </c>
+      <c r="J18" s="4">
+        <v>209214.85338000004</v>
+      </c>
+      <c r="K18" s="4">
+        <v>277.99999500000001</v>
+      </c>
+      <c r="L18" s="1">
+        <v>46055</v>
+      </c>
+      <c r="M18" s="21">
+        <v>219675.59604900001</v>
+      </c>
+      <c r="N18" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="O18" s="2"/>
+      <c r="P18" s="7">
+        <v>33</v>
+      </c>
+      <c r="Q18" s="66">
+        <v>3574.9946315919451</v>
+      </c>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2">
+        <v>27137</v>
+      </c>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+      <c r="W18" s="23">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="19" spans="2:23">
+      <c r="B19" s="18">
+        <v>96</v>
+      </c>
+      <c r="C19" s="1">
+        <v>46048</v>
+      </c>
+      <c r="D19" s="1">
+        <v>46048</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" s="19"/>
+      <c r="G19" s="147" t="s">
+        <v>167</v>
+      </c>
+      <c r="H19" s="3">
+        <v>505.4</v>
+      </c>
+      <c r="I19" s="4">
+        <v>285.70999999999998</v>
+      </c>
+      <c r="J19" s="4">
+        <v>144397.83399999997</v>
+      </c>
+      <c r="K19" s="4">
+        <v>299.99549999999999</v>
+      </c>
+      <c r="L19" s="1">
+        <v>46064</v>
+      </c>
+      <c r="M19" s="21">
+        <v>151617.72569999998</v>
+      </c>
+      <c r="N19" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="O19" s="2"/>
+      <c r="P19" s="7">
+        <v>32</v>
+      </c>
+      <c r="Q19" s="66">
+        <v>2392.6523288547942</v>
+      </c>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2">
+        <v>28149</v>
+      </c>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="23">
+        <v>46095</v>
+      </c>
+    </row>
+    <row r="20" spans="2:23">
+      <c r="B20" s="18">
+        <v>97</v>
+      </c>
+      <c r="C20" s="1">
+        <v>46051</v>
+      </c>
+      <c r="D20" s="1">
+        <v>46051</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" s="19"/>
+      <c r="G20" s="147" t="s">
+        <v>167</v>
+      </c>
+      <c r="H20" s="3">
+        <v>506.07</v>
+      </c>
+      <c r="I20" s="4">
+        <v>285.70999999999998</v>
+      </c>
+      <c r="J20" s="4">
+        <v>144589.2597</v>
+      </c>
+      <c r="K20" s="4">
+        <v>299.99549999999999</v>
+      </c>
+      <c r="L20" s="1">
+        <v>46067</v>
+      </c>
+      <c r="M20" s="21">
+        <v>151818.72268499999</v>
+      </c>
+      <c r="N20" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="O20" s="2"/>
+      <c r="P20" s="7">
+        <v>29</v>
+      </c>
+      <c r="Q20" s="66">
+        <v>2171.2157052484927</v>
+      </c>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2">
+        <v>28465</v>
+      </c>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="2"/>
+      <c r="W20" s="23">
+        <v>46095</v>
+      </c>
+    </row>
+    <row r="21" spans="2:23">
+      <c r="B21" s="18">
+        <v>99</v>
+      </c>
+      <c r="C21" s="1">
+        <v>46054</v>
+      </c>
+      <c r="D21" s="1">
+        <v>46055</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" s="19"/>
+      <c r="G21" s="147" t="s">
+        <v>167</v>
+      </c>
+      <c r="H21" s="3">
+        <v>495.33</v>
+      </c>
+      <c r="I21" s="4">
+        <v>285.70999999999998</v>
+      </c>
+      <c r="J21" s="4">
+        <v>141520.73429999998</v>
+      </c>
+      <c r="K21" s="4">
+        <v>299.99549999999999</v>
+      </c>
+      <c r="L21" s="1">
+        <v>46071</v>
+      </c>
+      <c r="M21" s="21">
+        <v>148596.77101500001</v>
+      </c>
+      <c r="N21" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="O21" s="2"/>
+      <c r="P21" s="7">
+        <v>25</v>
+      </c>
+      <c r="Q21" s="66">
+        <v>1832.0149851164385</v>
+      </c>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2">
+        <v>28842</v>
+      </c>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="2"/>
+      <c r="W21" s="23">
+        <v>46095</v>
+      </c>
+    </row>
+    <row r="22" spans="2:23">
+      <c r="B22" s="18">
+        <v>100</v>
+      </c>
+      <c r="C22" s="1">
+        <v>46063</v>
+      </c>
+      <c r="D22" s="1">
+        <v>46062</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" s="19"/>
+      <c r="G22" s="147" t="s">
+        <v>167</v>
+      </c>
+      <c r="H22" s="3">
+        <v>984.8</v>
+      </c>
+      <c r="I22" s="4">
+        <v>285.70999999999998</v>
+      </c>
+      <c r="J22" s="4">
+        <v>281367.20799999998</v>
+      </c>
+      <c r="K22" s="4">
+        <v>299.99549999999999</v>
+      </c>
+      <c r="L22" s="1">
+        <v>46078</v>
+      </c>
+      <c r="M22" s="21">
+        <v>295435.56839999999</v>
+      </c>
+      <c r="N22" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="O22" s="2"/>
+      <c r="P22" s="7">
+        <v>22</v>
+      </c>
+      <c r="Q22" s="66">
+        <v>3205.2735640109586</v>
+      </c>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2">
+        <v>29741</v>
+      </c>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="2"/>
+      <c r="W22" s="23">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="23" spans="2:23">
+      <c r="B23" s="18">
+        <v>101</v>
+      </c>
+      <c r="C23" s="1">
+        <v>46068</v>
+      </c>
+      <c r="D23" s="1">
+        <v>46067</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="G23" s="147" t="s">
+        <v>167</v>
+      </c>
+      <c r="H23" s="3">
+        <v>992.3</v>
+      </c>
+      <c r="I23" s="4">
+        <v>219.04759999999999</v>
+      </c>
+      <c r="J23" s="4">
+        <v>217360.93347999998</v>
+      </c>
+      <c r="K23" s="4">
+        <v>229.99997999999999</v>
+      </c>
+      <c r="L23" s="1">
+        <v>46083</v>
+      </c>
+      <c r="M23" s="21">
+        <v>228228.98015399999</v>
+      </c>
+      <c r="N23" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="O23" s="2"/>
+      <c r="P23" s="7">
+        <v>26</v>
+      </c>
+      <c r="Q23" s="66">
+        <v>2926.3332249882737</v>
+      </c>
+      <c r="R23" s="2"/>
+      <c r="S23" s="2">
+        <v>30305</v>
+      </c>
+      <c r="T23" s="2"/>
+      <c r="U23" s="2"/>
+      <c r="V23" s="2"/>
+      <c r="W23" s="23">
+        <v>46110</v>
+      </c>
+    </row>
+    <row r="24" spans="2:23">
+      <c r="B24" s="18">
+        <v>102</v>
+      </c>
+      <c r="C24" s="1">
+        <v>46070</v>
+      </c>
+      <c r="D24" s="1">
+        <v>46070</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="H24" s="3">
+        <v>360.8</v>
+      </c>
+      <c r="I24" s="4">
+        <v>181.02099999999999</v>
+      </c>
+      <c r="J24" s="4">
+        <v>65312.376799999998</v>
+      </c>
+      <c r="K24" s="4">
+        <v>190.07204999999999</v>
+      </c>
+      <c r="L24" s="1">
+        <v>46086</v>
+      </c>
+      <c r="M24" s="21">
+        <v>68577.995639999994</v>
+      </c>
+      <c r="N24" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="O24" s="2"/>
+      <c r="P24" s="7">
+        <v>23</v>
+      </c>
+      <c r="Q24" s="66">
+        <v>777.84356698520537</v>
+      </c>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="2"/>
+      <c r="W24" s="23">
+        <v>46110</v>
+      </c>
+    </row>
+    <row r="25" spans="2:23">
+      <c r="B25" s="18">
+        <v>103</v>
+      </c>
+      <c r="C25" s="1">
+        <v>46070</v>
+      </c>
+      <c r="D25" s="1">
+        <v>46070</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="H25" s="3">
+        <v>352</v>
+      </c>
+      <c r="I25" s="4">
+        <v>181.09</v>
+      </c>
+      <c r="J25" s="4">
+        <v>63743.68</v>
+      </c>
+      <c r="K25" s="4">
+        <v>190.14450000000002</v>
+      </c>
+      <c r="L25" s="1">
+        <v>46086</v>
+      </c>
+      <c r="M25" s="21">
+        <v>66930.864000000001</v>
+      </c>
+      <c r="N25" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="O25" s="2"/>
+      <c r="P25" s="7">
+        <v>23</v>
+      </c>
+      <c r="Q25" s="66">
+        <v>759.16103276712329</v>
+      </c>
+      <c r="R25" s="2"/>
+      <c r="S25" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="2"/>
+      <c r="W25" s="23">
+        <v>46110</v>
+      </c>
+    </row>
+    <row r="26" spans="2:23">
+      <c r="B26" s="18">
+        <v>104</v>
+      </c>
+      <c r="C26" s="1">
+        <v>46070</v>
+      </c>
+      <c r="D26" s="1">
+        <v>46070</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="H26" s="3">
+        <v>352</v>
+      </c>
+      <c r="I26" s="4">
+        <v>181.09</v>
+      </c>
+      <c r="J26" s="4">
+        <v>63743.68</v>
+      </c>
+      <c r="K26" s="4">
+        <v>190.14450000000002</v>
+      </c>
+      <c r="L26" s="1">
+        <v>46086</v>
+      </c>
+      <c r="M26" s="21">
+        <v>66930.864000000001</v>
+      </c>
+      <c r="N26" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="O26" s="2"/>
+      <c r="P26" s="7">
+        <v>23</v>
+      </c>
+      <c r="Q26" s="66">
+        <v>759.16103276712329</v>
+      </c>
+      <c r="R26" s="2"/>
+      <c r="S26" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="2"/>
+      <c r="W26" s="23">
+        <v>46110</v>
+      </c>
+    </row>
+    <row r="27" spans="2:23">
+      <c r="B27" s="18">
+        <v>105</v>
+      </c>
+      <c r="C27" s="1">
+        <v>46070</v>
+      </c>
+      <c r="D27" s="1">
+        <v>46070</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="H27" s="3">
+        <v>352</v>
+      </c>
+      <c r="I27" s="4">
+        <v>181.09</v>
+      </c>
+      <c r="J27" s="4">
+        <v>63743.68</v>
+      </c>
+      <c r="K27" s="4">
+        <v>190.14450000000002</v>
+      </c>
+      <c r="L27" s="1">
+        <v>46086</v>
+      </c>
+      <c r="M27" s="21">
+        <v>66930.864000000001</v>
+      </c>
+      <c r="N27" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="O27" s="2"/>
+      <c r="P27" s="7">
+        <v>23</v>
+      </c>
+      <c r="Q27" s="66">
+        <v>759.16103276712329</v>
+      </c>
+      <c r="R27" s="2"/>
+      <c r="S27" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="T27" s="2"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="2"/>
+      <c r="W27" s="23">
+        <v>46110</v>
+      </c>
+    </row>
+    <row r="28" spans="2:23">
+      <c r="B28" s="18">
+        <v>108</v>
+      </c>
+      <c r="C28" s="1">
+        <v>46086</v>
+      </c>
+      <c r="D28" s="1">
+        <v>46086</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="H28" s="3">
+        <v>1000.59</v>
+      </c>
+      <c r="I28" s="4">
+        <v>285.71420000000001</v>
+      </c>
+      <c r="J28" s="4">
+        <v>285882.77137800003</v>
+      </c>
+      <c r="K28" s="4">
+        <v>299.99991</v>
+      </c>
+      <c r="L28" s="1">
+        <v>46102</v>
+      </c>
+      <c r="M28" s="21">
+        <v>300176.90994690004</v>
+      </c>
+      <c r="N28" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="O28" s="2"/>
+      <c r="P28" s="7">
+        <v>9</v>
+      </c>
+      <c r="Q28" s="66">
+        <v>1332.292038668433</v>
+      </c>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2">
+        <v>31752</v>
+      </c>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="2"/>
+      <c r="W28" s="23">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="30" spans="2:23">
+      <c r="Q30" s="6">
+        <f>SUM(Q12:Q29)</f>
+        <v>25172.63930784597</v>
+      </c>
+    </row>
+    <row r="33" spans="4:23">
+      <c r="D33" s="1">
+        <v>45993</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G33" s="147" t="s">
+        <v>167</v>
+      </c>
+      <c r="H33" s="3">
+        <v>502.32</v>
+      </c>
+      <c r="I33" s="4">
+        <v>264.76190000000003</v>
+      </c>
+      <c r="J33" s="4">
+        <v>132995.19760800002</v>
+      </c>
+      <c r="K33" s="4">
+        <v>277.99999500000001</v>
+      </c>
+      <c r="L33" s="1">
+        <v>46011</v>
+      </c>
+      <c r="M33" s="21">
+        <v>139644.95748840002</v>
+      </c>
+      <c r="N33" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="O33" s="2"/>
+      <c r="P33" s="7">
+        <v>75</v>
+      </c>
+      <c r="Q33" s="66">
+        <v>5164.9504824476717</v>
+      </c>
+      <c r="R33" s="2"/>
+      <c r="S33" s="2">
+        <v>22819</v>
+      </c>
+      <c r="T33" s="2"/>
+      <c r="U33" s="2"/>
+      <c r="V33" s="2"/>
+      <c r="W33" s="23">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="34" spans="4:23">
+      <c r="D34" s="1">
+        <v>45995</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H34" s="3">
+        <v>320</v>
+      </c>
+      <c r="I34" s="4">
+        <v>280.95229999999998</v>
+      </c>
+      <c r="J34" s="4">
+        <v>89904.73599999999</v>
+      </c>
+      <c r="K34" s="4">
+        <v>294.99991499999999</v>
+      </c>
+      <c r="L34" s="1">
+        <v>46013</v>
+      </c>
+      <c r="M34" s="21">
+        <v>94399.972799999989</v>
+      </c>
+      <c r="N34" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="O34" s="2"/>
+      <c r="P34" s="7">
+        <v>73</v>
+      </c>
+      <c r="Q34" s="66">
+        <v>3398.3990207999996</v>
+      </c>
+      <c r="R34" s="2"/>
+      <c r="S34" s="2">
+        <v>23010</v>
+      </c>
+      <c r="T34" s="2"/>
+      <c r="U34" s="2"/>
+      <c r="V34" s="2"/>
+      <c r="W34" s="23">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="35" spans="4:23">
+      <c r="D35" s="1">
+        <v>46016</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G35" s="147" t="s">
+        <v>167</v>
+      </c>
+      <c r="H35" s="3">
+        <v>1008.82</v>
+      </c>
+      <c r="I35" s="4">
+        <v>264.76190000000003</v>
+      </c>
+      <c r="J35" s="4">
+        <v>267097.09995800006</v>
+      </c>
+      <c r="K35" s="4">
+        <v>277.99999500000001</v>
+      </c>
+      <c r="L35" s="1">
+        <v>46034</v>
+      </c>
+      <c r="M35" s="21">
+        <v>280451.95495590003</v>
+      </c>
+      <c r="N35" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="O35" s="2"/>
+      <c r="P35" s="7">
+        <v>56</v>
+      </c>
+      <c r="Q35" s="66">
+        <v>7745.0841259054032</v>
+      </c>
+      <c r="R35" s="2"/>
+      <c r="S35" s="2">
+        <v>24850</v>
+      </c>
+      <c r="T35" s="2"/>
+      <c r="U35" s="2"/>
+      <c r="V35" s="2"/>
+      <c r="W35" s="23">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="36" spans="4:23">
+      <c r="D36" s="1">
+        <v>46032</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H36" s="3">
+        <v>180</v>
+      </c>
+      <c r="I36" s="4">
+        <v>302</v>
+      </c>
+      <c r="J36" s="4">
+        <v>54360</v>
+      </c>
+      <c r="K36" s="4">
+        <v>317.10000000000002</v>
+      </c>
+      <c r="L36" s="1">
+        <v>46050</v>
+      </c>
+      <c r="M36" s="21">
+        <v>57078.000000000007</v>
+      </c>
+      <c r="N36" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="O36" s="2"/>
+      <c r="P36" s="7">
+        <v>40</v>
+      </c>
+      <c r="Q36" s="66">
+        <v>1125.922191780822</v>
+      </c>
+      <c r="R36" s="2"/>
+      <c r="S36" s="2">
+        <v>26396</v>
+      </c>
+      <c r="T36" s="2"/>
+      <c r="U36" s="2"/>
+      <c r="V36" s="2"/>
+      <c r="W36" s="23">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="37" spans="4:23">
+      <c r="D37" s="1">
+        <v>46037</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F37" s="2"/>
+      <c r="G37" s="147" t="s">
+        <v>167</v>
+      </c>
+      <c r="H37" s="3">
+        <v>496.7</v>
+      </c>
+      <c r="I37" s="4">
+        <v>264.76190000000003</v>
+      </c>
+      <c r="J37" s="4">
+        <v>131507.23573000001</v>
+      </c>
+      <c r="K37" s="4">
+        <v>277.99999500000001</v>
+      </c>
+      <c r="L37" s="1">
+        <v>46055</v>
+      </c>
+      <c r="M37" s="21">
+        <v>138082.59751650001</v>
+      </c>
+      <c r="N37" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="O37" s="2"/>
+      <c r="P37" s="7">
+        <v>36</v>
+      </c>
+      <c r="Q37" s="66">
+        <v>2451.438991525808</v>
+      </c>
+      <c r="R37" s="2"/>
+      <c r="S37" s="2">
+        <v>26842</v>
+      </c>
+      <c r="T37" s="2"/>
+      <c r="U37" s="2"/>
+      <c r="V37" s="2"/>
+      <c r="W37" s="23">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="38" spans="4:23">
+      <c r="D38" s="1">
+        <v>46038</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H38" s="3">
+        <v>200</v>
+      </c>
+      <c r="I38" s="4">
+        <v>302</v>
+      </c>
+      <c r="J38" s="4">
+        <v>60400</v>
+      </c>
+      <c r="K38" s="4">
+        <v>317.10000000000002</v>
+      </c>
+      <c r="L38" s="1">
+        <v>46056</v>
+      </c>
+      <c r="M38" s="21">
+        <v>63420.000000000007</v>
+      </c>
+      <c r="N38" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="O38" s="2"/>
+      <c r="P38" s="7">
+        <v>57</v>
+      </c>
+      <c r="Q38" s="66">
+        <v>1782.7101369863014</v>
+      </c>
+      <c r="R38" s="2"/>
+      <c r="S38" s="2">
+        <v>26999</v>
+      </c>
+      <c r="T38" s="2"/>
+      <c r="U38" s="2"/>
+      <c r="V38" s="2"/>
+      <c r="W38" s="23">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="39" spans="4:23">
+      <c r="D39" s="1">
+        <v>46044</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F39" s="2"/>
+      <c r="G39" s="147" t="s">
+        <v>167</v>
+      </c>
+      <c r="H39" s="3">
+        <v>495.24</v>
+      </c>
+      <c r="I39" s="4">
+        <v>264.76190000000003</v>
+      </c>
+      <c r="J39" s="4">
+        <v>131120.68335600002</v>
+      </c>
+      <c r="K39" s="4">
+        <v>277.99999500000001</v>
+      </c>
+      <c r="L39" s="1">
+        <v>46062</v>
+      </c>
+      <c r="M39" s="21">
+        <v>137676.71752380001</v>
+      </c>
+      <c r="N39" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="O39" s="2"/>
+      <c r="P39" s="7">
+        <v>51</v>
+      </c>
+      <c r="Q39" s="66">
+        <v>3462.6637448451615</v>
+      </c>
+      <c r="R39" s="2"/>
+      <c r="S39" s="2">
+        <v>27689</v>
+      </c>
+      <c r="T39" s="2"/>
+      <c r="U39" s="2"/>
+      <c r="V39" s="2"/>
+      <c r="W39" s="23">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="40" spans="4:23">
+      <c r="D40" s="1">
+        <v>46050</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F40" s="2"/>
+      <c r="G40" s="147" t="s">
+        <v>167</v>
+      </c>
+      <c r="H40" s="3">
+        <v>999.2</v>
+      </c>
+      <c r="I40" s="4">
+        <v>285.70999999999998</v>
+      </c>
+      <c r="J40" s="4">
+        <v>285481.43199999997</v>
+      </c>
+      <c r="K40" s="4">
+        <v>299.99549999999999</v>
+      </c>
+      <c r="L40" s="1">
+        <v>46068</v>
+      </c>
+      <c r="M40" s="21">
+        <v>299755.5036</v>
+      </c>
+      <c r="N40" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="O40" s="2"/>
+      <c r="P40" s="7">
+        <v>45</v>
+      </c>
+      <c r="Q40" s="66">
+        <v>6652.1084360547939</v>
+      </c>
+      <c r="R40" s="2"/>
+      <c r="S40" s="2">
+        <v>28387</v>
+      </c>
+      <c r="T40" s="2"/>
+      <c r="U40" s="2"/>
+      <c r="V40" s="2"/>
+      <c r="W40" s="23">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="41" spans="4:23">
+      <c r="D41" s="1">
+        <v>46057</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F41" s="2"/>
+      <c r="G41" s="147" t="s">
+        <v>167</v>
+      </c>
+      <c r="H41" s="3">
+        <v>990.14</v>
+      </c>
+      <c r="I41" s="4">
+        <v>285.70999999999998</v>
+      </c>
+      <c r="J41" s="4">
+        <v>282892.89939999999</v>
+      </c>
+      <c r="K41" s="4">
+        <v>299.99549999999999</v>
+      </c>
+      <c r="L41" s="1">
+        <v>46075</v>
+      </c>
+      <c r="M41" s="21">
+        <v>297037.54437000002</v>
+      </c>
+      <c r="N41" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="O41" s="2"/>
+      <c r="P41" s="7">
+        <v>44</v>
+      </c>
+      <c r="Q41" s="66">
+        <v>6445.3078120832879</v>
+      </c>
+      <c r="R41" s="2"/>
+      <c r="S41" s="2">
+        <v>29149</v>
+      </c>
+      <c r="T41" s="2"/>
+      <c r="U41" s="2"/>
+      <c r="V41" s="2"/>
+      <c r="W41" s="23">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="42" spans="4:23">
+      <c r="D42" s="1">
+        <v>46060</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="H42" s="3">
+        <v>489.21</v>
+      </c>
+      <c r="I42" s="4">
+        <v>285.70999999999998</v>
+      </c>
+      <c r="J42" s="4">
+        <v>139772.18909999999</v>
+      </c>
+      <c r="K42" s="4">
+        <v>299.99549999999999</v>
+      </c>
+      <c r="L42" s="1">
+        <v>46078</v>
+      </c>
+      <c r="M42" s="21">
+        <v>146760.79855499999</v>
+      </c>
+      <c r="N42" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="O42" s="2"/>
+      <c r="P42" s="7">
+        <v>48</v>
+      </c>
+      <c r="Q42" s="66">
+        <v>3474.0090397676713</v>
+      </c>
+      <c r="R42" s="2"/>
+      <c r="S42" s="2">
+        <v>29633</v>
+      </c>
+      <c r="T42" s="2"/>
+      <c r="U42" s="2"/>
+      <c r="V42" s="2"/>
+      <c r="W42" s="23">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="43" spans="4:23">
+      <c r="D43" s="1">
+        <v>46065</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="H43" s="3">
+        <v>989.72</v>
+      </c>
+      <c r="I43" s="3">
+        <v>285.70999999999998</v>
+      </c>
+      <c r="J43" s="4">
+        <v>282772.90119999996</v>
+      </c>
+      <c r="K43" s="4">
+        <v>299.99549999999999</v>
+      </c>
+      <c r="L43" s="1">
+        <v>46083</v>
+      </c>
+      <c r="M43" s="21">
+        <v>296911.54625999997</v>
+      </c>
+      <c r="N43" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="O43" s="2"/>
+      <c r="P43" s="7">
+        <v>41</v>
+      </c>
+      <c r="Q43" s="66">
+        <v>6003.307428489863</v>
+      </c>
+      <c r="R43" s="2"/>
+      <c r="S43" s="2">
+        <v>30218</v>
+      </c>
+      <c r="T43" s="2"/>
+      <c r="U43" s="2"/>
+      <c r="V43" s="2"/>
+      <c r="W43" s="23">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="44" spans="4:23">
+      <c r="D44" s="1">
+        <v>46081</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="H44" s="3">
+        <v>352</v>
+      </c>
+      <c r="I44" s="4">
+        <v>181.09</v>
+      </c>
+      <c r="J44" s="4">
+        <v>63743.68</v>
+      </c>
+      <c r="K44" s="4">
+        <v>190.14450000000002</v>
+      </c>
+      <c r="L44" s="1">
+        <v>46099</v>
+      </c>
+      <c r="M44" s="21">
+        <v>66930.864000000001</v>
+      </c>
+      <c r="N44" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="O44" s="2"/>
+      <c r="P44" s="7">
+        <v>25</v>
+      </c>
+      <c r="Q44" s="66">
+        <v>825.17503561643844</v>
+      </c>
+      <c r="R44" s="2"/>
+      <c r="S44" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="T44" s="2"/>
+      <c r="U44" s="2"/>
+      <c r="V44" s="2"/>
+      <c r="W44" s="23">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="45" spans="4:23">
+      <c r="D45" s="1">
+        <v>46081</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="H45" s="3">
+        <v>352</v>
+      </c>
+      <c r="I45" s="4">
+        <v>181.09</v>
+      </c>
+      <c r="J45" s="4">
+        <v>63743.68</v>
+      </c>
+      <c r="K45" s="4">
+        <v>190.14450000000002</v>
+      </c>
+      <c r="L45" s="1">
+        <v>46099</v>
+      </c>
+      <c r="M45" s="21">
+        <v>66930.864000000001</v>
+      </c>
+      <c r="N45" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="O45" s="2"/>
+      <c r="P45" s="7">
+        <v>25</v>
+      </c>
+      <c r="Q45" s="66">
+        <v>825.17503561643844</v>
+      </c>
+      <c r="R45" s="2"/>
+      <c r="S45" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="T45" s="2"/>
+      <c r="U45" s="2"/>
+      <c r="V45" s="2"/>
+      <c r="W45" s="23">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="46" spans="4:23">
+      <c r="D46" s="1">
+        <v>46081</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="H46" s="3">
+        <v>352</v>
+      </c>
+      <c r="I46" s="4">
+        <v>181.09</v>
+      </c>
+      <c r="J46" s="4">
+        <v>63743.68</v>
+      </c>
+      <c r="K46" s="4">
+        <v>190.14450000000002</v>
+      </c>
+      <c r="L46" s="1">
+        <v>46099</v>
+      </c>
+      <c r="M46" s="21">
+        <v>66930.864000000001</v>
+      </c>
+      <c r="N46" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="O46" s="2"/>
+      <c r="P46" s="7">
+        <v>25</v>
+      </c>
+      <c r="Q46" s="66">
+        <v>825.17503561643844</v>
+      </c>
+      <c r="R46" s="2"/>
+      <c r="S46" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="T46" s="2"/>
+      <c r="U46" s="2"/>
+      <c r="V46" s="2"/>
+      <c r="W46" s="23">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="48" spans="4:23">
+      <c r="Q48" s="6">
+        <f>SUM(Q33:Q47)</f>
+        <v>50181.4265175361</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/YarnBook-TEX WEAVES.xlsx
+++ b/YarnBook-TEX WEAVES.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="90" windowWidth="28755" windowHeight="12090" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="90" windowWidth="28755" windowHeight="12090" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="25-26" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2179" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2183" uniqueCount="315">
   <si>
     <t>H NO</t>
   </si>
@@ -3229,7 +3229,7 @@
       <c r="O16" s="2"/>
       <c r="P16" s="7">
         <f t="shared" ref="P16:P17" ca="1" si="9">DAYS360(L16,TODAY())-(1)</f>
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
@@ -3301,11 +3301,11 @@
       <c r="O17" s="49"/>
       <c r="P17" s="53">
         <f t="shared" ca="1" si="9"/>
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q17" s="66">
         <f t="shared" ref="Q17:Q26" ca="1" si="10">0.18*P17*M17/365</f>
-        <v>11195.885445751233</v>
+        <v>11260.977802993975</v>
       </c>
       <c r="R17" s="49"/>
       <c r="S17" s="49">
@@ -16795,7 +16795,7 @@
       <c r="O196" s="2"/>
       <c r="P196" s="7">
         <f t="shared" ref="P196:P229" ca="1" si="116">DAYS360(L196,TODAY())-(1)</f>
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q196" s="2"/>
       <c r="R196" s="2"/>
@@ -18014,7 +18014,7 @@
       <c r="O212" s="2"/>
       <c r="P212" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="Q212" s="2"/>
       <c r="R212" s="2"/>
@@ -18704,7 +18704,7 @@
       <c r="O221" s="2"/>
       <c r="P221" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q221" s="2"/>
       <c r="R221" s="2"/>
@@ -19015,7 +19015,7 @@
       <c r="O225" s="2"/>
       <c r="P225" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Q225" s="2"/>
       <c r="R225" s="2"/>
@@ -19087,7 +19087,7 @@
       <c r="O226" s="2"/>
       <c r="P226" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="Q226" s="2"/>
       <c r="R226" s="2"/>
@@ -19159,7 +19159,7 @@
       <c r="O227" s="2"/>
       <c r="P227" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="Q227" s="2"/>
       <c r="R227" s="2"/>
@@ -19231,7 +19231,7 @@
       <c r="O228" s="2"/>
       <c r="P228" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Q228" s="2"/>
       <c r="R228" s="2"/>
@@ -19303,7 +19303,7 @@
       <c r="O229" s="2"/>
       <c r="P229" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Q229" s="2"/>
       <c r="R229" s="2"/>
@@ -19797,7 +19797,7 @@
       <c r="O241" s="2"/>
       <c r="P241" s="7">
         <f t="shared" ref="P241" ca="1" si="133">DAYS360(L241,TODAY())-(1)</f>
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q241" s="2"/>
       <c r="R241" s="2"/>
@@ -20566,7 +20566,7 @@
       </c>
       <c r="L5" s="106"/>
       <c r="M5" s="6">
-        <f t="shared" ref="M5:M38" si="2">K5-((G5*H5)*0.02)</f>
+        <f t="shared" ref="M5:M40" si="2">K5-((G5*H5)*0.02)</f>
         <v>113174.0928</v>
       </c>
     </row>
@@ -21452,9 +21452,6 @@
         <f t="shared" si="2"/>
         <v>37551.987200000003</v>
       </c>
-      <c r="O25" s="123">
-        <v>46172</v>
-      </c>
     </row>
     <row r="26" spans="1:16">
       <c r="A26" s="2">
@@ -21963,32 +21960,76 @@
         <v>37</v>
       </c>
       <c r="B39" s="1">
-        <v>46188</v>
-      </c>
-      <c r="C39" s="1"/>
-      <c r="D39" s="2"/>
+        <v>46186</v>
+      </c>
+      <c r="C39" s="1">
+        <v>46186</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="E39" s="2"/>
-      <c r="F39" s="103"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
+      <c r="F39" s="103" t="s">
+        <v>210</v>
+      </c>
+      <c r="G39" s="3">
+        <v>1502</v>
+      </c>
+      <c r="H39" s="4">
+        <v>14.56</v>
+      </c>
+      <c r="I39" s="4">
+        <f t="shared" ref="I39:I40" si="3">H39*1.05</f>
+        <v>15.288000000000002</v>
+      </c>
       <c r="J39" s="2"/>
-      <c r="K39" s="104"/>
+      <c r="K39" s="104">
+        <f t="shared" ref="K39:K40" si="4">G39*I39</f>
+        <v>22962.576000000005</v>
+      </c>
       <c r="L39" s="106"/>
+      <c r="M39" s="6">
+        <f t="shared" si="2"/>
+        <v>22525.193600000006</v>
+      </c>
     </row>
     <row r="40" spans="1:13">
-      <c r="A40" s="2"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="2"/>
+      <c r="A40" s="2">
+        <v>38</v>
+      </c>
+      <c r="B40" s="1">
+        <v>46186</v>
+      </c>
+      <c r="C40" s="1">
+        <v>46186</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="E40" s="2"/>
-      <c r="F40" s="103"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
+      <c r="F40" s="103" t="s">
+        <v>210</v>
+      </c>
+      <c r="G40" s="3">
+        <v>1036</v>
+      </c>
+      <c r="H40" s="4">
+        <v>14.56</v>
+      </c>
+      <c r="I40" s="4">
+        <f t="shared" si="3"/>
+        <v>15.288000000000002</v>
+      </c>
       <c r="J40" s="2"/>
-      <c r="K40" s="104"/>
+      <c r="K40" s="104">
+        <f t="shared" si="4"/>
+        <v>15838.368000000002</v>
+      </c>
       <c r="L40" s="106"/>
+      <c r="M40" s="6">
+        <f t="shared" si="2"/>
+        <v>15536.684800000003</v>
+      </c>
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="2"/>
@@ -22125,17 +22166,17 @@
       <c r="F50" s="101"/>
       <c r="G50" s="12">
         <f>SUBTOTAL(9,G3:G49)</f>
-        <v>108920</v>
+        <v>111458</v>
       </c>
       <c r="H50" s="12">
         <f>(K50/1.05)/G50</f>
-        <v>14.302132941608521</v>
+        <v>14.308004808986345</v>
       </c>
       <c r="I50" s="10"/>
       <c r="J50" s="10"/>
       <c r="K50" s="107">
         <f>SUBTOTAL(9,K3:K49)</f>
-        <v>1635677.736</v>
+        <v>1674478.6800000002</v>
       </c>
       <c r="L50" s="108">
         <f>SUBTOTAL(9,L49:L49)</f>
@@ -24547,7 +24588,6 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AH135"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
@@ -24652,7 +24692,7 @@
       </c>
       <c r="Z2" s="149"/>
     </row>
-    <row r="3" spans="1:34" ht="15.75" hidden="1" thickBot="1">
+    <row r="3" spans="1:34" ht="15.75" thickBot="1">
       <c r="A3" t="s">
         <v>113</v>
       </c>
@@ -24695,7 +24735,7 @@
       <c r="AG3" s="2"/>
       <c r="AH3" s="1"/>
     </row>
-    <row r="4" spans="1:34" ht="15.75" hidden="1" thickBot="1">
+    <row r="4" spans="1:34" ht="15.75" thickBot="1">
       <c r="A4" t="s">
         <v>113</v>
       </c>
@@ -24862,7 +24902,7 @@
       <c r="AG5" s="2"/>
       <c r="AH5" s="23"/>
     </row>
-    <row r="6" spans="1:34" hidden="1">
+    <row r="6" spans="1:34">
       <c r="A6" t="s">
         <v>113</v>
       </c>
@@ -24908,7 +24948,7 @@
       <c r="O6" s="2"/>
       <c r="P6" s="7">
         <f t="shared" ref="P6:P27" ca="1" si="5">DAYS360(L6,TODAY())-(1)</f>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
@@ -24930,7 +24970,7 @@
       <c r="AG6" s="2"/>
       <c r="AH6" s="23"/>
     </row>
-    <row r="7" spans="1:34" hidden="1">
+    <row r="7" spans="1:34">
       <c r="A7" t="s">
         <v>113</v>
       </c>
@@ -24976,7 +25016,7 @@
       <c r="O7" s="2"/>
       <c r="P7" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
@@ -24998,7 +25038,7 @@
       <c r="AG7" s="2"/>
       <c r="AH7" s="23"/>
     </row>
-    <row r="8" spans="1:34" hidden="1">
+    <row r="8" spans="1:34">
       <c r="A8" t="s">
         <v>113</v>
       </c>
@@ -25044,7 +25084,7 @@
       <c r="O8" s="2"/>
       <c r="P8" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
@@ -25066,7 +25106,7 @@
       <c r="AG8" s="2"/>
       <c r="AH8" s="23"/>
     </row>
-    <row r="9" spans="1:34" hidden="1">
+    <row r="9" spans="1:34">
       <c r="A9" t="s">
         <v>113</v>
       </c>
@@ -25136,7 +25176,7 @@
       <c r="AG9" s="2"/>
       <c r="AH9" s="23"/>
     </row>
-    <row r="10" spans="1:34" hidden="1">
+    <row r="10" spans="1:34">
       <c r="A10" t="s">
         <v>113</v>
       </c>
@@ -25182,7 +25222,7 @@
       <c r="O10" s="2"/>
       <c r="P10" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
@@ -25204,7 +25244,7 @@
       <c r="AG10" s="2"/>
       <c r="AH10" s="23"/>
     </row>
-    <row r="11" spans="1:34" hidden="1">
+    <row r="11" spans="1:34">
       <c r="A11" t="s">
         <v>113</v>
       </c>
@@ -25277,7 +25317,7 @@
       <c r="AG11" s="2"/>
       <c r="AH11" s="23"/>
     </row>
-    <row r="12" spans="1:34" hidden="1">
+    <row r="12" spans="1:34">
       <c r="A12" t="s">
         <v>113</v>
       </c>
@@ -25323,7 +25363,7 @@
       <c r="O12" s="2"/>
       <c r="P12" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
@@ -25345,7 +25385,7 @@
       <c r="AG12" s="2"/>
       <c r="AH12" s="23"/>
     </row>
-    <row r="13" spans="1:34" hidden="1">
+    <row r="13" spans="1:34">
       <c r="A13" t="s">
         <v>270</v>
       </c>
@@ -25391,7 +25431,7 @@
       <c r="O13" s="2"/>
       <c r="P13" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
@@ -25413,7 +25453,7 @@
       <c r="AG13" s="2"/>
       <c r="AH13" s="23"/>
     </row>
-    <row r="14" spans="1:34" hidden="1">
+    <row r="14" spans="1:34">
       <c r="A14" t="s">
         <v>113</v>
       </c>
@@ -25459,7 +25499,7 @@
       <c r="O14" s="2"/>
       <c r="P14" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
@@ -25481,7 +25521,7 @@
       <c r="AG14" s="2"/>
       <c r="AH14" s="23"/>
     </row>
-    <row r="15" spans="1:34" hidden="1">
+    <row r="15" spans="1:34">
       <c r="A15" t="s">
         <v>113</v>
       </c>
@@ -25527,7 +25567,7 @@
       <c r="O15" s="2"/>
       <c r="P15" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
@@ -25549,7 +25589,7 @@
       <c r="AG15" s="2"/>
       <c r="AH15" s="23"/>
     </row>
-    <row r="16" spans="1:34" hidden="1">
+    <row r="16" spans="1:34">
       <c r="A16" t="s">
         <v>113</v>
       </c>
@@ -25595,7 +25635,7 @@
       <c r="O16" s="2"/>
       <c r="P16" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
@@ -25617,7 +25657,7 @@
       <c r="AG16" s="2"/>
       <c r="AH16" s="23"/>
     </row>
-    <row r="17" spans="1:34" hidden="1">
+    <row r="17" spans="1:34">
       <c r="A17" t="s">
         <v>113</v>
       </c>
@@ -25663,7 +25703,7 @@
       <c r="O17" s="2"/>
       <c r="P17" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
@@ -25685,7 +25725,7 @@
       <c r="AG17" s="2"/>
       <c r="AH17" s="23"/>
     </row>
-    <row r="18" spans="1:34" hidden="1">
+    <row r="18" spans="1:34">
       <c r="A18" t="s">
         <v>113</v>
       </c>
@@ -25731,7 +25771,7 @@
       <c r="O18" s="2"/>
       <c r="P18" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
@@ -25753,7 +25793,7 @@
       <c r="AG18" s="2"/>
       <c r="AH18" s="23"/>
     </row>
-    <row r="19" spans="1:34" hidden="1">
+    <row r="19" spans="1:34">
       <c r="A19" t="s">
         <v>113</v>
       </c>
@@ -25799,7 +25839,7 @@
       <c r="O19" s="2"/>
       <c r="P19" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
@@ -25821,7 +25861,7 @@
       <c r="AG19" s="2"/>
       <c r="AH19" s="23"/>
     </row>
-    <row r="20" spans="1:34" hidden="1">
+    <row r="20" spans="1:34">
       <c r="A20" t="s">
         <v>113</v>
       </c>
@@ -25867,7 +25907,7 @@
       <c r="O20" s="2"/>
       <c r="P20" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
@@ -25889,7 +25929,7 @@
       <c r="AG20" s="2"/>
       <c r="AH20" s="23"/>
     </row>
-    <row r="21" spans="1:34" hidden="1">
+    <row r="21" spans="1:34">
       <c r="A21" t="s">
         <v>113</v>
       </c>
@@ -25935,7 +25975,7 @@
       <c r="O21" s="2"/>
       <c r="P21" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
@@ -25957,7 +25997,7 @@
       <c r="AG21" s="2"/>
       <c r="AH21" s="23"/>
     </row>
-    <row r="22" spans="1:34" hidden="1">
+    <row r="22" spans="1:34">
       <c r="A22" t="s">
         <v>113</v>
       </c>
@@ -26003,7 +26043,7 @@
       <c r="O22" s="2"/>
       <c r="P22" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
@@ -26025,7 +26065,7 @@
       <c r="AG22" s="2"/>
       <c r="AH22" s="23"/>
     </row>
-    <row r="23" spans="1:34" hidden="1">
+    <row r="23" spans="1:34">
       <c r="A23" t="s">
         <v>113</v>
       </c>
@@ -26071,7 +26111,7 @@
       <c r="O23" s="2"/>
       <c r="P23" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
@@ -26093,7 +26133,7 @@
       <c r="AG23" s="2"/>
       <c r="AH23" s="23"/>
     </row>
-    <row r="24" spans="1:34" hidden="1">
+    <row r="24" spans="1:34">
       <c r="A24" t="s">
         <v>113</v>
       </c>
@@ -26139,7 +26179,7 @@
       <c r="O24" s="130"/>
       <c r="P24" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q24" s="130"/>
       <c r="R24" s="130"/>
@@ -26161,7 +26201,7 @@
       <c r="AG24" s="2"/>
       <c r="AH24" s="23"/>
     </row>
-    <row r="25" spans="1:34" hidden="1">
+    <row r="25" spans="1:34">
       <c r="A25" t="s">
         <v>113</v>
       </c>
@@ -26207,7 +26247,7 @@
       <c r="O25" s="130"/>
       <c r="P25" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q25" s="130"/>
       <c r="R25" s="130"/>
@@ -26229,7 +26269,7 @@
       <c r="AG25" s="2"/>
       <c r="AH25" s="23"/>
     </row>
-    <row r="26" spans="1:34" hidden="1">
+    <row r="26" spans="1:34">
       <c r="A26" t="s">
         <v>113</v>
       </c>
@@ -26275,7 +26315,7 @@
       <c r="O26" s="130"/>
       <c r="P26" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q26" s="130"/>
       <c r="R26" s="130"/>
@@ -26297,7 +26337,7 @@
       <c r="AG26" s="2"/>
       <c r="AH26" s="23"/>
     </row>
-    <row r="27" spans="1:34" hidden="1">
+    <row r="27" spans="1:34">
       <c r="A27" t="s">
         <v>113</v>
       </c>
@@ -26343,7 +26383,7 @@
       <c r="O27" s="130"/>
       <c r="P27" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q27" s="130"/>
       <c r="R27" s="130"/>
@@ -26365,7 +26405,7 @@
       <c r="AG27" s="2"/>
       <c r="AH27" s="23"/>
     </row>
-    <row r="28" spans="1:34" hidden="1">
+    <row r="28" spans="1:34">
       <c r="A28" s="133" t="s">
         <v>113</v>
       </c>
@@ -26411,7 +26451,7 @@
       <c r="O28" s="130"/>
       <c r="P28" s="7">
         <f t="shared" ref="P28:P35" ca="1" si="18">DAYS360(L28,TODAY())-(1)</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q28" s="130"/>
       <c r="R28" s="130"/>
@@ -26433,7 +26473,7 @@
       <c r="AG28" s="2"/>
       <c r="AH28" s="23"/>
     </row>
-    <row r="29" spans="1:34" hidden="1">
+    <row r="29" spans="1:34">
       <c r="A29" s="133" t="s">
         <v>113</v>
       </c>
@@ -26479,7 +26519,7 @@
       <c r="O29" s="130"/>
       <c r="P29" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q29" s="130"/>
       <c r="R29" s="130"/>
@@ -26501,7 +26541,7 @@
       <c r="AG29" s="2"/>
       <c r="AH29" s="23"/>
     </row>
-    <row r="30" spans="1:34" hidden="1">
+    <row r="30" spans="1:34">
       <c r="A30" s="133" t="s">
         <v>113</v>
       </c>
@@ -26547,7 +26587,7 @@
       <c r="O30" s="130"/>
       <c r="P30" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q30" s="130"/>
       <c r="R30" s="130"/>
@@ -26569,7 +26609,7 @@
       <c r="AG30" s="2"/>
       <c r="AH30" s="23"/>
     </row>
-    <row r="31" spans="1:34" hidden="1">
+    <row r="31" spans="1:34">
       <c r="A31" s="133" t="s">
         <v>113</v>
       </c>
@@ -26615,7 +26655,7 @@
       <c r="O31" s="130"/>
       <c r="P31" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q31" s="130"/>
       <c r="R31" s="130"/>
@@ -26637,7 +26677,7 @@
       <c r="AG31" s="2"/>
       <c r="AH31" s="23"/>
     </row>
-    <row r="32" spans="1:34" hidden="1">
+    <row r="32" spans="1:34">
       <c r="A32" s="133" t="s">
         <v>113</v>
       </c>
@@ -26683,7 +26723,7 @@
       <c r="O32" s="130"/>
       <c r="P32" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q32" s="130"/>
       <c r="R32" s="130"/>
@@ -26705,7 +26745,7 @@
       <c r="AG32" s="2"/>
       <c r="AH32" s="23"/>
     </row>
-    <row r="33" spans="1:34" hidden="1">
+    <row r="33" spans="1:34">
       <c r="A33" s="133" t="s">
         <v>113</v>
       </c>
@@ -26751,7 +26791,7 @@
       <c r="O33" s="130"/>
       <c r="P33" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q33" s="130"/>
       <c r="R33" s="130"/>
@@ -26819,7 +26859,7 @@
       <c r="O34" s="130"/>
       <c r="P34" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q34" s="130"/>
       <c r="R34" s="130"/>
@@ -26887,7 +26927,7 @@
       <c r="O35" s="130"/>
       <c r="P35" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q35" s="130"/>
       <c r="R35" s="130"/>
@@ -26909,7 +26949,7 @@
       <c r="AG35" s="2"/>
       <c r="AH35" s="23"/>
     </row>
-    <row r="36" spans="1:34" hidden="1">
+    <row r="36" spans="1:34">
       <c r="A36" t="s">
         <v>113</v>
       </c>
@@ -26946,7 +26986,7 @@
       <c r="AG36" s="2"/>
       <c r="AH36" s="23"/>
     </row>
-    <row r="37" spans="1:34" hidden="1">
+    <row r="37" spans="1:34">
       <c r="A37" t="s">
         <v>113</v>
       </c>
@@ -26983,7 +27023,7 @@
       <c r="AG37" s="2"/>
       <c r="AH37" s="23"/>
     </row>
-    <row r="38" spans="1:34" hidden="1">
+    <row r="38" spans="1:34">
       <c r="A38" t="s">
         <v>113</v>
       </c>
@@ -27020,7 +27060,7 @@
       <c r="AG38" s="2"/>
       <c r="AH38" s="23"/>
     </row>
-    <row r="39" spans="1:34" hidden="1">
+    <row r="39" spans="1:34">
       <c r="A39" t="s">
         <v>113</v>
       </c>
@@ -27057,7 +27097,7 @@
       <c r="AG39" s="2"/>
       <c r="AH39" s="23"/>
     </row>
-    <row r="40" spans="1:34" hidden="1">
+    <row r="40" spans="1:34">
       <c r="A40" t="s">
         <v>113</v>
       </c>
@@ -27094,7 +27134,7 @@
       <c r="AG40" s="2"/>
       <c r="AH40" s="23"/>
     </row>
-    <row r="41" spans="1:34" hidden="1">
+    <row r="41" spans="1:34">
       <c r="A41" t="s">
         <v>113</v>
       </c>
@@ -27131,7 +27171,7 @@
       <c r="AG41" s="2"/>
       <c r="AH41" s="23"/>
     </row>
-    <row r="42" spans="1:34" hidden="1">
+    <row r="42" spans="1:34">
       <c r="A42" t="s">
         <v>113</v>
       </c>
@@ -27168,7 +27208,7 @@
       <c r="AG42" s="2"/>
       <c r="AH42" s="23"/>
     </row>
-    <row r="43" spans="1:34" hidden="1">
+    <row r="43" spans="1:34">
       <c r="A43" t="s">
         <v>113</v>
       </c>
@@ -27205,7 +27245,7 @@
       <c r="AG43" s="2"/>
       <c r="AH43" s="23"/>
     </row>
-    <row r="44" spans="1:34" hidden="1">
+    <row r="44" spans="1:34">
       <c r="A44" t="s">
         <v>113</v>
       </c>
@@ -27242,7 +27282,7 @@
       <c r="AG44" s="2"/>
       <c r="AH44" s="23"/>
     </row>
-    <row r="45" spans="1:34" hidden="1">
+    <row r="45" spans="1:34">
       <c r="A45" t="s">
         <v>113</v>
       </c>
@@ -27279,7 +27319,7 @@
       <c r="AG45" s="2"/>
       <c r="AH45" s="23"/>
     </row>
-    <row r="46" spans="1:34" hidden="1">
+    <row r="46" spans="1:34">
       <c r="A46" t="s">
         <v>113</v>
       </c>
@@ -27316,7 +27356,7 @@
       <c r="AG46" s="2"/>
       <c r="AH46" s="23"/>
     </row>
-    <row r="47" spans="1:34" ht="15.75" hidden="1" thickBot="1">
+    <row r="47" spans="1:34" ht="15.75" thickBot="1">
       <c r="A47" t="s">
         <v>113</v>
       </c>
@@ -27353,7 +27393,7 @@
       <c r="AG47" s="30"/>
       <c r="AH47" s="35"/>
     </row>
-    <row r="48" spans="1:34" ht="15.75" hidden="1" thickBot="1">
+    <row r="48" spans="1:34" ht="15.75" thickBot="1">
       <c r="A48" t="s">
         <v>113</v>
       </c>
@@ -27390,7 +27430,7 @@
       <c r="AG48" s="2"/>
       <c r="AH48" s="23"/>
     </row>
-    <row r="49" spans="1:34" ht="15.75" hidden="1" thickBot="1">
+    <row r="49" spans="1:34" ht="15.75" thickBot="1">
       <c r="A49" t="s">
         <v>113</v>
       </c>
@@ -27454,7 +27494,7 @@
       <c r="AG49" s="10"/>
       <c r="AH49" s="17"/>
     </row>
-    <row r="50" spans="1:34" hidden="1">
+    <row r="50" spans="1:34">
       <c r="A50" t="s">
         <v>114</v>
       </c>
@@ -27490,7 +27530,7 @@
       <c r="AG50" s="2"/>
       <c r="AH50" s="1"/>
     </row>
-    <row r="51" spans="1:34" hidden="1">
+    <row r="51" spans="1:34">
       <c r="A51" t="s">
         <v>114</v>
       </c>
@@ -27504,7 +27544,7 @@
       </c>
       <c r="Z51" s="149"/>
     </row>
-    <row r="52" spans="1:34" ht="15.75" hidden="1" thickBot="1">
+    <row r="52" spans="1:34" ht="15.75" thickBot="1">
       <c r="A52" t="s">
         <v>114</v>
       </c>
@@ -27526,7 +27566,7 @@
       <c r="AG52" s="2"/>
       <c r="AH52" s="1"/>
     </row>
-    <row r="53" spans="1:34" ht="15.75" hidden="1" thickBot="1">
+    <row r="53" spans="1:34" ht="15.75" thickBot="1">
       <c r="A53" t="s">
         <v>114</v>
       </c>
@@ -27621,7 +27661,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:34" hidden="1">
+    <row r="54" spans="1:34">
       <c r="A54" t="s">
         <v>114</v>
       </c>
@@ -27842,7 +27882,7 @@
       <c r="AG56" s="2"/>
       <c r="AH56" s="23"/>
     </row>
-    <row r="57" spans="1:34" hidden="1">
+    <row r="57" spans="1:34">
       <c r="A57" t="s">
         <v>114</v>
       </c>
@@ -27888,7 +27928,7 @@
       <c r="O57" s="2"/>
       <c r="P57" s="7">
         <f t="shared" ref="P57:P79" ca="1" si="25">DAYS360(L57,TODAY())-(1)</f>
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" s="2"/>
@@ -27910,7 +27950,7 @@
       <c r="AG57" s="2"/>
       <c r="AH57" s="23"/>
     </row>
-    <row r="58" spans="1:34" hidden="1">
+    <row r="58" spans="1:34">
       <c r="A58" t="s">
         <v>114</v>
       </c>
@@ -27956,7 +27996,7 @@
       <c r="O58" s="2"/>
       <c r="P58" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" s="2"/>
@@ -27980,7 +28020,7 @@
       <c r="AG58" s="2"/>
       <c r="AH58" s="23"/>
     </row>
-    <row r="59" spans="1:34" hidden="1">
+    <row r="59" spans="1:34">
       <c r="A59" t="s">
         <v>114</v>
       </c>
@@ -28026,7 +28066,7 @@
       <c r="O59" s="2"/>
       <c r="P59" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" s="2"/>
@@ -28048,7 +28088,7 @@
       <c r="AG59" s="2"/>
       <c r="AH59" s="23"/>
     </row>
-    <row r="60" spans="1:34" hidden="1">
+    <row r="60" spans="1:34">
       <c r="A60" t="s">
         <v>114</v>
       </c>
@@ -28094,7 +28134,7 @@
       <c r="O60" s="2"/>
       <c r="P60" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" s="2"/>
@@ -28116,7 +28156,7 @@
       <c r="AG60" s="2"/>
       <c r="AH60" s="23"/>
     </row>
-    <row r="61" spans="1:34" hidden="1">
+    <row r="61" spans="1:34">
       <c r="A61" t="s">
         <v>114</v>
       </c>
@@ -28162,7 +28202,7 @@
       <c r="O61" s="2"/>
       <c r="P61" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="Q61" s="2"/>
       <c r="R61" s="2"/>
@@ -28186,7 +28226,7 @@
       <c r="AG61" s="2"/>
       <c r="AH61" s="23"/>
     </row>
-    <row r="62" spans="1:34" hidden="1">
+    <row r="62" spans="1:34">
       <c r="A62" t="s">
         <v>114</v>
       </c>
@@ -28232,7 +28272,7 @@
       <c r="O62" s="2"/>
       <c r="P62" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" s="2"/>
@@ -28256,7 +28296,7 @@
       <c r="AG62" s="2"/>
       <c r="AH62" s="23"/>
     </row>
-    <row r="63" spans="1:34" hidden="1">
+    <row r="63" spans="1:34">
       <c r="A63" t="s">
         <v>114</v>
       </c>
@@ -28302,7 +28342,7 @@
       <c r="O63" s="2"/>
       <c r="P63" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Q63" s="2"/>
       <c r="R63" s="2"/>
@@ -28324,7 +28364,7 @@
       <c r="AG63" s="2"/>
       <c r="AH63" s="23"/>
     </row>
-    <row r="64" spans="1:34" hidden="1">
+    <row r="64" spans="1:34">
       <c r="A64" t="s">
         <v>114</v>
       </c>
@@ -28394,7 +28434,7 @@
       <c r="AG64" s="2"/>
       <c r="AH64" s="23"/>
     </row>
-    <row r="65" spans="1:34" hidden="1">
+    <row r="65" spans="1:34">
       <c r="A65" t="s">
         <v>114</v>
       </c>
@@ -28440,7 +28480,7 @@
       <c r="O65" s="2"/>
       <c r="P65" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" s="2"/>
@@ -28462,7 +28502,7 @@
       <c r="AG65" s="2"/>
       <c r="AH65" s="23"/>
     </row>
-    <row r="66" spans="1:34" hidden="1">
+    <row r="66" spans="1:34">
       <c r="A66" t="s">
         <v>114</v>
       </c>
@@ -28532,7 +28572,7 @@
       <c r="AG66" s="2"/>
       <c r="AH66" s="23"/>
     </row>
-    <row r="67" spans="1:34" hidden="1">
+    <row r="67" spans="1:34">
       <c r="A67" t="s">
         <v>114</v>
       </c>
@@ -28578,7 +28618,7 @@
       <c r="O67" s="2"/>
       <c r="P67" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" s="2"/>
@@ -28646,7 +28686,7 @@
       <c r="O68" s="2"/>
       <c r="P68" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Q68" s="2"/>
       <c r="R68" s="2"/>
@@ -28668,7 +28708,7 @@
       <c r="AG68" s="2"/>
       <c r="AH68" s="23"/>
     </row>
-    <row r="69" spans="1:34" hidden="1">
+    <row r="69" spans="1:34">
       <c r="A69" t="s">
         <v>114</v>
       </c>
@@ -28714,7 +28754,7 @@
       <c r="O69" s="2"/>
       <c r="P69" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" s="2"/>
@@ -28736,7 +28776,7 @@
       <c r="AG69" s="2"/>
       <c r="AH69" s="23"/>
     </row>
-    <row r="70" spans="1:34" hidden="1">
+    <row r="70" spans="1:34">
       <c r="A70" t="s">
         <v>114</v>
       </c>
@@ -28782,7 +28822,7 @@
       <c r="O70" s="2"/>
       <c r="P70" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" s="2"/>
@@ -28804,7 +28844,7 @@
       <c r="AG70" s="2"/>
       <c r="AH70" s="23"/>
     </row>
-    <row r="71" spans="1:34" hidden="1">
+    <row r="71" spans="1:34">
       <c r="A71" t="s">
         <v>114</v>
       </c>
@@ -28850,7 +28890,7 @@
       <c r="O71" s="2"/>
       <c r="P71" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" s="2"/>
@@ -28918,7 +28958,7 @@
       <c r="O72" s="2"/>
       <c r="P72" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q72" s="2"/>
       <c r="R72" s="2"/>
@@ -28940,7 +28980,7 @@
       <c r="AG72" s="2"/>
       <c r="AH72" s="23"/>
     </row>
-    <row r="73" spans="1:34" hidden="1">
+    <row r="73" spans="1:34">
       <c r="A73" t="s">
         <v>114</v>
       </c>
@@ -28986,7 +29026,7 @@
       <c r="O73" s="2"/>
       <c r="P73" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q73" s="2"/>
       <c r="R73" s="2"/>
@@ -29008,7 +29048,7 @@
       <c r="AG73" s="2"/>
       <c r="AH73" s="23"/>
     </row>
-    <row r="74" spans="1:34" hidden="1">
+    <row r="74" spans="1:34">
       <c r="A74" t="s">
         <v>114</v>
       </c>
@@ -29054,7 +29094,7 @@
       <c r="O74" s="130"/>
       <c r="P74" s="131">
         <f t="shared" ca="1" si="25"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q74" s="130"/>
       <c r="R74" s="130"/>
@@ -29076,7 +29116,7 @@
       <c r="AG74" s="2"/>
       <c r="AH74" s="23"/>
     </row>
-    <row r="75" spans="1:34" hidden="1">
+    <row r="75" spans="1:34">
       <c r="A75" t="s">
         <v>114</v>
       </c>
@@ -29122,7 +29162,7 @@
       <c r="O75" s="130"/>
       <c r="P75" s="131">
         <f t="shared" ca="1" si="25"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q75" s="130"/>
       <c r="R75" s="130"/>
@@ -29144,7 +29184,7 @@
       <c r="AG75" s="2"/>
       <c r="AH75" s="23"/>
     </row>
-    <row r="76" spans="1:34" hidden="1">
+    <row r="76" spans="1:34">
       <c r="A76" t="s">
         <v>114</v>
       </c>
@@ -29190,7 +29230,7 @@
       <c r="O76" s="130"/>
       <c r="P76" s="131">
         <f t="shared" ca="1" si="25"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q76" s="130"/>
       <c r="R76" s="130"/>
@@ -29212,7 +29252,7 @@
       <c r="AG76" s="2"/>
       <c r="AH76" s="23"/>
     </row>
-    <row r="77" spans="1:34" hidden="1">
+    <row r="77" spans="1:34">
       <c r="A77" t="s">
         <v>114</v>
       </c>
@@ -29258,7 +29298,7 @@
       <c r="O77" s="130"/>
       <c r="P77" s="131">
         <f t="shared" ca="1" si="25"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Q77" s="130"/>
       <c r="R77" s="130"/>
@@ -29280,7 +29320,7 @@
       <c r="AG77" s="2"/>
       <c r="AH77" s="23"/>
     </row>
-    <row r="78" spans="1:34" hidden="1">
+    <row r="78" spans="1:34">
       <c r="A78" t="s">
         <v>114</v>
       </c>
@@ -29326,7 +29366,7 @@
       <c r="O78" s="130"/>
       <c r="P78" s="131">
         <f t="shared" ca="1" si="25"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q78" s="130"/>
       <c r="R78" s="130"/>
@@ -29348,7 +29388,7 @@
       <c r="AG78" s="2"/>
       <c r="AH78" s="23"/>
     </row>
-    <row r="79" spans="1:34" s="133" customFormat="1" hidden="1">
+    <row r="79" spans="1:34" s="133" customFormat="1">
       <c r="A79" s="133" t="s">
         <v>114</v>
       </c>
@@ -29394,7 +29434,7 @@
       <c r="O79" s="130"/>
       <c r="P79" s="131">
         <f t="shared" ca="1" si="25"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q79" s="130"/>
       <c r="R79" s="130"/>
@@ -29416,7 +29456,7 @@
       <c r="AG79" s="130"/>
       <c r="AH79" s="139"/>
     </row>
-    <row r="80" spans="1:34" s="133" customFormat="1" hidden="1">
+    <row r="80" spans="1:34" s="133" customFormat="1">
       <c r="A80" s="133" t="s">
         <v>114</v>
       </c>
@@ -29483,7 +29523,7 @@
       <c r="AG80" s="130"/>
       <c r="AH80" s="139"/>
     </row>
-    <row r="81" spans="1:34" s="133" customFormat="1" hidden="1">
+    <row r="81" spans="1:34" s="133" customFormat="1">
       <c r="A81" s="133" t="s">
         <v>114</v>
       </c>
@@ -29548,7 +29588,7 @@
       <c r="AG81" s="130"/>
       <c r="AH81" s="139"/>
     </row>
-    <row r="82" spans="1:34" s="133" customFormat="1" hidden="1">
+    <row r="82" spans="1:34" s="133" customFormat="1">
       <c r="A82" s="133" t="s">
         <v>114</v>
       </c>
@@ -29615,7 +29655,7 @@
       <c r="AG82" s="130"/>
       <c r="AH82" s="139"/>
     </row>
-    <row r="83" spans="1:34" s="133" customFormat="1" hidden="1">
+    <row r="83" spans="1:34" s="133" customFormat="1">
       <c r="A83" s="133" t="s">
         <v>114</v>
       </c>
@@ -29682,7 +29722,7 @@
       <c r="AG83" s="130"/>
       <c r="AH83" s="139"/>
     </row>
-    <row r="84" spans="1:34" s="133" customFormat="1" hidden="1">
+    <row r="84" spans="1:34" s="133" customFormat="1">
       <c r="A84" s="133" t="s">
         <v>114</v>
       </c>
@@ -29749,7 +29789,7 @@
       <c r="AG84" s="130"/>
       <c r="AH84" s="139"/>
     </row>
-    <row r="85" spans="1:34" s="133" customFormat="1" hidden="1">
+    <row r="85" spans="1:34" s="133" customFormat="1">
       <c r="A85" s="133" t="s">
         <v>114</v>
       </c>
@@ -29816,7 +29856,7 @@
       <c r="AG85" s="130"/>
       <c r="AH85" s="139"/>
     </row>
-    <row r="86" spans="1:34" s="133" customFormat="1" hidden="1">
+    <row r="86" spans="1:34" s="133" customFormat="1">
       <c r="A86" s="133" t="s">
         <v>114</v>
       </c>
@@ -29946,7 +29986,7 @@
       <c r="AG87" s="130"/>
       <c r="AH87" s="139"/>
     </row>
-    <row r="88" spans="1:34" hidden="1">
+    <row r="88" spans="1:34">
       <c r="A88" t="s">
         <v>114</v>
       </c>
@@ -29983,7 +30023,7 @@
       <c r="AG88" s="2"/>
       <c r="AH88" s="23"/>
     </row>
-    <row r="89" spans="1:34" hidden="1">
+    <row r="89" spans="1:34">
       <c r="A89" t="s">
         <v>114</v>
       </c>
@@ -30020,7 +30060,7 @@
       <c r="AG89" s="2"/>
       <c r="AH89" s="23"/>
     </row>
-    <row r="90" spans="1:34" hidden="1">
+    <row r="90" spans="1:34">
       <c r="A90" t="s">
         <v>114</v>
       </c>
@@ -30057,7 +30097,7 @@
       <c r="AG90" s="2"/>
       <c r="AH90" s="23"/>
     </row>
-    <row r="91" spans="1:34" hidden="1">
+    <row r="91" spans="1:34">
       <c r="A91" t="s">
         <v>114</v>
       </c>
@@ -30094,7 +30134,7 @@
       <c r="AG91" s="2"/>
       <c r="AH91" s="23"/>
     </row>
-    <row r="92" spans="1:34" hidden="1">
+    <row r="92" spans="1:34">
       <c r="A92" t="s">
         <v>114</v>
       </c>
@@ -30131,7 +30171,7 @@
       <c r="AG92" s="2"/>
       <c r="AH92" s="23"/>
     </row>
-    <row r="93" spans="1:34" hidden="1">
+    <row r="93" spans="1:34">
       <c r="A93" t="s">
         <v>114</v>
       </c>
@@ -30168,7 +30208,7 @@
       <c r="AG93" s="2"/>
       <c r="AH93" s="23"/>
     </row>
-    <row r="94" spans="1:34" hidden="1">
+    <row r="94" spans="1:34">
       <c r="A94" t="s">
         <v>114</v>
       </c>
@@ -30205,7 +30245,7 @@
       <c r="AG94" s="2"/>
       <c r="AH94" s="23"/>
     </row>
-    <row r="95" spans="1:34" hidden="1">
+    <row r="95" spans="1:34">
       <c r="A95" t="s">
         <v>114</v>
       </c>
@@ -30242,7 +30282,7 @@
       <c r="AG95" s="2"/>
       <c r="AH95" s="23"/>
     </row>
-    <row r="96" spans="1:34" hidden="1">
+    <row r="96" spans="1:34">
       <c r="A96" t="s">
         <v>114</v>
       </c>
@@ -30279,7 +30319,7 @@
       <c r="AG96" s="2"/>
       <c r="AH96" s="23"/>
     </row>
-    <row r="97" spans="1:34" hidden="1">
+    <row r="97" spans="1:34">
       <c r="A97" t="s">
         <v>114</v>
       </c>
@@ -30316,7 +30356,7 @@
       <c r="AG97" s="2"/>
       <c r="AH97" s="23"/>
     </row>
-    <row r="98" spans="1:34" hidden="1">
+    <row r="98" spans="1:34">
       <c r="A98" t="s">
         <v>114</v>
       </c>
@@ -30353,7 +30393,7 @@
       <c r="AG98" s="2"/>
       <c r="AH98" s="23"/>
     </row>
-    <row r="99" spans="1:34" hidden="1">
+    <row r="99" spans="1:34">
       <c r="A99" t="s">
         <v>114</v>
       </c>
@@ -30390,7 +30430,7 @@
       <c r="AG99" s="2"/>
       <c r="AH99" s="23"/>
     </row>
-    <row r="100" spans="1:34" hidden="1">
+    <row r="100" spans="1:34">
       <c r="A100" t="s">
         <v>114</v>
       </c>
@@ -30427,7 +30467,7 @@
       <c r="AG100" s="2"/>
       <c r="AH100" s="23"/>
     </row>
-    <row r="101" spans="1:34" hidden="1">
+    <row r="101" spans="1:34">
       <c r="A101" t="s">
         <v>114</v>
       </c>
@@ -30464,7 +30504,7 @@
       <c r="AG101" s="2"/>
       <c r="AH101" s="23"/>
     </row>
-    <row r="102" spans="1:34" hidden="1">
+    <row r="102" spans="1:34">
       <c r="A102" t="s">
         <v>114</v>
       </c>
@@ -30501,7 +30541,7 @@
       <c r="AG102" s="2"/>
       <c r="AH102" s="23"/>
     </row>
-    <row r="103" spans="1:34" hidden="1">
+    <row r="103" spans="1:34">
       <c r="A103" t="s">
         <v>114</v>
       </c>
@@ -30538,7 +30578,7 @@
       <c r="AG103" s="2"/>
       <c r="AH103" s="23"/>
     </row>
-    <row r="104" spans="1:34" hidden="1">
+    <row r="104" spans="1:34">
       <c r="A104" t="s">
         <v>114</v>
       </c>
@@ -30575,7 +30615,7 @@
       <c r="AG104" s="2"/>
       <c r="AH104" s="23"/>
     </row>
-    <row r="105" spans="1:34" hidden="1">
+    <row r="105" spans="1:34">
       <c r="A105" t="s">
         <v>114</v>
       </c>
@@ -30612,7 +30652,7 @@
       <c r="AG105" s="2"/>
       <c r="AH105" s="23"/>
     </row>
-    <row r="106" spans="1:34" hidden="1">
+    <row r="106" spans="1:34">
       <c r="A106" t="s">
         <v>114</v>
       </c>
@@ -30649,7 +30689,7 @@
       <c r="AG106" s="2"/>
       <c r="AH106" s="23"/>
     </row>
-    <row r="107" spans="1:34" hidden="1">
+    <row r="107" spans="1:34">
       <c r="A107" t="s">
         <v>114</v>
       </c>
@@ -30686,7 +30726,7 @@
       <c r="AG107" s="2"/>
       <c r="AH107" s="23"/>
     </row>
-    <row r="108" spans="1:34" hidden="1">
+    <row r="108" spans="1:34">
       <c r="A108" t="s">
         <v>114</v>
       </c>
@@ -30723,7 +30763,7 @@
       <c r="AG108" s="2"/>
       <c r="AH108" s="23"/>
     </row>
-    <row r="109" spans="1:34" hidden="1">
+    <row r="109" spans="1:34">
       <c r="A109" t="s">
         <v>114</v>
       </c>
@@ -30760,7 +30800,7 @@
       <c r="AG109" s="2"/>
       <c r="AH109" s="23"/>
     </row>
-    <row r="110" spans="1:34" hidden="1">
+    <row r="110" spans="1:34">
       <c r="A110" t="s">
         <v>114</v>
       </c>
@@ -30797,7 +30837,7 @@
       <c r="AG110" s="2"/>
       <c r="AH110" s="23"/>
     </row>
-    <row r="111" spans="1:34" hidden="1">
+    <row r="111" spans="1:34">
       <c r="A111" t="s">
         <v>114</v>
       </c>
@@ -30834,7 +30874,7 @@
       <c r="AG111" s="2"/>
       <c r="AH111" s="23"/>
     </row>
-    <row r="112" spans="1:34" hidden="1">
+    <row r="112" spans="1:34">
       <c r="A112" t="s">
         <v>114</v>
       </c>
@@ -30871,7 +30911,7 @@
       <c r="AG112" s="2"/>
       <c r="AH112" s="23"/>
     </row>
-    <row r="113" spans="1:34" hidden="1">
+    <row r="113" spans="1:34">
       <c r="A113" t="s">
         <v>114</v>
       </c>
@@ -30908,7 +30948,7 @@
       <c r="AG113" s="2"/>
       <c r="AH113" s="23"/>
     </row>
-    <row r="114" spans="1:34" hidden="1">
+    <row r="114" spans="1:34">
       <c r="A114" t="s">
         <v>114</v>
       </c>
@@ -30945,7 +30985,7 @@
       <c r="AG114" s="2"/>
       <c r="AH114" s="23"/>
     </row>
-    <row r="115" spans="1:34" hidden="1">
+    <row r="115" spans="1:34">
       <c r="A115" t="s">
         <v>114</v>
       </c>
@@ -30982,7 +31022,7 @@
       <c r="AG115" s="2"/>
       <c r="AH115" s="23"/>
     </row>
-    <row r="116" spans="1:34" ht="15.75" hidden="1" thickBot="1">
+    <row r="116" spans="1:34" ht="15.75" thickBot="1">
       <c r="A116" t="s">
         <v>114</v>
       </c>
@@ -31019,7 +31059,7 @@
       <c r="AG116" s="30"/>
       <c r="AH116" s="35"/>
     </row>
-    <row r="117" spans="1:34" ht="15.75" hidden="1" thickBot="1">
+    <row r="117" spans="1:34" ht="15.75" thickBot="1">
       <c r="A117" t="s">
         <v>114</v>
       </c>
@@ -31056,7 +31096,7 @@
       <c r="AG117" s="2"/>
       <c r="AH117" s="23"/>
     </row>
-    <row r="118" spans="1:34" ht="15.75" hidden="1" thickBot="1">
+    <row r="118" spans="1:34" ht="15.75" thickBot="1">
       <c r="A118" t="s">
         <v>114</v>
       </c>
@@ -31120,7 +31160,7 @@
       <c r="AG118" s="10"/>
       <c r="AH118" s="17"/>
     </row>
-    <row r="119" spans="1:34" hidden="1">
+    <row r="119" spans="1:34">
       <c r="A119" t="s">
         <v>56</v>
       </c>
@@ -31129,7 +31169,7 @@
         <v>34014.763000000006</v>
       </c>
     </row>
-    <row r="120" spans="1:34" hidden="1">
+    <row r="120" spans="1:34">
       <c r="A120" t="s">
         <v>56</v>
       </c>
@@ -31143,7 +31183,7 @@
       </c>
       <c r="Z120" s="149"/>
     </row>
-    <row r="121" spans="1:34" ht="15.75" hidden="1" thickBot="1">
+    <row r="121" spans="1:34" ht="15.75" thickBot="1">
       <c r="A121" t="s">
         <v>56</v>
       </c>
@@ -31165,7 +31205,7 @@
       <c r="AG121" s="2"/>
       <c r="AH121" s="1"/>
     </row>
-    <row r="122" spans="1:34" ht="15.75" hidden="1" thickBot="1">
+    <row r="122" spans="1:34" ht="15.75" thickBot="1">
       <c r="A122" t="s">
         <v>56</v>
       </c>
@@ -31260,7 +31300,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="123" spans="1:34" hidden="1">
+    <row r="123" spans="1:34">
       <c r="A123" t="s">
         <v>56</v>
       </c>
@@ -31313,7 +31353,7 @@
       <c r="AG123" s="2"/>
       <c r="AH123" s="23"/>
     </row>
-    <row r="124" spans="1:34" hidden="1">
+    <row r="124" spans="1:34">
       <c r="A124" t="s">
         <v>56</v>
       </c>
@@ -31350,7 +31390,7 @@
       <c r="AG124" s="2"/>
       <c r="AH124" s="23"/>
     </row>
-    <row r="125" spans="1:34" hidden="1">
+    <row r="125" spans="1:34">
       <c r="A125" t="s">
         <v>56</v>
       </c>
@@ -31387,7 +31427,7 @@
       <c r="AG125" s="2"/>
       <c r="AH125" s="23"/>
     </row>
-    <row r="126" spans="1:34" hidden="1">
+    <row r="126" spans="1:34">
       <c r="A126" t="s">
         <v>56</v>
       </c>
@@ -31424,7 +31464,7 @@
       <c r="AG126" s="2"/>
       <c r="AH126" s="23"/>
     </row>
-    <row r="127" spans="1:34" hidden="1">
+    <row r="127" spans="1:34">
       <c r="A127" t="s">
         <v>56</v>
       </c>
@@ -31461,7 +31501,7 @@
       <c r="AG127" s="2"/>
       <c r="AH127" s="23"/>
     </row>
-    <row r="128" spans="1:34" hidden="1">
+    <row r="128" spans="1:34">
       <c r="A128" t="s">
         <v>56</v>
       </c>
@@ -31498,7 +31538,7 @@
       <c r="AG128" s="2"/>
       <c r="AH128" s="23"/>
     </row>
-    <row r="129" spans="1:34" hidden="1">
+    <row r="129" spans="1:34">
       <c r="A129" t="s">
         <v>56</v>
       </c>
@@ -31535,7 +31575,7 @@
       <c r="AG129" s="2"/>
       <c r="AH129" s="23"/>
     </row>
-    <row r="130" spans="1:34" ht="15.75" hidden="1" thickBot="1">
+    <row r="130" spans="1:34" ht="15.75" thickBot="1">
       <c r="A130" t="s">
         <v>56</v>
       </c>
@@ -31572,7 +31612,7 @@
       <c r="AG130" s="30"/>
       <c r="AH130" s="35"/>
     </row>
-    <row r="131" spans="1:34" ht="15.75" hidden="1" thickBot="1">
+    <row r="131" spans="1:34" ht="15.75" thickBot="1">
       <c r="A131" t="s">
         <v>56</v>
       </c>
@@ -31609,7 +31649,7 @@
       <c r="AG131" s="2"/>
       <c r="AH131" s="23"/>
     </row>
-    <row r="132" spans="1:34" ht="15.75" hidden="1" thickBot="1">
+    <row r="132" spans="1:34" ht="15.75" thickBot="1">
       <c r="A132" t="s">
         <v>56</v>
       </c>
@@ -31686,15 +31726,15 @@
       <c r="G135" s="68"/>
       <c r="H135" s="12">
         <f>SUBTOTAL(9,H5:H48)+SUBTOTAL(9,H54:H117)+SUBTOTAL(9,H123:H130)</f>
-        <v>5607.83</v>
+        <v>34014.763000000006</v>
       </c>
       <c r="I135" s="12">
         <f>J135/H135</f>
-        <v>271.16253449337802</v>
+        <v>271.82960129644289</v>
       </c>
       <c r="J135" s="12">
         <f>SUBTOTAL(9,J5:J48)+SUBTOTAL(9,J54:J117)+SUBTOTAL(9,J123:J130)</f>
-        <v>1520633.3958080001</v>
+        <v>9246219.4644829985</v>
       </c>
       <c r="K135" s="68"/>
       <c r="L135" s="68"/>
@@ -31716,27 +31756,23 @@
   </sheetData>
   <autoFilter ref="A2:AH132">
     <filterColumn colId="1" showButton="0"/>
-    <filterColumn colId="4">
-      <filters>
-        <filter val="SHREE RAM YARN TRADING CO."/>
-      </filters>
-    </filterColumn>
+    <filterColumn colId="4"/>
     <filterColumn colId="6"/>
     <filterColumn colId="24" showButton="0"/>
   </autoFilter>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="Y2:Z2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="Y3:Z3"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="Y51:Z51"/>
     <mergeCell ref="B52:C52"/>
     <mergeCell ref="Y52:Z52"/>
     <mergeCell ref="B120:C120"/>
     <mergeCell ref="Y120:Z120"/>
     <mergeCell ref="B121:C121"/>
     <mergeCell ref="Y121:Z121"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="Y3:Z3"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="Y51:Z51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/YarnBook-TEX WEAVES.xlsx
+++ b/YarnBook-TEX WEAVES.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'25-26'!$A$2:$AH$251</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'25-26 JW'!$A$2:$O$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'25-26 JW'!$A$2:$O$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'26-27'!$A$2:$AH$132</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">SHEET!$A$3:$AC$45</definedName>
   </definedNames>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2183" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2228" uniqueCount="338">
   <si>
     <t>H NO</t>
   </si>
@@ -970,6 +970,75 @@
   </si>
   <si>
     <t>JOB15</t>
+  </si>
+  <si>
+    <t>JOB16</t>
+  </si>
+  <si>
+    <t>JOB17</t>
+  </si>
+  <si>
+    <t>JOB18</t>
+  </si>
+  <si>
+    <t>JOB19</t>
+  </si>
+  <si>
+    <t>JOB20</t>
+  </si>
+  <si>
+    <t>JOB21</t>
+  </si>
+  <si>
+    <t>JOB22</t>
+  </si>
+  <si>
+    <t>JOB23</t>
+  </si>
+  <si>
+    <t>JOB24</t>
+  </si>
+  <si>
+    <t>JOB25</t>
+  </si>
+  <si>
+    <t>JOB26</t>
+  </si>
+  <si>
+    <t>JOB27</t>
+  </si>
+  <si>
+    <t>JOB28</t>
+  </si>
+  <si>
+    <t>JOB29</t>
+  </si>
+  <si>
+    <t>JOB30</t>
+  </si>
+  <si>
+    <t>J-10</t>
+  </si>
+  <si>
+    <t>JOB31</t>
+  </si>
+  <si>
+    <t>JOB32</t>
+  </si>
+  <si>
+    <t>JOB33</t>
+  </si>
+  <si>
+    <t>JOB34</t>
+  </si>
+  <si>
+    <t>JOB35</t>
+  </si>
+  <si>
+    <t>JOB36</t>
+  </si>
+  <si>
+    <t>JOB37</t>
   </si>
 </sst>
 </file>
@@ -3229,7 +3298,7 @@
       <c r="O16" s="2"/>
       <c r="P16" s="7">
         <f t="shared" ref="P16:P17" ca="1" si="9">DAYS360(L16,TODAY())-(1)</f>
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
@@ -3301,11 +3370,11 @@
       <c r="O17" s="49"/>
       <c r="P17" s="53">
         <f t="shared" ca="1" si="9"/>
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q17" s="66">
         <f t="shared" ref="Q17:Q26" ca="1" si="10">0.18*P17*M17/365</f>
-        <v>11260.977802993975</v>
+        <v>11293.523981615344</v>
       </c>
       <c r="R17" s="49"/>
       <c r="S17" s="49">
@@ -16795,7 +16864,7 @@
       <c r="O196" s="2"/>
       <c r="P196" s="7">
         <f t="shared" ref="P196:P229" ca="1" si="116">DAYS360(L196,TODAY())-(1)</f>
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q196" s="2"/>
       <c r="R196" s="2"/>
@@ -18014,7 +18083,7 @@
       <c r="O212" s="2"/>
       <c r="P212" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q212" s="2"/>
       <c r="R212" s="2"/>
@@ -18704,7 +18773,7 @@
       <c r="O221" s="2"/>
       <c r="P221" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q221" s="2"/>
       <c r="R221" s="2"/>
@@ -19015,7 +19084,7 @@
       <c r="O225" s="2"/>
       <c r="P225" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q225" s="2"/>
       <c r="R225" s="2"/>
@@ -19087,7 +19156,7 @@
       <c r="O226" s="2"/>
       <c r="P226" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q226" s="2"/>
       <c r="R226" s="2"/>
@@ -19159,7 +19228,7 @@
       <c r="O227" s="2"/>
       <c r="P227" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q227" s="2"/>
       <c r="R227" s="2"/>
@@ -19231,7 +19300,7 @@
       <c r="O228" s="2"/>
       <c r="P228" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Q228" s="2"/>
       <c r="R228" s="2"/>
@@ -19303,7 +19372,7 @@
       <c r="O229" s="2"/>
       <c r="P229" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Q229" s="2"/>
       <c r="R229" s="2"/>
@@ -19797,7 +19866,7 @@
       <c r="O241" s="2"/>
       <c r="P241" s="7">
         <f t="shared" ref="P241" ca="1" si="133">DAYS360(L241,TODAY())-(1)</f>
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q241" s="2"/>
       <c r="R241" s="2"/>
@@ -20381,7 +20450,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P50"/>
+  <dimension ref="A1:P58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="12.28515625" customWidth="1"/>
@@ -20475,7 +20544,7 @@
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="104">
-        <f t="shared" ref="K3:K38" si="0">G3*I3</f>
+        <f t="shared" ref="K3:K40" si="0">G3*I3</f>
         <v>68994.744000000006</v>
       </c>
       <c r="L3" s="106"/>
@@ -20556,7 +20625,7 @@
         <v>13.68</v>
       </c>
       <c r="I5" s="4">
-        <f t="shared" ref="I5:I38" si="1">H5*1.05</f>
+        <f t="shared" ref="I5:I40" si="1">H5*1.05</f>
         <v>14.364000000000001</v>
       </c>
       <c r="J5" s="2"/>
@@ -20566,7 +20635,7 @@
       </c>
       <c r="L5" s="106"/>
       <c r="M5" s="6">
-        <f t="shared" ref="M5:M40" si="2">K5-((G5*H5)*0.02)</f>
+        <f t="shared" ref="M5:M51" si="2">K5-((G5*H5)*0.02)</f>
         <v>113174.0928</v>
       </c>
     </row>
@@ -21452,6 +21521,12 @@
         <f t="shared" si="2"/>
         <v>37551.987200000003</v>
       </c>
+      <c r="O25" s="123">
+        <v>46200</v>
+      </c>
+      <c r="P25" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="26" spans="1:16">
       <c r="A26" s="2">
@@ -21566,9 +21641,15 @@
         <v>38235.288000000008</v>
       </c>
       <c r="L28" s="106"/>
-      <c r="M28" s="6">
+      <c r="M28" s="124">
         <f t="shared" si="2"/>
         <v>37506.996800000008</v>
+      </c>
+      <c r="O28" s="123">
+        <v>46200</v>
+      </c>
+      <c r="P28" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -21604,9 +21685,15 @@
         <v>38281.152000000002</v>
       </c>
       <c r="L29" s="106"/>
-      <c r="M29" s="6">
+      <c r="M29" s="124">
         <f t="shared" si="2"/>
         <v>37551.987200000003</v>
+      </c>
+      <c r="O29" s="123">
+        <v>46200</v>
+      </c>
+      <c r="P29" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -21642,9 +21729,15 @@
         <v>38296.44</v>
       </c>
       <c r="L30" s="106"/>
-      <c r="M30" s="6">
+      <c r="M30" s="124">
         <f t="shared" si="2"/>
         <v>37566.984000000004</v>
+      </c>
+      <c r="O30" s="123">
+        <v>46200</v>
+      </c>
+      <c r="P30" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -21680,9 +21773,15 @@
         <v>38541.048000000003</v>
       </c>
       <c r="L31" s="106"/>
-      <c r="M31" s="6">
+      <c r="M31" s="124">
         <f t="shared" si="2"/>
         <v>37806.932800000002</v>
+      </c>
+      <c r="O31" s="123">
+        <v>46200</v>
+      </c>
+      <c r="P31" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -21725,7 +21824,7 @@
         <v>85087.723199999993</v>
       </c>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:16">
       <c r="A33" s="2">
         <v>31</v>
       </c>
@@ -21765,7 +21864,7 @@
         <v>31896.957600000002</v>
       </c>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:16">
       <c r="A34" s="2">
         <v>32</v>
       </c>
@@ -21798,12 +21897,18 @@
         <v>41308.176000000007</v>
       </c>
       <c r="L34" s="106"/>
-      <c r="M34" s="6">
+      <c r="M34" s="124">
         <f t="shared" si="2"/>
         <v>40521.353600000009</v>
       </c>
-    </row>
-    <row r="35" spans="1:13">
+      <c r="O34" s="123">
+        <v>46200</v>
+      </c>
+      <c r="P34" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
       <c r="A35" s="2">
         <v>33</v>
       </c>
@@ -21836,20 +21941,26 @@
         <v>41369.328000000009</v>
       </c>
       <c r="L35" s="106"/>
-      <c r="M35" s="6">
+      <c r="M35" s="124">
         <f t="shared" si="2"/>
         <v>40581.340800000005</v>
       </c>
-    </row>
-    <row r="36" spans="1:13">
+      <c r="O35" s="123">
+        <v>46200</v>
+      </c>
+      <c r="P35" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
       <c r="A36" s="2">
         <v>34</v>
       </c>
       <c r="B36" s="1">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="C36" s="113">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>209</v>
@@ -21859,7 +21970,7 @@
         <v>210</v>
       </c>
       <c r="G36" s="3">
-        <v>3002</v>
+        <v>2534</v>
       </c>
       <c r="H36" s="4">
         <v>14.56</v>
@@ -21871,23 +21982,29 @@
       <c r="J36" s="2"/>
       <c r="K36" s="104">
         <f t="shared" si="0"/>
-        <v>45894.576000000008</v>
+        <v>38739.792000000009</v>
       </c>
       <c r="L36" s="106"/>
-      <c r="M36" s="6">
+      <c r="M36" s="124">
         <f t="shared" si="2"/>
-        <v>45020.39360000001</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13">
+        <v>38001.891200000005</v>
+      </c>
+      <c r="O36" s="123">
+        <v>46200</v>
+      </c>
+      <c r="P36" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
       <c r="A37" s="2">
         <v>35</v>
       </c>
       <c r="B37" s="1">
-        <v>46182</v>
-      </c>
-      <c r="C37" s="1">
-        <v>46182</v>
+        <v>46177</v>
+      </c>
+      <c r="C37" s="113">
+        <v>46177</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>209</v>
@@ -21897,7 +22014,7 @@
         <v>210</v>
       </c>
       <c r="G37" s="3">
-        <v>2682</v>
+        <v>2514</v>
       </c>
       <c r="H37" s="4">
         <v>14.56</v>
@@ -21909,23 +22026,29 @@
       <c r="J37" s="2"/>
       <c r="K37" s="104">
         <f t="shared" si="0"/>
-        <v>41002.416000000005</v>
+        <v>38434.032000000007</v>
       </c>
       <c r="L37" s="106"/>
-      <c r="M37" s="6">
+      <c r="M37" s="124">
         <f t="shared" si="2"/>
-        <v>40221.417600000008</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13">
+        <v>37701.955200000004</v>
+      </c>
+      <c r="O37" s="123">
+        <v>46200</v>
+      </c>
+      <c r="P37" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
       <c r="A38" s="2">
         <v>36</v>
       </c>
       <c r="B38" s="1">
-        <v>46185</v>
-      </c>
-      <c r="C38" s="1">
-        <v>46185</v>
+        <v>46178</v>
+      </c>
+      <c r="C38" s="113">
+        <v>46178</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>209</v>
@@ -21935,7 +22058,7 @@
         <v>210</v>
       </c>
       <c r="G38" s="3">
-        <v>4283</v>
+        <v>3002</v>
       </c>
       <c r="H38" s="4">
         <v>14.56</v>
@@ -21947,23 +22070,29 @@
       <c r="J38" s="2"/>
       <c r="K38" s="104">
         <f t="shared" si="0"/>
-        <v>65478.504000000008</v>
+        <v>45894.576000000008</v>
       </c>
       <c r="L38" s="106"/>
-      <c r="M38" s="6">
+      <c r="M38" s="124">
         <f t="shared" si="2"/>
-        <v>64231.294400000006</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13">
+        <v>45020.39360000001</v>
+      </c>
+      <c r="O38" s="123">
+        <v>46200</v>
+      </c>
+      <c r="P38" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
       <c r="A39" s="2">
         <v>37</v>
       </c>
       <c r="B39" s="1">
-        <v>46186</v>
+        <v>46182</v>
       </c>
       <c r="C39" s="1">
-        <v>46186</v>
+        <v>46182</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>209</v>
@@ -21973,35 +22102,41 @@
         <v>210</v>
       </c>
       <c r="G39" s="3">
-        <v>1502</v>
+        <v>2682</v>
       </c>
       <c r="H39" s="4">
         <v>14.56</v>
       </c>
       <c r="I39" s="4">
-        <f t="shared" ref="I39:I40" si="3">H39*1.05</f>
+        <f t="shared" si="1"/>
         <v>15.288000000000002</v>
       </c>
       <c r="J39" s="2"/>
       <c r="K39" s="104">
-        <f t="shared" ref="K39:K40" si="4">G39*I39</f>
-        <v>22962.576000000005</v>
+        <f t="shared" si="0"/>
+        <v>41002.416000000005</v>
       </c>
       <c r="L39" s="106"/>
-      <c r="M39" s="6">
+      <c r="M39" s="124">
         <f t="shared" si="2"/>
-        <v>22525.193600000006</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13">
+        <v>40221.417600000008</v>
+      </c>
+      <c r="O39" s="123">
+        <v>46200</v>
+      </c>
+      <c r="P39" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
       <c r="A40" s="2">
         <v>38</v>
       </c>
       <c r="B40" s="1">
-        <v>46186</v>
+        <v>46185</v>
       </c>
       <c r="C40" s="1">
-        <v>46186</v>
+        <v>46185</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>209</v>
@@ -22011,180 +22146,594 @@
         <v>210</v>
       </c>
       <c r="G40" s="3">
-        <v>1036</v>
+        <v>4283</v>
       </c>
       <c r="H40" s="4">
         <v>14.56</v>
       </c>
       <c r="I40" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>15.288000000000002</v>
       </c>
       <c r="J40" s="2"/>
       <c r="K40" s="104">
-        <f t="shared" si="4"/>
-        <v>15838.368000000002</v>
+        <f t="shared" si="0"/>
+        <v>65478.504000000008</v>
       </c>
       <c r="L40" s="106"/>
       <c r="M40" s="6">
         <f t="shared" si="2"/>
+        <v>64231.294400000006</v>
+      </c>
+      <c r="P40" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41" s="2">
+        <v>39</v>
+      </c>
+      <c r="B41" s="1">
+        <v>46186</v>
+      </c>
+      <c r="C41" s="1">
+        <v>46186</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" s="103" t="s">
+        <v>210</v>
+      </c>
+      <c r="G41" s="3">
+        <v>1502</v>
+      </c>
+      <c r="H41" s="4">
+        <v>14.56</v>
+      </c>
+      <c r="I41" s="4">
+        <f t="shared" ref="I41:I45" si="3">H41*1.05</f>
+        <v>15.288000000000002</v>
+      </c>
+      <c r="J41" s="2"/>
+      <c r="K41" s="104">
+        <f t="shared" ref="K41:K45" si="4">G41*I41</f>
+        <v>22962.576000000005</v>
+      </c>
+      <c r="L41" s="106"/>
+      <c r="M41" s="6">
+        <f t="shared" si="2"/>
+        <v>22525.193600000006</v>
+      </c>
+      <c r="P41" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42" s="2">
+        <v>40</v>
+      </c>
+      <c r="B42" s="1">
+        <v>46186</v>
+      </c>
+      <c r="C42" s="1">
+        <v>46186</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" s="103" t="s">
+        <v>210</v>
+      </c>
+      <c r="G42" s="3">
+        <v>1036</v>
+      </c>
+      <c r="H42" s="4">
+        <v>14.56</v>
+      </c>
+      <c r="I42" s="4">
+        <f t="shared" si="3"/>
+        <v>15.288000000000002</v>
+      </c>
+      <c r="J42" s="2"/>
+      <c r="K42" s="104">
+        <f t="shared" si="4"/>
+        <v>15838.368000000002</v>
+      </c>
+      <c r="L42" s="106"/>
+      <c r="M42" s="6">
+        <f t="shared" si="2"/>
         <v>15536.684800000003</v>
       </c>
-    </row>
-    <row r="41" spans="1:13">
-      <c r="A41" s="2"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="103"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="104"/>
-      <c r="L41" s="106"/>
-    </row>
-    <row r="42" spans="1:13">
-      <c r="A42" s="2"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="103"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="2"/>
-      <c r="K42" s="104"/>
-      <c r="L42" s="106"/>
-    </row>
-    <row r="43" spans="1:13">
-      <c r="A43" s="2"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="2"/>
+      <c r="P42" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43" s="2">
+        <v>41</v>
+      </c>
+      <c r="B43" s="1">
+        <v>46188</v>
+      </c>
+      <c r="C43" s="1">
+        <v>46188</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="103"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
+      <c r="F43" s="103" t="s">
+        <v>210</v>
+      </c>
+      <c r="G43" s="3">
+        <v>1826</v>
+      </c>
+      <c r="H43" s="4">
+        <v>14.56</v>
+      </c>
+      <c r="I43" s="4">
+        <f t="shared" si="3"/>
+        <v>15.288000000000002</v>
+      </c>
       <c r="J43" s="2"/>
-      <c r="K43" s="104"/>
+      <c r="K43" s="104">
+        <f t="shared" si="4"/>
+        <v>27915.888000000003</v>
+      </c>
       <c r="L43" s="106"/>
-    </row>
-    <row r="44" spans="1:13">
-      <c r="A44" s="2"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="2"/>
+      <c r="M43" s="6">
+        <f t="shared" si="2"/>
+        <v>27384.156800000004</v>
+      </c>
+      <c r="P43" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44" s="2">
+        <v>42</v>
+      </c>
+      <c r="B44" s="1">
+        <v>46188</v>
+      </c>
+      <c r="C44" s="1">
+        <v>46188</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>211</v>
+      </c>
       <c r="E44" s="2"/>
-      <c r="F44" s="103"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
+      <c r="F44" s="103" t="s">
+        <v>299</v>
+      </c>
+      <c r="G44" s="3">
+        <v>11804</v>
+      </c>
+      <c r="H44" s="4">
+        <v>14.16</v>
+      </c>
+      <c r="I44" s="4">
+        <f t="shared" si="3"/>
+        <v>14.868</v>
+      </c>
       <c r="J44" s="2"/>
-      <c r="K44" s="104"/>
+      <c r="K44" s="104">
+        <f t="shared" si="4"/>
+        <v>175501.872</v>
+      </c>
       <c r="L44" s="106"/>
-    </row>
-    <row r="45" spans="1:13">
-      <c r="A45" s="2"/>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="2"/>
+      <c r="M44" s="6">
+        <f t="shared" si="2"/>
+        <v>172158.9792</v>
+      </c>
+      <c r="P44" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45" s="2">
+        <v>43</v>
+      </c>
+      <c r="B45" s="1">
+        <v>46192</v>
+      </c>
+      <c r="C45" s="1">
+        <v>46192</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="E45" s="2"/>
-      <c r="F45" s="103"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4"/>
+      <c r="F45" s="103" t="s">
+        <v>210</v>
+      </c>
+      <c r="G45" s="3">
+        <v>2865</v>
+      </c>
+      <c r="H45" s="4">
+        <v>14.56</v>
+      </c>
+      <c r="I45" s="4">
+        <f t="shared" si="3"/>
+        <v>15.288000000000002</v>
+      </c>
       <c r="J45" s="2"/>
-      <c r="K45" s="104"/>
+      <c r="K45" s="104">
+        <f t="shared" si="4"/>
+        <v>43800.12</v>
+      </c>
       <c r="L45" s="106"/>
-    </row>
-    <row r="46" spans="1:13">
-      <c r="A46" s="2"/>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="2"/>
+      <c r="M45" s="6">
+        <f t="shared" si="2"/>
+        <v>42965.832000000002</v>
+      </c>
+      <c r="P45" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46" s="2">
+        <v>44</v>
+      </c>
+      <c r="B46" s="1">
+        <v>46192</v>
+      </c>
+      <c r="C46" s="1">
+        <v>46192</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="E46" s="2"/>
-      <c r="F46" s="103"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
+      <c r="F46" s="103" t="s">
+        <v>210</v>
+      </c>
+      <c r="G46" s="3">
+        <v>2986</v>
+      </c>
+      <c r="H46" s="4">
+        <v>14.56</v>
+      </c>
+      <c r="I46" s="4">
+        <f t="shared" ref="I46" si="5">H46*1.05</f>
+        <v>15.288000000000002</v>
+      </c>
       <c r="J46" s="2"/>
-      <c r="K46" s="104"/>
+      <c r="K46" s="104">
+        <f t="shared" ref="K46" si="6">G46*I46</f>
+        <v>45649.968000000008</v>
+      </c>
       <c r="L46" s="106"/>
-    </row>
-    <row r="47" spans="1:13">
-      <c r="A47" s="2"/>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="D47" s="2"/>
+      <c r="M46" s="6">
+        <f t="shared" si="2"/>
+        <v>44780.444800000005</v>
+      </c>
+      <c r="P46" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47" s="2">
+        <v>45</v>
+      </c>
+      <c r="B47" s="1">
+        <v>46194</v>
+      </c>
+      <c r="C47" s="1">
+        <v>46194</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="E47" s="2"/>
-      <c r="F47" s="103"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
+      <c r="F47" s="103" t="s">
+        <v>210</v>
+      </c>
+      <c r="G47" s="3">
+        <v>2574</v>
+      </c>
+      <c r="H47" s="4">
+        <v>14.56</v>
+      </c>
+      <c r="I47" s="4">
+        <f t="shared" ref="I47:I49" si="7">H47*1.05</f>
+        <v>15.288000000000002</v>
+      </c>
       <c r="J47" s="2"/>
-      <c r="K47" s="104"/>
+      <c r="K47" s="104">
+        <f t="shared" ref="K47:K49" si="8">G47*I47</f>
+        <v>39351.312000000005</v>
+      </c>
       <c r="L47" s="106"/>
-    </row>
-    <row r="48" spans="1:13">
-      <c r="A48" s="2"/>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="D48" s="2"/>
+      <c r="M47" s="6">
+        <f t="shared" si="2"/>
+        <v>38601.763200000009</v>
+      </c>
+      <c r="P47" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48" s="2">
+        <v>46</v>
+      </c>
+      <c r="B48" s="1">
+        <v>46194</v>
+      </c>
+      <c r="C48" s="1">
+        <v>46194</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="E48" s="2"/>
-      <c r="F48" s="103"/>
-      <c r="G48" s="3"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
+      <c r="F48" s="103" t="s">
+        <v>210</v>
+      </c>
+      <c r="G48" s="3">
+        <v>2067</v>
+      </c>
+      <c r="H48" s="4">
+        <v>14.56</v>
+      </c>
+      <c r="I48" s="4">
+        <f t="shared" si="7"/>
+        <v>15.288000000000002</v>
+      </c>
       <c r="J48" s="2"/>
-      <c r="K48" s="104"/>
+      <c r="K48" s="104">
+        <f t="shared" si="8"/>
+        <v>31600.296000000006</v>
+      </c>
       <c r="L48" s="106"/>
-    </row>
-    <row r="49" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A49" s="18"/>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="D49" s="2"/>
+      <c r="M48" s="6">
+        <f t="shared" si="2"/>
+        <v>30998.385600000005</v>
+      </c>
+      <c r="P48" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49" s="2">
+        <v>47</v>
+      </c>
+      <c r="B49" s="1">
+        <v>46197</v>
+      </c>
+      <c r="C49" s="1">
+        <v>46197</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="103"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="2"/>
+      <c r="F49" s="103" t="s">
+        <v>210</v>
+      </c>
+      <c r="G49" s="3">
+        <v>2091</v>
+      </c>
+      <c r="H49" s="4">
+        <v>14.56</v>
+      </c>
+      <c r="I49" s="4">
+        <f t="shared" si="7"/>
+        <v>15.288000000000002</v>
+      </c>
       <c r="J49" s="2"/>
-      <c r="K49" s="105"/>
-      <c r="L49" s="36"/>
-    </row>
-    <row r="50" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A50" s="8"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="10"/>
-      <c r="E50" s="10"/>
-      <c r="F50" s="101"/>
-      <c r="G50" s="12">
-        <f>SUBTOTAL(9,G3:G49)</f>
-        <v>111458</v>
-      </c>
-      <c r="H50" s="12">
-        <f>(K50/1.05)/G50</f>
-        <v>14.308004808986345</v>
-      </c>
-      <c r="I50" s="10"/>
-      <c r="J50" s="10"/>
-      <c r="K50" s="107">
-        <f>SUBTOTAL(9,K3:K49)</f>
-        <v>1674478.6800000002</v>
-      </c>
-      <c r="L50" s="108">
-        <f>SUBTOTAL(9,L49:L49)</f>
+      <c r="K49" s="104">
+        <f t="shared" si="8"/>
+        <v>31967.208000000006</v>
+      </c>
+      <c r="L49" s="106"/>
+      <c r="M49" s="6">
+        <f t="shared" si="2"/>
+        <v>31358.308800000006</v>
+      </c>
+      <c r="P49" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50" s="2">
+        <v>48</v>
+      </c>
+      <c r="B50" s="1">
+        <v>46197</v>
+      </c>
+      <c r="C50" s="1">
+        <v>46197</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" s="103" t="s">
+        <v>210</v>
+      </c>
+      <c r="G50" s="3">
+        <v>2013</v>
+      </c>
+      <c r="H50" s="4">
+        <v>14.56</v>
+      </c>
+      <c r="I50" s="4">
+        <f t="shared" ref="I50:I51" si="9">H50*1.05</f>
+        <v>15.288000000000002</v>
+      </c>
+      <c r="J50" s="2"/>
+      <c r="K50" s="104">
+        <f t="shared" ref="K50:K51" si="10">G50*I50</f>
+        <v>30774.744000000002</v>
+      </c>
+      <c r="L50" s="106"/>
+      <c r="M50" s="6">
+        <f t="shared" si="2"/>
+        <v>30188.558400000002</v>
+      </c>
+      <c r="P50" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
+      <c r="A51" s="2">
+        <v>49</v>
+      </c>
+      <c r="B51" s="1">
+        <v>46199</v>
+      </c>
+      <c r="C51" s="1">
+        <v>46199</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" s="103" t="s">
+        <v>210</v>
+      </c>
+      <c r="G51" s="3">
+        <v>1794</v>
+      </c>
+      <c r="H51" s="4">
+        <v>14.56</v>
+      </c>
+      <c r="I51" s="4">
+        <f t="shared" si="9"/>
+        <v>15.288000000000002</v>
+      </c>
+      <c r="J51" s="2"/>
+      <c r="K51" s="104">
+        <f t="shared" si="10"/>
+        <v>27426.672000000002</v>
+      </c>
+      <c r="L51" s="106"/>
+      <c r="M51" s="6">
+        <f t="shared" si="2"/>
+        <v>26904.259200000004</v>
+      </c>
+      <c r="P51" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
+      <c r="A52" s="2">
+        <v>50</v>
+      </c>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="103"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="104"/>
+      <c r="L52" s="106"/>
+    </row>
+    <row r="53" spans="1:16">
+      <c r="A53" s="2"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="103"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="104"/>
+      <c r="L53" s="106"/>
+    </row>
+    <row r="54" spans="1:16">
+      <c r="A54" s="2"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="103"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="104"/>
+      <c r="L54" s="106"/>
+    </row>
+    <row r="55" spans="1:16">
+      <c r="A55" s="2"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="103"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="104"/>
+      <c r="L55" s="106"/>
+    </row>
+    <row r="56" spans="1:16">
+      <c r="A56" s="2"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="103"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="104"/>
+      <c r="L56" s="106"/>
+    </row>
+    <row r="57" spans="1:16" ht="15.75" thickBot="1">
+      <c r="A57" s="18"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="103"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="105"/>
+      <c r="L57" s="36"/>
+    </row>
+    <row r="58" spans="1:16" ht="15.75" thickBot="1">
+      <c r="A58" s="8"/>
+      <c r="B58" s="9"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="101"/>
+      <c r="G58" s="12">
+        <f>SUBTOTAL(9,G3:G57)</f>
+        <v>146526</v>
+      </c>
+      <c r="H58" s="12">
+        <f>(K58/1.05)/G58</f>
+        <v>14.336091069161784</v>
+      </c>
+      <c r="I58" s="10"/>
+      <c r="J58" s="10"/>
+      <c r="K58" s="107">
+        <f>SUBTOTAL(9,K3:K57)</f>
+        <v>2205640.5839999998</v>
+      </c>
+      <c r="L58" s="108">
+        <f>SUBTOTAL(9,L57:L57)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:O39">
+  <autoFilter ref="A2:O42">
     <filterColumn colId="3"/>
     <filterColumn colId="5"/>
   </autoFilter>
@@ -24948,7 +25497,7 @@
       <c r="O6" s="2"/>
       <c r="P6" s="7">
         <f t="shared" ref="P6:P27" ca="1" si="5">DAYS360(L6,TODAY())-(1)</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
@@ -25016,7 +25565,7 @@
       <c r="O7" s="2"/>
       <c r="P7" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
@@ -25084,7 +25633,7 @@
       <c r="O8" s="2"/>
       <c r="P8" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
@@ -25222,7 +25771,7 @@
       <c r="O10" s="2"/>
       <c r="P10" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
@@ -25363,7 +25912,7 @@
       <c r="O12" s="2"/>
       <c r="P12" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
@@ -25431,7 +25980,7 @@
       <c r="O13" s="2"/>
       <c r="P13" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
@@ -25499,7 +26048,7 @@
       <c r="O14" s="2"/>
       <c r="P14" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
@@ -25567,7 +26116,7 @@
       <c r="O15" s="2"/>
       <c r="P15" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
@@ -25635,7 +26184,7 @@
       <c r="O16" s="2"/>
       <c r="P16" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
@@ -25703,7 +26252,7 @@
       <c r="O17" s="2"/>
       <c r="P17" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
@@ -25771,7 +26320,7 @@
       <c r="O18" s="2"/>
       <c r="P18" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
@@ -25839,7 +26388,7 @@
       <c r="O19" s="2"/>
       <c r="P19" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
@@ -25907,7 +26456,7 @@
       <c r="O20" s="2"/>
       <c r="P20" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
@@ -25975,7 +26524,7 @@
       <c r="O21" s="2"/>
       <c r="P21" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
@@ -26043,7 +26592,7 @@
       <c r="O22" s="2"/>
       <c r="P22" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
@@ -26111,7 +26660,7 @@
       <c r="O23" s="2"/>
       <c r="P23" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
@@ -26179,7 +26728,7 @@
       <c r="O24" s="130"/>
       <c r="P24" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q24" s="130"/>
       <c r="R24" s="130"/>
@@ -26247,7 +26796,7 @@
       <c r="O25" s="130"/>
       <c r="P25" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q25" s="130"/>
       <c r="R25" s="130"/>
@@ -26315,7 +26864,7 @@
       <c r="O26" s="130"/>
       <c r="P26" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q26" s="130"/>
       <c r="R26" s="130"/>
@@ -26383,7 +26932,7 @@
       <c r="O27" s="130"/>
       <c r="P27" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q27" s="130"/>
       <c r="R27" s="130"/>
@@ -26451,7 +27000,7 @@
       <c r="O28" s="130"/>
       <c r="P28" s="7">
         <f t="shared" ref="P28:P35" ca="1" si="18">DAYS360(L28,TODAY())-(1)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q28" s="130"/>
       <c r="R28" s="130"/>
@@ -26519,7 +27068,7 @@
       <c r="O29" s="130"/>
       <c r="P29" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q29" s="130"/>
       <c r="R29" s="130"/>
@@ -26587,7 +27136,7 @@
       <c r="O30" s="130"/>
       <c r="P30" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q30" s="130"/>
       <c r="R30" s="130"/>
@@ -26655,7 +27204,7 @@
       <c r="O31" s="130"/>
       <c r="P31" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q31" s="130"/>
       <c r="R31" s="130"/>
@@ -26723,7 +27272,7 @@
       <c r="O32" s="130"/>
       <c r="P32" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q32" s="130"/>
       <c r="R32" s="130"/>
@@ -26791,7 +27340,7 @@
       <c r="O33" s="130"/>
       <c r="P33" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q33" s="130"/>
       <c r="R33" s="130"/>
@@ -26859,7 +27408,7 @@
       <c r="O34" s="130"/>
       <c r="P34" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q34" s="130"/>
       <c r="R34" s="130"/>
@@ -26927,7 +27476,7 @@
       <c r="O35" s="130"/>
       <c r="P35" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q35" s="130"/>
       <c r="R35" s="130"/>
@@ -27928,7 +28477,7 @@
       <c r="O57" s="2"/>
       <c r="P57" s="7">
         <f t="shared" ref="P57:P79" ca="1" si="25">DAYS360(L57,TODAY())-(1)</f>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" s="2"/>
@@ -27996,7 +28545,7 @@
       <c r="O58" s="2"/>
       <c r="P58" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" s="2"/>
@@ -28066,7 +28615,7 @@
       <c r="O59" s="2"/>
       <c r="P59" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" s="2"/>
@@ -28134,7 +28683,7 @@
       <c r="O60" s="2"/>
       <c r="P60" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" s="2"/>
@@ -28202,7 +28751,7 @@
       <c r="O61" s="2"/>
       <c r="P61" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q61" s="2"/>
       <c r="R61" s="2"/>
@@ -28272,7 +28821,7 @@
       <c r="O62" s="2"/>
       <c r="P62" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" s="2"/>
@@ -28342,7 +28891,7 @@
       <c r="O63" s="2"/>
       <c r="P63" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q63" s="2"/>
       <c r="R63" s="2"/>
@@ -28480,7 +29029,7 @@
       <c r="O65" s="2"/>
       <c r="P65" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" s="2"/>
@@ -28618,7 +29167,7 @@
       <c r="O67" s="2"/>
       <c r="P67" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" s="2"/>
@@ -28686,7 +29235,7 @@
       <c r="O68" s="2"/>
       <c r="P68" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q68" s="2"/>
       <c r="R68" s="2"/>
@@ -28754,7 +29303,7 @@
       <c r="O69" s="2"/>
       <c r="P69" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" s="2"/>
@@ -28822,7 +29371,7 @@
       <c r="O70" s="2"/>
       <c r="P70" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" s="2"/>
@@ -28890,7 +29439,7 @@
       <c r="O71" s="2"/>
       <c r="P71" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" s="2"/>
@@ -28958,7 +29507,7 @@
       <c r="O72" s="2"/>
       <c r="P72" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q72" s="2"/>
       <c r="R72" s="2"/>
@@ -29026,7 +29575,7 @@
       <c r="O73" s="2"/>
       <c r="P73" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q73" s="2"/>
       <c r="R73" s="2"/>
@@ -29094,7 +29643,7 @@
       <c r="O74" s="130"/>
       <c r="P74" s="131">
         <f t="shared" ca="1" si="25"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q74" s="130"/>
       <c r="R74" s="130"/>
@@ -29162,7 +29711,7 @@
       <c r="O75" s="130"/>
       <c r="P75" s="131">
         <f t="shared" ca="1" si="25"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q75" s="130"/>
       <c r="R75" s="130"/>
@@ -29230,7 +29779,7 @@
       <c r="O76" s="130"/>
       <c r="P76" s="131">
         <f t="shared" ca="1" si="25"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q76" s="130"/>
       <c r="R76" s="130"/>
@@ -29298,7 +29847,7 @@
       <c r="O77" s="130"/>
       <c r="P77" s="131">
         <f t="shared" ca="1" si="25"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q77" s="130"/>
       <c r="R77" s="130"/>
@@ -29366,7 +29915,7 @@
       <c r="O78" s="130"/>
       <c r="P78" s="131">
         <f t="shared" ca="1" si="25"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q78" s="130"/>
       <c r="R78" s="130"/>
@@ -29434,7 +29983,7 @@
       <c r="O79" s="130"/>
       <c r="P79" s="131">
         <f t="shared" ca="1" si="25"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q79" s="130"/>
       <c r="R79" s="130"/>
@@ -31761,18 +32310,18 @@
     <filterColumn colId="24" showButton="0"/>
   </autoFilter>
   <mergeCells count="12">
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="Y52:Z52"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="Y120:Z120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="Y121:Z121"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="Y2:Z2"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="Y3:Z3"/>
     <mergeCell ref="B51:C51"/>
     <mergeCell ref="Y51:Z51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="Y52:Z52"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="Y120:Z120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="Y121:Z121"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/YarnBook-TEX WEAVES.xlsx
+++ b/YarnBook-TEX WEAVES.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="90" windowWidth="28755" windowHeight="12090" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="90" windowWidth="28755" windowHeight="12090" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="25-26" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2228" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2255" uniqueCount="347">
   <si>
     <t>H NO</t>
   </si>
@@ -1039,6 +1039,33 @@
   </si>
   <si>
     <t>JOB37</t>
+  </si>
+  <si>
+    <t>J-11</t>
+  </si>
+  <si>
+    <t>JOB38</t>
+  </si>
+  <si>
+    <t>JOB39</t>
+  </si>
+  <si>
+    <t>JOB40</t>
+  </si>
+  <si>
+    <t>JOB41</t>
+  </si>
+  <si>
+    <t>JOB42</t>
+  </si>
+  <si>
+    <t>JOB43</t>
+  </si>
+  <si>
+    <t>JOB44</t>
+  </si>
+  <si>
+    <t>J-12</t>
   </si>
 </sst>
 </file>
@@ -3298,7 +3325,7 @@
       <c r="O16" s="2"/>
       <c r="P16" s="7">
         <f t="shared" ref="P16:P17" ca="1" si="9">DAYS360(L16,TODAY())-(1)</f>
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
@@ -3370,11 +3397,11 @@
       <c r="O17" s="49"/>
       <c r="P17" s="53">
         <f t="shared" ca="1" si="9"/>
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="Q17" s="66">
         <f t="shared" ref="Q17:Q26" ca="1" si="10">0.18*P17*M17/365</f>
-        <v>11293.523981615344</v>
+        <v>11586.439589207674</v>
       </c>
       <c r="R17" s="49"/>
       <c r="S17" s="49">
@@ -16864,7 +16891,7 @@
       <c r="O196" s="2"/>
       <c r="P196" s="7">
         <f t="shared" ref="P196:P229" ca="1" si="116">DAYS360(L196,TODAY())-(1)</f>
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="Q196" s="2"/>
       <c r="R196" s="2"/>
@@ -18083,7 +18110,7 @@
       <c r="O212" s="2"/>
       <c r="P212" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="Q212" s="2"/>
       <c r="R212" s="2"/>
@@ -18773,7 +18800,7 @@
       <c r="O221" s="2"/>
       <c r="P221" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="Q221" s="2"/>
       <c r="R221" s="2"/>
@@ -19084,7 +19111,7 @@
       <c r="O225" s="2"/>
       <c r="P225" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="Q225" s="2"/>
       <c r="R225" s="2"/>
@@ -19156,7 +19183,7 @@
       <c r="O226" s="2"/>
       <c r="P226" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="Q226" s="2"/>
       <c r="R226" s="2"/>
@@ -19228,7 +19255,7 @@
       <c r="O227" s="2"/>
       <c r="P227" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="Q227" s="2"/>
       <c r="R227" s="2"/>
@@ -19300,7 +19327,7 @@
       <c r="O228" s="2"/>
       <c r="P228" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="Q228" s="2"/>
       <c r="R228" s="2"/>
@@ -19372,7 +19399,7 @@
       <c r="O229" s="2"/>
       <c r="P229" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="Q229" s="2"/>
       <c r="R229" s="2"/>
@@ -19866,7 +19893,7 @@
       <c r="O241" s="2"/>
       <c r="P241" s="7">
         <f t="shared" ref="P241" ca="1" si="133">DAYS360(L241,TODAY())-(1)</f>
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="Q241" s="2"/>
       <c r="R241" s="2"/>
@@ -20450,7 +20477,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P58"/>
+  <dimension ref="A1:P66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="12.28515625" customWidth="1"/>
@@ -22584,151 +22611,504 @@
         <v>49</v>
       </c>
       <c r="B51" s="1">
-        <v>46199</v>
+        <v>46198</v>
       </c>
       <c r="C51" s="1">
-        <v>46199</v>
+        <v>46198</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="103" t="s">
-        <v>210</v>
+        <v>298</v>
       </c>
       <c r="G51" s="3">
-        <v>1794</v>
+        <v>6553</v>
       </c>
       <c r="H51" s="4">
-        <v>14.56</v>
+        <v>14.16</v>
       </c>
       <c r="I51" s="4">
         <f t="shared" si="9"/>
-        <v>15.288000000000002</v>
+        <v>14.868</v>
       </c>
       <c r="J51" s="2"/>
       <c r="K51" s="104">
         <f t="shared" si="10"/>
-        <v>27426.672000000002</v>
+        <v>97430.004000000001</v>
       </c>
       <c r="L51" s="106"/>
       <c r="M51" s="6">
         <f t="shared" si="2"/>
-        <v>26904.259200000004</v>
+        <v>95574.194400000008</v>
       </c>
       <c r="P51" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="52" spans="1:16">
       <c r="A52" s="2">
         <v>50</v>
       </c>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="D52" s="2"/>
+      <c r="B52" s="1">
+        <v>46199</v>
+      </c>
+      <c r="C52" s="1">
+        <v>46199</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="E52" s="2"/>
-      <c r="F52" s="103"/>
-      <c r="G52" s="3"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
+      <c r="F52" s="103" t="s">
+        <v>210</v>
+      </c>
+      <c r="G52" s="3">
+        <v>1794</v>
+      </c>
+      <c r="H52" s="4">
+        <v>14.56</v>
+      </c>
+      <c r="I52" s="4">
+        <f t="shared" ref="I52:I60" si="11">H52*1.05</f>
+        <v>15.288000000000002</v>
+      </c>
       <c r="J52" s="2"/>
-      <c r="K52" s="104"/>
+      <c r="K52" s="104">
+        <f t="shared" ref="K52:K60" si="12">G52*I52</f>
+        <v>27426.672000000002</v>
+      </c>
       <c r="L52" s="106"/>
+      <c r="M52" s="6">
+        <f t="shared" ref="M52:M60" si="13">K52-((G52*H52)*0.02)</f>
+        <v>26904.259200000004</v>
+      </c>
+      <c r="P52" t="s">
+        <v>337</v>
+      </c>
     </row>
     <row r="53" spans="1:16">
-      <c r="A53" s="2"/>
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
-      <c r="D53" s="2"/>
+      <c r="A53" s="2">
+        <v>51</v>
+      </c>
+      <c r="B53" s="1">
+        <v>46202</v>
+      </c>
+      <c r="C53" s="1">
+        <v>46202</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="E53" s="2"/>
-      <c r="F53" s="103"/>
-      <c r="G53" s="3"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
+      <c r="F53" s="103" t="s">
+        <v>210</v>
+      </c>
+      <c r="G53" s="3">
+        <v>1620</v>
+      </c>
+      <c r="H53" s="4">
+        <v>14.56</v>
+      </c>
+      <c r="I53" s="4">
+        <f t="shared" si="11"/>
+        <v>15.288000000000002</v>
+      </c>
       <c r="J53" s="2"/>
-      <c r="K53" s="104"/>
+      <c r="K53" s="104">
+        <f t="shared" si="12"/>
+        <v>24766.560000000005</v>
+      </c>
       <c r="L53" s="106"/>
+      <c r="M53" s="6">
+        <f t="shared" si="13"/>
+        <v>24294.816000000006</v>
+      </c>
+      <c r="P53" t="s">
+        <v>339</v>
+      </c>
     </row>
     <row r="54" spans="1:16">
-      <c r="A54" s="2"/>
-      <c r="B54" s="1"/>
-      <c r="C54" s="1"/>
-      <c r="D54" s="2"/>
+      <c r="A54" s="2">
+        <v>52</v>
+      </c>
+      <c r="B54" s="1">
+        <v>46203</v>
+      </c>
+      <c r="C54" s="1">
+        <v>46203</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="E54" s="2"/>
-      <c r="F54" s="103"/>
-      <c r="G54" s="3"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
+      <c r="F54" s="103" t="s">
+        <v>210</v>
+      </c>
+      <c r="G54" s="3">
+        <v>3007</v>
+      </c>
+      <c r="H54" s="4">
+        <v>14.56</v>
+      </c>
+      <c r="I54" s="4">
+        <f t="shared" si="11"/>
+        <v>15.288000000000002</v>
+      </c>
       <c r="J54" s="2"/>
-      <c r="K54" s="104"/>
+      <c r="K54" s="104">
+        <f t="shared" si="12"/>
+        <v>45971.016000000003</v>
+      </c>
       <c r="L54" s="106"/>
+      <c r="M54" s="6">
+        <f t="shared" si="13"/>
+        <v>45095.3776</v>
+      </c>
+      <c r="P54" t="s">
+        <v>340</v>
+      </c>
     </row>
     <row r="55" spans="1:16">
-      <c r="A55" s="2"/>
-      <c r="B55" s="1"/>
-      <c r="C55" s="1"/>
-      <c r="D55" s="2"/>
+      <c r="A55" s="2">
+        <v>53</v>
+      </c>
+      <c r="B55" s="1">
+        <v>46206</v>
+      </c>
+      <c r="C55" s="1">
+        <v>46206</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="E55" s="2"/>
-      <c r="F55" s="103"/>
-      <c r="G55" s="3"/>
-      <c r="H55" s="4"/>
-      <c r="I55" s="4"/>
+      <c r="F55" s="103" t="s">
+        <v>210</v>
+      </c>
+      <c r="G55" s="3">
+        <v>1602</v>
+      </c>
+      <c r="H55" s="4">
+        <v>14.56</v>
+      </c>
+      <c r="I55" s="4">
+        <f t="shared" si="11"/>
+        <v>15.288000000000002</v>
+      </c>
       <c r="J55" s="2"/>
-      <c r="K55" s="104"/>
+      <c r="K55" s="104">
+        <f t="shared" si="12"/>
+        <v>24491.376000000004</v>
+      </c>
       <c r="L55" s="106"/>
+      <c r="M55" s="6">
+        <f t="shared" si="13"/>
+        <v>24024.873600000003</v>
+      </c>
+      <c r="P55" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="56" spans="1:16">
-      <c r="A56" s="2"/>
-      <c r="B56" s="1"/>
-      <c r="C56" s="1"/>
-      <c r="D56" s="2"/>
+      <c r="A56" s="2">
+        <v>54</v>
+      </c>
+      <c r="B56" s="1">
+        <v>46206</v>
+      </c>
+      <c r="C56" s="1">
+        <v>46206</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="E56" s="2"/>
-      <c r="F56" s="103"/>
-      <c r="G56" s="3"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4"/>
+      <c r="F56" s="103" t="s">
+        <v>210</v>
+      </c>
+      <c r="G56" s="3">
+        <v>1613</v>
+      </c>
+      <c r="H56" s="4">
+        <v>14.56</v>
+      </c>
+      <c r="I56" s="4">
+        <f t="shared" si="11"/>
+        <v>15.288000000000002</v>
+      </c>
       <c r="J56" s="2"/>
-      <c r="K56" s="104"/>
+      <c r="K56" s="104">
+        <f t="shared" si="12"/>
+        <v>24659.544000000002</v>
+      </c>
       <c r="L56" s="106"/>
-    </row>
-    <row r="57" spans="1:16" ht="15.75" thickBot="1">
-      <c r="A57" s="18"/>
-      <c r="B57" s="1"/>
-      <c r="C57" s="1"/>
-      <c r="D57" s="2"/>
+      <c r="M56" s="6">
+        <f t="shared" si="13"/>
+        <v>24189.838400000001</v>
+      </c>
+      <c r="P56" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16">
+      <c r="A57" s="2">
+        <v>55</v>
+      </c>
+      <c r="B57" s="1">
+        <v>46207</v>
+      </c>
+      <c r="C57" s="1">
+        <v>46207</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="E57" s="2"/>
-      <c r="F57" s="103"/>
-      <c r="G57" s="3"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="2"/>
+      <c r="F57" s="103" t="s">
+        <v>210</v>
+      </c>
+      <c r="G57" s="3">
+        <v>1496</v>
+      </c>
+      <c r="H57" s="4">
+        <v>14.56</v>
+      </c>
+      <c r="I57" s="4">
+        <f t="shared" si="11"/>
+        <v>15.288000000000002</v>
+      </c>
       <c r="J57" s="2"/>
-      <c r="K57" s="105"/>
-      <c r="L57" s="36"/>
-    </row>
-    <row r="58" spans="1:16" ht="15.75" thickBot="1">
-      <c r="A58" s="8"/>
-      <c r="B58" s="9"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="10"/>
-      <c r="E58" s="10"/>
-      <c r="F58" s="101"/>
-      <c r="G58" s="12">
-        <f>SUBTOTAL(9,G3:G57)</f>
-        <v>146526</v>
-      </c>
-      <c r="H58" s="12">
-        <f>(K58/1.05)/G58</f>
-        <v>14.336091069161784</v>
-      </c>
-      <c r="I58" s="10"/>
-      <c r="J58" s="10"/>
-      <c r="K58" s="107">
-        <f>SUBTOTAL(9,K3:K57)</f>
-        <v>2205640.5839999998</v>
-      </c>
-      <c r="L58" s="108">
-        <f>SUBTOTAL(9,L57:L57)</f>
+      <c r="K57" s="104">
+        <f t="shared" si="12"/>
+        <v>22870.848000000002</v>
+      </c>
+      <c r="L57" s="106"/>
+      <c r="M57" s="6">
+        <f t="shared" si="13"/>
+        <v>22435.212800000001</v>
+      </c>
+      <c r="P57" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16">
+      <c r="A58" s="2">
+        <v>56</v>
+      </c>
+      <c r="B58" s="1">
+        <v>46209</v>
+      </c>
+      <c r="C58" s="1">
+        <v>46209</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" s="103" t="s">
+        <v>210</v>
+      </c>
+      <c r="G58" s="3">
+        <v>2008</v>
+      </c>
+      <c r="H58" s="4">
+        <v>14.56</v>
+      </c>
+      <c r="I58" s="4">
+        <f t="shared" si="11"/>
+        <v>15.288000000000002</v>
+      </c>
+      <c r="J58" s="2"/>
+      <c r="K58" s="104">
+        <f t="shared" si="12"/>
+        <v>30698.304000000004</v>
+      </c>
+      <c r="L58" s="106"/>
+      <c r="M58" s="6">
+        <f t="shared" si="13"/>
+        <v>30113.574400000005</v>
+      </c>
+      <c r="P58" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16">
+      <c r="A59" s="2">
+        <v>57</v>
+      </c>
+      <c r="B59" s="1">
+        <v>46209</v>
+      </c>
+      <c r="C59" s="1">
+        <v>46209</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" s="103" t="s">
+        <v>210</v>
+      </c>
+      <c r="G59" s="3">
+        <v>2020</v>
+      </c>
+      <c r="H59" s="4">
+        <v>14.56</v>
+      </c>
+      <c r="I59" s="4">
+        <f t="shared" si="11"/>
+        <v>15.288000000000002</v>
+      </c>
+      <c r="J59" s="2"/>
+      <c r="K59" s="104">
+        <f t="shared" si="12"/>
+        <v>30881.760000000006</v>
+      </c>
+      <c r="L59" s="106"/>
+      <c r="M59" s="6">
+        <f t="shared" si="13"/>
+        <v>30293.536000000007</v>
+      </c>
+      <c r="P59" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
+      <c r="A60" s="2">
+        <v>58</v>
+      </c>
+      <c r="B60" s="1">
+        <v>46209</v>
+      </c>
+      <c r="C60" s="1">
+        <v>46209</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" s="103" t="s">
+        <v>210</v>
+      </c>
+      <c r="G60" s="3">
+        <v>2717</v>
+      </c>
+      <c r="H60" s="4">
+        <v>14.16</v>
+      </c>
+      <c r="I60" s="4">
+        <f t="shared" si="11"/>
+        <v>14.868</v>
+      </c>
+      <c r="J60" s="2"/>
+      <c r="K60" s="104">
+        <f t="shared" si="12"/>
+        <v>40396.356</v>
+      </c>
+      <c r="L60" s="106"/>
+      <c r="M60" s="6">
+        <f t="shared" si="13"/>
+        <v>39626.901599999997</v>
+      </c>
+      <c r="P60" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
+      <c r="A61" s="2"/>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="103"/>
+      <c r="G61" s="3"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="104"/>
+      <c r="L61" s="106"/>
+    </row>
+    <row r="62" spans="1:16">
+      <c r="A62" s="2"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="103"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="104"/>
+      <c r="L62" s="106"/>
+    </row>
+    <row r="63" spans="1:16">
+      <c r="A63" s="2"/>
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="103"/>
+      <c r="G63" s="3"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="104"/>
+      <c r="L63" s="106"/>
+    </row>
+    <row r="64" spans="1:16">
+      <c r="A64" s="2"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="103"/>
+      <c r="G64" s="3"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="2"/>
+      <c r="K64" s="104"/>
+      <c r="L64" s="106"/>
+    </row>
+    <row r="65" spans="1:12" ht="15.75" thickBot="1">
+      <c r="A65" s="18"/>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="103"/>
+      <c r="G65" s="3"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="105"/>
+      <c r="L65" s="36"/>
+    </row>
+    <row r="66" spans="1:12" ht="15.75" thickBot="1">
+      <c r="A66" s="8"/>
+      <c r="B66" s="9"/>
+      <c r="C66" s="9"/>
+      <c r="D66" s="10"/>
+      <c r="E66" s="10"/>
+      <c r="F66" s="101"/>
+      <c r="G66" s="12">
+        <f>SUBTOTAL(9,G3:G65)</f>
+        <v>169162</v>
+      </c>
+      <c r="H66" s="12">
+        <f>(K66/1.05)/G66</f>
+        <v>14.344133079533229</v>
+      </c>
+      <c r="I66" s="10"/>
+      <c r="J66" s="10"/>
+      <c r="K66" s="107">
+        <f>SUBTOTAL(9,K3:K65)</f>
+        <v>2547806.3520000004</v>
+      </c>
+      <c r="L66" s="108">
+        <f>SUBTOTAL(9,L65:L65)</f>
         <v>0</v>
       </c>
     </row>
@@ -25497,7 +25877,7 @@
       <c r="O6" s="2"/>
       <c r="P6" s="7">
         <f t="shared" ref="P6:P27" ca="1" si="5">DAYS360(L6,TODAY())-(1)</f>
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
@@ -25565,7 +25945,7 @@
       <c r="O7" s="2"/>
       <c r="P7" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
@@ -25633,7 +26013,7 @@
       <c r="O8" s="2"/>
       <c r="P8" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
@@ -25771,7 +26151,7 @@
       <c r="O10" s="2"/>
       <c r="P10" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
@@ -25912,7 +26292,7 @@
       <c r="O12" s="2"/>
       <c r="P12" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
@@ -25980,7 +26360,7 @@
       <c r="O13" s="2"/>
       <c r="P13" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
@@ -26048,7 +26428,7 @@
       <c r="O14" s="2"/>
       <c r="P14" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
@@ -26116,7 +26496,7 @@
       <c r="O15" s="2"/>
       <c r="P15" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
@@ -26184,7 +26564,7 @@
       <c r="O16" s="2"/>
       <c r="P16" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
@@ -26252,7 +26632,7 @@
       <c r="O17" s="2"/>
       <c r="P17" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
@@ -26320,7 +26700,7 @@
       <c r="O18" s="2"/>
       <c r="P18" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
@@ -26388,7 +26768,7 @@
       <c r="O19" s="2"/>
       <c r="P19" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
@@ -26456,7 +26836,7 @@
       <c r="O20" s="2"/>
       <c r="P20" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
@@ -26524,7 +26904,7 @@
       <c r="O21" s="2"/>
       <c r="P21" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
@@ -26592,7 +26972,7 @@
       <c r="O22" s="2"/>
       <c r="P22" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
@@ -26660,7 +27040,7 @@
       <c r="O23" s="2"/>
       <c r="P23" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
@@ -26728,7 +27108,7 @@
       <c r="O24" s="130"/>
       <c r="P24" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="Q24" s="130"/>
       <c r="R24" s="130"/>
@@ -26796,7 +27176,7 @@
       <c r="O25" s="130"/>
       <c r="P25" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="Q25" s="130"/>
       <c r="R25" s="130"/>
@@ -26864,7 +27244,7 @@
       <c r="O26" s="130"/>
       <c r="P26" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="Q26" s="130"/>
       <c r="R26" s="130"/>
@@ -26932,7 +27312,7 @@
       <c r="O27" s="130"/>
       <c r="P27" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="Q27" s="130"/>
       <c r="R27" s="130"/>
@@ -27000,7 +27380,7 @@
       <c r="O28" s="130"/>
       <c r="P28" s="7">
         <f t="shared" ref="P28:P35" ca="1" si="18">DAYS360(L28,TODAY())-(1)</f>
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q28" s="130"/>
       <c r="R28" s="130"/>
@@ -27068,7 +27448,7 @@
       <c r="O29" s="130"/>
       <c r="P29" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="Q29" s="130"/>
       <c r="R29" s="130"/>
@@ -27136,7 +27516,7 @@
       <c r="O30" s="130"/>
       <c r="P30" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="Q30" s="130"/>
       <c r="R30" s="130"/>
@@ -27204,7 +27584,7 @@
       <c r="O31" s="130"/>
       <c r="P31" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="Q31" s="130"/>
       <c r="R31" s="130"/>
@@ -27272,7 +27652,7 @@
       <c r="O32" s="130"/>
       <c r="P32" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="Q32" s="130"/>
       <c r="R32" s="130"/>
@@ -27340,7 +27720,7 @@
       <c r="O33" s="130"/>
       <c r="P33" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="Q33" s="130"/>
       <c r="R33" s="130"/>
@@ -27408,7 +27788,7 @@
       <c r="O34" s="130"/>
       <c r="P34" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="Q34" s="130"/>
       <c r="R34" s="130"/>
@@ -27476,7 +27856,7 @@
       <c r="O35" s="130"/>
       <c r="P35" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="Q35" s="130"/>
       <c r="R35" s="130"/>
@@ -28477,7 +28857,7 @@
       <c r="O57" s="2"/>
       <c r="P57" s="7">
         <f t="shared" ref="P57:P79" ca="1" si="25">DAYS360(L57,TODAY())-(1)</f>
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" s="2"/>
@@ -28545,7 +28925,7 @@
       <c r="O58" s="2"/>
       <c r="P58" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" s="2"/>
@@ -28615,7 +28995,7 @@
       <c r="O59" s="2"/>
       <c r="P59" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" s="2"/>
@@ -28683,7 +29063,7 @@
       <c r="O60" s="2"/>
       <c r="P60" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" s="2"/>
@@ -28751,7 +29131,7 @@
       <c r="O61" s="2"/>
       <c r="P61" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="Q61" s="2"/>
       <c r="R61" s="2"/>
@@ -28821,7 +29201,7 @@
       <c r="O62" s="2"/>
       <c r="P62" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" s="2"/>
@@ -28891,7 +29271,7 @@
       <c r="O63" s="2"/>
       <c r="P63" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="Q63" s="2"/>
       <c r="R63" s="2"/>
@@ -29029,7 +29409,7 @@
       <c r="O65" s="2"/>
       <c r="P65" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" s="2"/>
@@ -29167,7 +29547,7 @@
       <c r="O67" s="2"/>
       <c r="P67" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" s="2"/>
@@ -29235,7 +29615,7 @@
       <c r="O68" s="2"/>
       <c r="P68" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="Q68" s="2"/>
       <c r="R68" s="2"/>
@@ -29303,7 +29683,7 @@
       <c r="O69" s="2"/>
       <c r="P69" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" s="2"/>
@@ -29371,7 +29751,7 @@
       <c r="O70" s="2"/>
       <c r="P70" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" s="2"/>
@@ -29439,7 +29819,7 @@
       <c r="O71" s="2"/>
       <c r="P71" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" s="2"/>
@@ -29507,7 +29887,7 @@
       <c r="O72" s="2"/>
       <c r="P72" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="Q72" s="2"/>
       <c r="R72" s="2"/>
@@ -29575,7 +29955,7 @@
       <c r="O73" s="2"/>
       <c r="P73" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q73" s="2"/>
       <c r="R73" s="2"/>
@@ -29643,7 +30023,7 @@
       <c r="O74" s="130"/>
       <c r="P74" s="131">
         <f t="shared" ca="1" si="25"/>
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q74" s="130"/>
       <c r="R74" s="130"/>
@@ -29711,7 +30091,7 @@
       <c r="O75" s="130"/>
       <c r="P75" s="131">
         <f t="shared" ca="1" si="25"/>
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q75" s="130"/>
       <c r="R75" s="130"/>
@@ -29779,7 +30159,7 @@
       <c r="O76" s="130"/>
       <c r="P76" s="131">
         <f t="shared" ca="1" si="25"/>
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q76" s="130"/>
       <c r="R76" s="130"/>
@@ -29847,7 +30227,7 @@
       <c r="O77" s="130"/>
       <c r="P77" s="131">
         <f t="shared" ca="1" si="25"/>
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="Q77" s="130"/>
       <c r="R77" s="130"/>
@@ -29915,7 +30295,7 @@
       <c r="O78" s="130"/>
       <c r="P78" s="131">
         <f t="shared" ca="1" si="25"/>
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q78" s="130"/>
       <c r="R78" s="130"/>
@@ -29983,7 +30363,7 @@
       <c r="O79" s="130"/>
       <c r="P79" s="131">
         <f t="shared" ca="1" si="25"/>
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q79" s="130"/>
       <c r="R79" s="130"/>
@@ -32310,18 +32690,18 @@
     <filterColumn colId="24" showButton="0"/>
   </autoFilter>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="Y2:Z2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="Y3:Z3"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="Y51:Z51"/>
     <mergeCell ref="B52:C52"/>
     <mergeCell ref="Y52:Z52"/>
     <mergeCell ref="B120:C120"/>
     <mergeCell ref="Y120:Z120"/>
     <mergeCell ref="B121:C121"/>
     <mergeCell ref="Y121:Z121"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="Y3:Z3"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="Y51:Z51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/YarnBook-TEX WEAVES.xlsx
+++ b/YarnBook-TEX WEAVES.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'25-26'!$A$2:$AH$251</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'25-26 JW'!$A$2:$O$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'25-26 JW'!$A$2:$O$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'26-27'!$A$2:$AH$132</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">SHEET!$A$3:$AC$45</definedName>
   </definedNames>
@@ -3325,7 +3325,7 @@
       <c r="O16" s="2"/>
       <c r="P16" s="7">
         <f t="shared" ref="P16:P17" ca="1" si="9">DAYS360(L16,TODAY())-(1)</f>
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
@@ -3397,11 +3397,11 @@
       <c r="O17" s="49"/>
       <c r="P17" s="53">
         <f t="shared" ca="1" si="9"/>
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="Q17" s="66">
         <f t="shared" ref="Q17:Q26" ca="1" si="10">0.18*P17*M17/365</f>
-        <v>11586.439589207674</v>
+        <v>11716.624303693154</v>
       </c>
       <c r="R17" s="49"/>
       <c r="S17" s="49">
@@ -16891,7 +16891,7 @@
       <c r="O196" s="2"/>
       <c r="P196" s="7">
         <f t="shared" ref="P196:P229" ca="1" si="116">DAYS360(L196,TODAY())-(1)</f>
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="Q196" s="2"/>
       <c r="R196" s="2"/>
@@ -18110,7 +18110,7 @@
       <c r="O212" s="2"/>
       <c r="P212" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="Q212" s="2"/>
       <c r="R212" s="2"/>
@@ -18800,7 +18800,7 @@
       <c r="O221" s="2"/>
       <c r="P221" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="Q221" s="2"/>
       <c r="R221" s="2"/>
@@ -19111,7 +19111,7 @@
       <c r="O225" s="2"/>
       <c r="P225" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="Q225" s="2"/>
       <c r="R225" s="2"/>
@@ -19183,7 +19183,7 @@
       <c r="O226" s="2"/>
       <c r="P226" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="Q226" s="2"/>
       <c r="R226" s="2"/>
@@ -19255,7 +19255,7 @@
       <c r="O227" s="2"/>
       <c r="P227" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="Q227" s="2"/>
       <c r="R227" s="2"/>
@@ -19327,7 +19327,7 @@
       <c r="O228" s="2"/>
       <c r="P228" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="Q228" s="2"/>
       <c r="R228" s="2"/>
@@ -19399,7 +19399,7 @@
       <c r="O229" s="2"/>
       <c r="P229" s="7">
         <f t="shared" ca="1" si="116"/>
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="Q229" s="2"/>
       <c r="R229" s="2"/>
@@ -19893,7 +19893,7 @@
       <c r="O241" s="2"/>
       <c r="P241" s="7">
         <f t="shared" ref="P241" ca="1" si="133">DAYS360(L241,TODAY())-(1)</f>
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q241" s="2"/>
       <c r="R241" s="2"/>
@@ -20477,6 +20477,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:P66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -20583,7 +20584,7 @@
         <v>46156</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" hidden="1">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -20626,7 +20627,7 @@
         <v>46156</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" hidden="1">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -20661,7 +20662,7 @@
         <v>115371.648</v>
       </c>
       <c r="L5" s="106"/>
-      <c r="M5" s="6">
+      <c r="M5" s="124">
         <f t="shared" ref="M5:M51" si="2">K5-((G5*H5)*0.02)</f>
         <v>113174.0928</v>
       </c>
@@ -21126,7 +21127,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" hidden="1">
       <c r="A16" s="2">
         <v>14</v>
       </c>
@@ -21161,12 +21162,12 @@
         <v>19462.212</v>
       </c>
       <c r="L16" s="106"/>
-      <c r="M16" s="6">
+      <c r="M16" s="124">
         <f t="shared" si="2"/>
         <v>19091.503199999999</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" hidden="1">
       <c r="A17" s="2">
         <v>15</v>
       </c>
@@ -21201,7 +21202,7 @@
         <v>50618.736000000004</v>
       </c>
       <c r="L17" s="106"/>
-      <c r="M17" s="6">
+      <c r="M17" s="124">
         <f t="shared" si="2"/>
         <v>49654.569600000003</v>
       </c>
@@ -21435,7 +21436,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" hidden="1">
       <c r="A23" s="2">
         <v>21</v>
       </c>
@@ -21468,12 +21469,12 @@
         <v>96924.491999999998</v>
       </c>
       <c r="L23" s="106"/>
-      <c r="M23" s="6">
+      <c r="M23" s="124">
         <f t="shared" si="2"/>
         <v>95078.311199999996</v>
       </c>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:16" hidden="1">
       <c r="A24" s="2">
         <v>22</v>
       </c>
@@ -21506,7 +21507,7 @@
         <v>85743.756000000008</v>
       </c>
       <c r="L24" s="106"/>
-      <c r="M24" s="6">
+      <c r="M24" s="124">
         <f t="shared" si="2"/>
         <v>84110.541600000011</v>
       </c>
@@ -21555,7 +21556,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:16" hidden="1">
       <c r="A26" s="2">
         <v>24</v>
       </c>
@@ -21595,7 +21596,7 @@
         <v>57493.281600000002</v>
       </c>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:16" hidden="1">
       <c r="A27" s="2">
         <v>25</v>
       </c>
@@ -21811,7 +21812,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:16" hidden="1">
       <c r="A32" s="2">
         <v>30</v>
       </c>
@@ -21851,7 +21852,7 @@
         <v>85087.723199999993</v>
       </c>
     </row>
-    <row r="33" spans="1:16">
+    <row r="33" spans="1:16" hidden="1">
       <c r="A33" s="2">
         <v>31</v>
       </c>
@@ -22188,7 +22189,7 @@
         <v>65478.504000000008</v>
       </c>
       <c r="L40" s="106"/>
-      <c r="M40" s="6">
+      <c r="M40" s="124">
         <f t="shared" si="2"/>
         <v>64231.294400000006</v>
       </c>
@@ -22229,7 +22230,7 @@
         <v>22962.576000000005</v>
       </c>
       <c r="L41" s="106"/>
-      <c r="M41" s="6">
+      <c r="M41" s="124">
         <f t="shared" si="2"/>
         <v>22525.193600000006</v>
       </c>
@@ -22270,7 +22271,7 @@
         <v>15838.368000000002</v>
       </c>
       <c r="L42" s="106"/>
-      <c r="M42" s="6">
+      <c r="M42" s="124">
         <f t="shared" si="2"/>
         <v>15536.684800000003</v>
       </c>
@@ -22311,7 +22312,7 @@
         <v>27915.888000000003</v>
       </c>
       <c r="L43" s="106"/>
-      <c r="M43" s="6">
+      <c r="M43" s="124">
         <f t="shared" si="2"/>
         <v>27384.156800000004</v>
       </c>
@@ -22319,7 +22320,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="44" spans="1:16">
+    <row r="44" spans="1:16" hidden="1">
       <c r="A44" s="2">
         <v>42</v>
       </c>
@@ -22606,7 +22607,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="51" spans="1:16">
+    <row r="51" spans="1:16" hidden="1">
       <c r="A51" s="2">
         <v>49</v>
       </c>
@@ -22975,7 +22976,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="60" spans="1:16">
+    <row r="60" spans="1:16" hidden="1">
       <c r="A60" s="2">
         <v>58</v>
       </c>
@@ -23095,17 +23096,17 @@
       <c r="F66" s="101"/>
       <c r="G66" s="12">
         <f>SUBTOTAL(9,G3:G65)</f>
-        <v>169162</v>
+        <v>101248</v>
       </c>
       <c r="H66" s="12">
         <f>(K66/1.05)/G66</f>
-        <v>14.344133079533229</v>
+        <v>14.560000000000004</v>
       </c>
       <c r="I66" s="10"/>
       <c r="J66" s="10"/>
       <c r="K66" s="107">
         <f>SUBTOTAL(9,K3:K65)</f>
-        <v>2547806.3520000004</v>
+        <v>1547879.4240000003</v>
       </c>
       <c r="L66" s="108">
         <f>SUBTOTAL(9,L65:L65)</f>
@@ -23113,8 +23114,12 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:O42">
-    <filterColumn colId="3"/>
+  <autoFilter ref="A2:O60">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="M S D TEXTILE"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="5"/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -25877,7 +25882,7 @@
       <c r="O6" s="2"/>
       <c r="P6" s="7">
         <f t="shared" ref="P6:P27" ca="1" si="5">DAYS360(L6,TODAY())-(1)</f>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
@@ -25945,7 +25950,7 @@
       <c r="O7" s="2"/>
       <c r="P7" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
@@ -26013,7 +26018,7 @@
       <c r="O8" s="2"/>
       <c r="P8" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
@@ -26151,7 +26156,7 @@
       <c r="O10" s="2"/>
       <c r="P10" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
@@ -26292,7 +26297,7 @@
       <c r="O12" s="2"/>
       <c r="P12" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
@@ -26360,7 +26365,7 @@
       <c r="O13" s="2"/>
       <c r="P13" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
@@ -26428,7 +26433,7 @@
       <c r="O14" s="2"/>
       <c r="P14" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
@@ -26496,7 +26501,7 @@
       <c r="O15" s="2"/>
       <c r="P15" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
@@ -26564,7 +26569,7 @@
       <c r="O16" s="2"/>
       <c r="P16" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
@@ -26632,7 +26637,7 @@
       <c r="O17" s="2"/>
       <c r="P17" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
@@ -26700,7 +26705,7 @@
       <c r="O18" s="2"/>
       <c r="P18" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
@@ -26768,7 +26773,7 @@
       <c r="O19" s="2"/>
       <c r="P19" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
@@ -26836,7 +26841,7 @@
       <c r="O20" s="2"/>
       <c r="P20" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
@@ -26904,7 +26909,7 @@
       <c r="O21" s="2"/>
       <c r="P21" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
@@ -26972,7 +26977,7 @@
       <c r="O22" s="2"/>
       <c r="P22" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
@@ -27040,7 +27045,7 @@
       <c r="O23" s="2"/>
       <c r="P23" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
@@ -27108,7 +27113,7 @@
       <c r="O24" s="130"/>
       <c r="P24" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="Q24" s="130"/>
       <c r="R24" s="130"/>
@@ -27176,7 +27181,7 @@
       <c r="O25" s="130"/>
       <c r="P25" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="Q25" s="130"/>
       <c r="R25" s="130"/>
@@ -27244,7 +27249,7 @@
       <c r="O26" s="130"/>
       <c r="P26" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="Q26" s="130"/>
       <c r="R26" s="130"/>
@@ -27312,7 +27317,7 @@
       <c r="O27" s="130"/>
       <c r="P27" s="7">
         <f t="shared" ca="1" si="5"/>
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="Q27" s="130"/>
       <c r="R27" s="130"/>
@@ -27380,7 +27385,7 @@
       <c r="O28" s="130"/>
       <c r="P28" s="7">
         <f t="shared" ref="P28:P35" ca="1" si="18">DAYS360(L28,TODAY())-(1)</f>
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="Q28" s="130"/>
       <c r="R28" s="130"/>
@@ -27448,7 +27453,7 @@
       <c r="O29" s="130"/>
       <c r="P29" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Q29" s="130"/>
       <c r="R29" s="130"/>
@@ -27516,7 +27521,7 @@
       <c r="O30" s="130"/>
       <c r="P30" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="Q30" s="130"/>
       <c r="R30" s="130"/>
@@ -27584,7 +27589,7 @@
       <c r="O31" s="130"/>
       <c r="P31" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="Q31" s="130"/>
       <c r="R31" s="130"/>
@@ -27652,7 +27657,7 @@
       <c r="O32" s="130"/>
       <c r="P32" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="Q32" s="130"/>
       <c r="R32" s="130"/>
@@ -27720,7 +27725,7 @@
       <c r="O33" s="130"/>
       <c r="P33" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q33" s="130"/>
       <c r="R33" s="130"/>
@@ -27788,7 +27793,7 @@
       <c r="O34" s="130"/>
       <c r="P34" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Q34" s="130"/>
       <c r="R34" s="130"/>
@@ -27856,7 +27861,7 @@
       <c r="O35" s="130"/>
       <c r="P35" s="7">
         <f t="shared" ca="1" si="18"/>
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Q35" s="130"/>
       <c r="R35" s="130"/>
@@ -28857,7 +28862,7 @@
       <c r="O57" s="2"/>
       <c r="P57" s="7">
         <f t="shared" ref="P57:P79" ca="1" si="25">DAYS360(L57,TODAY())-(1)</f>
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" s="2"/>
@@ -28925,7 +28930,7 @@
       <c r="O58" s="2"/>
       <c r="P58" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" s="2"/>
@@ -28995,7 +29000,7 @@
       <c r="O59" s="2"/>
       <c r="P59" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" s="2"/>
@@ -29063,7 +29068,7 @@
       <c r="O60" s="2"/>
       <c r="P60" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" s="2"/>
@@ -29131,7 +29136,7 @@
       <c r="O61" s="2"/>
       <c r="P61" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="Q61" s="2"/>
       <c r="R61" s="2"/>
@@ -29201,7 +29206,7 @@
       <c r="O62" s="2"/>
       <c r="P62" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" s="2"/>
@@ -29271,7 +29276,7 @@
       <c r="O63" s="2"/>
       <c r="P63" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="Q63" s="2"/>
       <c r="R63" s="2"/>
@@ -29409,7 +29414,7 @@
       <c r="O65" s="2"/>
       <c r="P65" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" s="2"/>
@@ -29547,7 +29552,7 @@
       <c r="O67" s="2"/>
       <c r="P67" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" s="2"/>
@@ -29615,7 +29620,7 @@
       <c r="O68" s="2"/>
       <c r="P68" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="Q68" s="2"/>
       <c r="R68" s="2"/>
@@ -29683,7 +29688,7 @@
       <c r="O69" s="2"/>
       <c r="P69" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" s="2"/>
@@ -29751,7 +29756,7 @@
       <c r="O70" s="2"/>
       <c r="P70" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" s="2"/>
@@ -29819,7 +29824,7 @@
       <c r="O71" s="2"/>
       <c r="P71" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" s="2"/>
@@ -29887,7 +29892,7 @@
       <c r="O72" s="2"/>
       <c r="P72" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="Q72" s="2"/>
       <c r="R72" s="2"/>
@@ -29955,7 +29960,7 @@
       <c r="O73" s="2"/>
       <c r="P73" s="7">
         <f t="shared" ca="1" si="25"/>
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="Q73" s="2"/>
       <c r="R73" s="2"/>
@@ -30023,7 +30028,7 @@
       <c r="O74" s="130"/>
       <c r="P74" s="131">
         <f t="shared" ca="1" si="25"/>
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="Q74" s="130"/>
       <c r="R74" s="130"/>
@@ -30091,7 +30096,7 @@
       <c r="O75" s="130"/>
       <c r="P75" s="131">
         <f t="shared" ca="1" si="25"/>
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="Q75" s="130"/>
       <c r="R75" s="130"/>
@@ -30159,7 +30164,7 @@
       <c r="O76" s="130"/>
       <c r="P76" s="131">
         <f t="shared" ca="1" si="25"/>
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="Q76" s="130"/>
       <c r="R76" s="130"/>
@@ -30227,7 +30232,7 @@
       <c r="O77" s="130"/>
       <c r="P77" s="131">
         <f t="shared" ca="1" si="25"/>
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="Q77" s="130"/>
       <c r="R77" s="130"/>
@@ -30295,7 +30300,7 @@
       <c r="O78" s="130"/>
       <c r="P78" s="131">
         <f t="shared" ca="1" si="25"/>
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="Q78" s="130"/>
       <c r="R78" s="130"/>
@@ -30363,7 +30368,7 @@
       <c r="O79" s="130"/>
       <c r="P79" s="131">
         <f t="shared" ca="1" si="25"/>
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="Q79" s="130"/>
       <c r="R79" s="130"/>
@@ -32690,18 +32695,18 @@
     <filterColumn colId="24" showButton="0"/>
   </autoFilter>
   <mergeCells count="12">
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="Y52:Z52"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="Y120:Z120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="Y121:Z121"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="Y2:Z2"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="Y3:Z3"/>
     <mergeCell ref="B51:C51"/>
     <mergeCell ref="Y51:Z51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="Y52:Z52"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="Y120:Z120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="Y121:Z121"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
